--- a/datos/Malla_Curricular_LLYA.xlsx
+++ b/datos/Malla_Curricular_LLYA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Analsis_coding\estimacion_infraestructura\Consumo_horas_educacion_secundaria\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consumo_horas_educacion_secundaria\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E407127-F117-4506-AE32-9F255080A154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024B4E04-5757-437C-BE6D-35C849F1C0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Malla_Curricular_LLYM" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="91">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -592,23 +592,24 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:O1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="23.109375" customWidth="1"/>
-    <col min="3" max="3" width="36.109375" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
-    <col min="5" max="6" width="12.5546875" customWidth="1"/>
-    <col min="7" max="8" width="18" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" customWidth="1"/>
-    <col min="11" max="11" width="19.6640625" customWidth="1"/>
-    <col min="12" max="12" width="25.5546875" customWidth="1"/>
-    <col min="13" max="13" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="8" width="18" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.5703125" customWidth="1"/>
+    <col min="13" max="13" width="23.42578125" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -655,7 +656,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -703,7 +704,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>15</v>
       </c>
@@ -751,7 +752,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
@@ -799,7 +800,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -844,7 +845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -889,7 +890,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -934,7 +935,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
@@ -979,7 +980,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1027,7 +1028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1075,7 +1076,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>15</v>
       </c>
@@ -1123,7 +1124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>15</v>
       </c>
@@ -1171,7 +1172,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
@@ -1219,7 +1220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
@@ -1264,7 +1265,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>15</v>
       </c>
@@ -1306,13 +1307,13 @@
         <v>21</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="O15" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1360,7 +1361,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -1408,7 +1409,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
@@ -1456,7 +1457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
@@ -1504,7 +1505,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>15</v>
       </c>
@@ -1552,7 +1553,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
@@ -1600,7 +1601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>15</v>
       </c>
@@ -1639,13 +1640,13 @@
         <v>4</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
@@ -1693,7 +1694,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>15</v>
       </c>
@@ -1741,7 +1742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>15</v>
       </c>
@@ -1789,7 +1790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>15</v>
       </c>
@@ -1834,7 +1835,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>15</v>
       </c>
@@ -1882,7 +1883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>15</v>
       </c>
@@ -1930,7 +1931,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
@@ -1978,7 +1979,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>15</v>
       </c>
@@ -2026,7 +2027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>15</v>
       </c>
@@ -2071,7 +2072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
         <v>15</v>
       </c>
@@ -2119,7 +2120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>15</v>
       </c>
@@ -2167,7 +2168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>15</v>
       </c>
@@ -2215,7 +2216,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>15</v>
       </c>
@@ -2263,7 +2264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>15</v>
       </c>
@@ -2311,7 +2312,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>15</v>
       </c>
@@ -2359,7 +2360,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>15</v>
       </c>
@@ -2404,7 +2405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
@@ -2452,7 +2453,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>15</v>
       </c>
@@ -2500,7 +2501,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>15</v>
       </c>
@@ -2548,7 +2549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>15</v>
       </c>
@@ -2596,7 +2597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>15</v>
       </c>
@@ -2644,7 +2645,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>15</v>
       </c>
@@ -2692,7 +2693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>15</v>
       </c>
@@ -2737,7 +2738,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>15</v>
       </c>
@@ -2785,7 +2786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>15</v>
       </c>
@@ -2833,7 +2834,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>15</v>
       </c>
@@ -2881,7 +2882,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>15</v>
       </c>
@@ -2929,7 +2930,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>15</v>
       </c>
@@ -2974,7 +2975,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>15</v>
       </c>
@@ -3022,7 +3023,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>15</v>
       </c>
@@ -3070,7 +3071,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
         <v>15</v>
       </c>
@@ -3118,7 +3119,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
         <v>15</v>
       </c>
@@ -3163,7 +3164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
         <v>15</v>
       </c>
@@ -3211,7 +3212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
         <v>15</v>
       </c>
@@ -3259,7 +3260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
         <v>15</v>
       </c>
@@ -3307,7 +3308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
         <v>15</v>
       </c>
@@ -3355,7 +3356,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>15</v>
       </c>
@@ -3403,7 +3404,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>15</v>
       </c>
@@ -3451,7 +3452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
         <v>15</v>
       </c>
@@ -3483,23 +3484,21 @@
         <v>4</v>
       </c>
       <c r="K61" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L61" s="4">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N61" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="N61" s="5"/>
       <c r="O61" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>15</v>
       </c>
@@ -3547,7 +3546,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>15</v>
       </c>
@@ -3595,7 +3594,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>15</v>
       </c>
@@ -3643,7 +3642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
         <v>15</v>
       </c>
@@ -3691,7 +3690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
         <v>15</v>
       </c>
@@ -3723,23 +3722,21 @@
         <v>4</v>
       </c>
       <c r="K66" s="5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L66" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="N66" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="N66" s="5"/>
       <c r="O66" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -3752,7 +3749,7 @@
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
     </row>
-    <row r="68" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
@@ -3765,7 +3762,7 @@
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
     </row>
-    <row r="69" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
@@ -3778,7 +3775,7 @@
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
     </row>
-    <row r="70" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
@@ -3791,7 +3788,7 @@
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
     </row>
-    <row r="71" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
@@ -3804,7 +3801,7 @@
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
     </row>
-    <row r="72" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
@@ -3817,7 +3814,7 @@
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
     </row>
-    <row r="73" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
@@ -3830,7 +3827,7 @@
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
     </row>
-    <row r="74" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
@@ -3843,7 +3840,7 @@
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
     </row>
-    <row r="75" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
@@ -3856,7 +3853,7 @@
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
@@ -3869,7 +3866,7 @@
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
     </row>
-    <row r="77" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
@@ -3882,7 +3879,7 @@
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
     </row>
-    <row r="78" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
@@ -3895,7 +3892,7 @@
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
     </row>
-    <row r="79" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
@@ -3908,7 +3905,7 @@
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
     </row>
-    <row r="80" spans="1:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
@@ -3921,7 +3918,7 @@
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
     </row>
-    <row r="81" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
@@ -3934,7 +3931,7 @@
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
     </row>
-    <row r="82" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
@@ -3947,7 +3944,7 @@
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
     </row>
-    <row r="83" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
@@ -3960,7 +3957,7 @@
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
     </row>
-    <row r="84" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
@@ -3973,7 +3970,7 @@
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
     </row>
-    <row r="85" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
@@ -3986,7 +3983,7 @@
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
@@ -3999,7 +3996,7 @@
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
     </row>
-    <row r="87" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
@@ -4012,7 +4009,7 @@
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
     </row>
-    <row r="88" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
@@ -4025,7 +4022,7 @@
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
     </row>
-    <row r="89" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
@@ -4038,7 +4035,7 @@
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
     </row>
-    <row r="90" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
@@ -4051,7 +4048,7 @@
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
     </row>
-    <row r="91" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
@@ -4064,7 +4061,7 @@
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
     </row>
-    <row r="92" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
@@ -4077,7 +4074,7 @@
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
     </row>
-    <row r="93" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -4090,7 +4087,7 @@
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
     </row>
-    <row r="94" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
@@ -4103,7 +4100,7 @@
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
     </row>
-    <row r="95" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
@@ -4116,7 +4113,7 @@
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
     </row>
-    <row r="96" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
@@ -4129,7 +4126,7 @@
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
     </row>
-    <row r="97" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
@@ -4142,7 +4139,7 @@
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
     </row>
-    <row r="98" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
@@ -4155,7 +4152,7 @@
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
     </row>
-    <row r="99" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
@@ -4168,7 +4165,7 @@
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
     </row>
-    <row r="100" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
@@ -4181,7 +4178,7 @@
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
     </row>
-    <row r="101" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
@@ -4194,7 +4191,7 @@
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
     </row>
-    <row r="102" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
@@ -4207,7 +4204,7 @@
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
     </row>
-    <row r="103" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
@@ -4220,7 +4217,7 @@
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
     </row>
-    <row r="104" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
@@ -4233,7 +4230,7 @@
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
     </row>
-    <row r="105" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
@@ -4246,7 +4243,7 @@
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
     </row>
-    <row r="106" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
@@ -4259,7 +4256,7 @@
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
     </row>
-    <row r="107" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
@@ -4272,7 +4269,7 @@
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
     </row>
-    <row r="108" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
@@ -4285,7 +4282,7 @@
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
     </row>
-    <row r="109" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
@@ -4298,7 +4295,7 @@
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
     </row>
-    <row r="110" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
@@ -4311,7 +4308,7 @@
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
     </row>
-    <row r="111" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
@@ -4324,7 +4321,7 @@
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
     </row>
-    <row r="112" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
@@ -4337,7 +4334,7 @@
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
     </row>
-    <row r="113" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
@@ -4350,7 +4347,7 @@
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
     </row>
-    <row r="114" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
@@ -4363,7 +4360,7 @@
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
     </row>
-    <row r="115" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
@@ -4376,7 +4373,7 @@
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
     </row>
-    <row r="116" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
@@ -4389,7 +4386,7 @@
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
     </row>
-    <row r="117" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
@@ -4402,7 +4399,7 @@
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
     </row>
-    <row r="118" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
@@ -4415,7 +4412,7 @@
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
     </row>
-    <row r="119" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
@@ -4428,7 +4425,7 @@
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
     </row>
-    <row r="120" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
@@ -4441,7 +4438,7 @@
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
     </row>
-    <row r="121" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
@@ -4454,7 +4451,7 @@
       <c r="N121" s="4"/>
       <c r="O121" s="4"/>
     </row>
-    <row r="122" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
@@ -4467,7 +4464,7 @@
       <c r="N122" s="4"/>
       <c r="O122" s="4"/>
     </row>
-    <row r="123" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
@@ -4480,7 +4477,7 @@
       <c r="N123" s="4"/>
       <c r="O123" s="4"/>
     </row>
-    <row r="124" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
@@ -4493,7 +4490,7 @@
       <c r="N124" s="4"/>
       <c r="O124" s="4"/>
     </row>
-    <row r="125" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
@@ -4506,7 +4503,7 @@
       <c r="N125" s="4"/>
       <c r="O125" s="4"/>
     </row>
-    <row r="126" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
@@ -4519,7 +4516,7 @@
       <c r="N126" s="4"/>
       <c r="O126" s="4"/>
     </row>
-    <row r="127" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
@@ -4532,7 +4529,7 @@
       <c r="N127" s="4"/>
       <c r="O127" s="4"/>
     </row>
-    <row r="128" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
@@ -4545,7 +4542,7 @@
       <c r="N128" s="4"/>
       <c r="O128" s="4"/>
     </row>
-    <row r="129" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
@@ -4558,7 +4555,7 @@
       <c r="N129" s="4"/>
       <c r="O129" s="4"/>
     </row>
-    <row r="130" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
@@ -4571,7 +4568,7 @@
       <c r="N130" s="4"/>
       <c r="O130" s="4"/>
     </row>
-    <row r="131" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
@@ -4584,7 +4581,7 @@
       <c r="N131" s="4"/>
       <c r="O131" s="4"/>
     </row>
-    <row r="132" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
@@ -4597,7 +4594,7 @@
       <c r="N132" s="4"/>
       <c r="O132" s="4"/>
     </row>
-    <row r="133" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
@@ -4610,7 +4607,7 @@
       <c r="N133" s="4"/>
       <c r="O133" s="4"/>
     </row>
-    <row r="134" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
@@ -4623,7 +4620,7 @@
       <c r="N134" s="4"/>
       <c r="O134" s="4"/>
     </row>
-    <row r="135" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
@@ -4636,7 +4633,7 @@
       <c r="N135" s="4"/>
       <c r="O135" s="4"/>
     </row>
-    <row r="136" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
@@ -4649,7 +4646,7 @@
       <c r="N136" s="4"/>
       <c r="O136" s="4"/>
     </row>
-    <row r="137" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
@@ -4662,7 +4659,7 @@
       <c r="N137" s="4"/>
       <c r="O137" s="4"/>
     </row>
-    <row r="138" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
@@ -4675,7 +4672,7 @@
       <c r="N138" s="4"/>
       <c r="O138" s="4"/>
     </row>
-    <row r="139" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
@@ -4688,7 +4685,7 @@
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
     </row>
-    <row r="140" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
@@ -4701,7 +4698,7 @@
       <c r="N140" s="4"/>
       <c r="O140" s="4"/>
     </row>
-    <row r="141" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
@@ -4714,7 +4711,7 @@
       <c r="N141" s="4"/>
       <c r="O141" s="4"/>
     </row>
-    <row r="142" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
@@ -4727,7 +4724,7 @@
       <c r="N142" s="4"/>
       <c r="O142" s="4"/>
     </row>
-    <row r="143" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
@@ -4740,7 +4737,7 @@
       <c r="N143" s="4"/>
       <c r="O143" s="4"/>
     </row>
-    <row r="144" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
@@ -4753,7 +4750,7 @@
       <c r="N144" s="4"/>
       <c r="O144" s="4"/>
     </row>
-    <row r="145" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
@@ -4766,7 +4763,7 @@
       <c r="N145" s="4"/>
       <c r="O145" s="4"/>
     </row>
-    <row r="146" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
@@ -4779,7 +4776,7 @@
       <c r="N146" s="4"/>
       <c r="O146" s="4"/>
     </row>
-    <row r="147" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
@@ -4792,7 +4789,7 @@
       <c r="N147" s="4"/>
       <c r="O147" s="4"/>
     </row>
-    <row r="148" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
@@ -4805,7 +4802,7 @@
       <c r="N148" s="4"/>
       <c r="O148" s="4"/>
     </row>
-    <row r="149" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
@@ -4818,7 +4815,7 @@
       <c r="N149" s="4"/>
       <c r="O149" s="4"/>
     </row>
-    <row r="150" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
@@ -4831,7 +4828,7 @@
       <c r="N150" s="4"/>
       <c r="O150" s="4"/>
     </row>
-    <row r="151" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
@@ -4844,7 +4841,7 @@
       <c r="N151" s="4"/>
       <c r="O151" s="4"/>
     </row>
-    <row r="152" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
@@ -4857,7 +4854,7 @@
       <c r="N152" s="4"/>
       <c r="O152" s="4"/>
     </row>
-    <row r="153" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
@@ -4870,7 +4867,7 @@
       <c r="N153" s="4"/>
       <c r="O153" s="4"/>
     </row>
-    <row r="154" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
@@ -4883,7 +4880,7 @@
       <c r="N154" s="4"/>
       <c r="O154" s="4"/>
     </row>
-    <row r="155" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
@@ -4896,7 +4893,7 @@
       <c r="N155" s="4"/>
       <c r="O155" s="4"/>
     </row>
-    <row r="156" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
@@ -4909,7 +4906,7 @@
       <c r="N156" s="4"/>
       <c r="O156" s="4"/>
     </row>
-    <row r="157" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
@@ -4922,7 +4919,7 @@
       <c r="N157" s="4"/>
       <c r="O157" s="4"/>
     </row>
-    <row r="158" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
@@ -4935,7 +4932,7 @@
       <c r="N158" s="4"/>
       <c r="O158" s="4"/>
     </row>
-    <row r="159" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
@@ -4948,7 +4945,7 @@
       <c r="N159" s="4"/>
       <c r="O159" s="4"/>
     </row>
-    <row r="160" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
@@ -4961,7 +4958,7 @@
       <c r="N160" s="4"/>
       <c r="O160" s="4"/>
     </row>
-    <row r="161" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
@@ -4974,7 +4971,7 @@
       <c r="N161" s="4"/>
       <c r="O161" s="4"/>
     </row>
-    <row r="162" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
@@ -4987,7 +4984,7 @@
       <c r="N162" s="4"/>
       <c r="O162" s="4"/>
     </row>
-    <row r="163" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
@@ -5000,7 +4997,7 @@
       <c r="N163" s="4"/>
       <c r="O163" s="4"/>
     </row>
-    <row r="164" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
@@ -5013,7 +5010,7 @@
       <c r="N164" s="4"/>
       <c r="O164" s="4"/>
     </row>
-    <row r="165" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
@@ -5026,7 +5023,7 @@
       <c r="N165" s="4"/>
       <c r="O165" s="4"/>
     </row>
-    <row r="166" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
@@ -5039,7 +5036,7 @@
       <c r="N166" s="4"/>
       <c r="O166" s="4"/>
     </row>
-    <row r="167" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
@@ -5052,7 +5049,7 @@
       <c r="N167" s="4"/>
       <c r="O167" s="4"/>
     </row>
-    <row r="168" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
@@ -5065,7 +5062,7 @@
       <c r="N168" s="4"/>
       <c r="O168" s="4"/>
     </row>
-    <row r="169" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
@@ -5078,7 +5075,7 @@
       <c r="N169" s="4"/>
       <c r="O169" s="4"/>
     </row>
-    <row r="170" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
@@ -5091,7 +5088,7 @@
       <c r="N170" s="4"/>
       <c r="O170" s="4"/>
     </row>
-    <row r="171" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
@@ -5104,7 +5101,7 @@
       <c r="N171" s="4"/>
       <c r="O171" s="4"/>
     </row>
-    <row r="172" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
@@ -5117,7 +5114,7 @@
       <c r="N172" s="4"/>
       <c r="O172" s="4"/>
     </row>
-    <row r="173" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
@@ -5130,7 +5127,7 @@
       <c r="N173" s="4"/>
       <c r="O173" s="4"/>
     </row>
-    <row r="174" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
@@ -5143,7 +5140,7 @@
       <c r="N174" s="4"/>
       <c r="O174" s="4"/>
     </row>
-    <row r="175" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
@@ -5156,7 +5153,7 @@
       <c r="N175" s="4"/>
       <c r="O175" s="4"/>
     </row>
-    <row r="176" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
@@ -5169,7 +5166,7 @@
       <c r="N176" s="4"/>
       <c r="O176" s="4"/>
     </row>
-    <row r="177" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
@@ -5182,7 +5179,7 @@
       <c r="N177" s="4"/>
       <c r="O177" s="4"/>
     </row>
-    <row r="178" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
@@ -5195,7 +5192,7 @@
       <c r="N178" s="4"/>
       <c r="O178" s="4"/>
     </row>
-    <row r="179" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
@@ -5208,7 +5205,7 @@
       <c r="N179" s="4"/>
       <c r="O179" s="4"/>
     </row>
-    <row r="180" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
@@ -5221,7 +5218,7 @@
       <c r="N180" s="4"/>
       <c r="O180" s="4"/>
     </row>
-    <row r="181" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
@@ -5234,7 +5231,7 @@
       <c r="N181" s="4"/>
       <c r="O181" s="4"/>
     </row>
-    <row r="182" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
@@ -5247,7 +5244,7 @@
       <c r="N182" s="4"/>
       <c r="O182" s="4"/>
     </row>
-    <row r="183" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
@@ -5260,7 +5257,7 @@
       <c r="N183" s="4"/>
       <c r="O183" s="4"/>
     </row>
-    <row r="184" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
@@ -5273,7 +5270,7 @@
       <c r="N184" s="4"/>
       <c r="O184" s="4"/>
     </row>
-    <row r="185" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
@@ -5286,7 +5283,7 @@
       <c r="N185" s="4"/>
       <c r="O185" s="4"/>
     </row>
-    <row r="186" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
@@ -5299,7 +5296,7 @@
       <c r="N186" s="4"/>
       <c r="O186" s="4"/>
     </row>
-    <row r="187" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
@@ -5312,7 +5309,7 @@
       <c r="N187" s="4"/>
       <c r="O187" s="4"/>
     </row>
-    <row r="188" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
       <c r="F188" s="4"/>
@@ -5325,7 +5322,7 @@
       <c r="N188" s="4"/>
       <c r="O188" s="4"/>
     </row>
-    <row r="189" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
@@ -5338,7 +5335,7 @@
       <c r="N189" s="4"/>
       <c r="O189" s="4"/>
     </row>
-    <row r="190" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
@@ -5351,7 +5348,7 @@
       <c r="N190" s="4"/>
       <c r="O190" s="4"/>
     </row>
-    <row r="191" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
@@ -5364,7 +5361,7 @@
       <c r="N191" s="4"/>
       <c r="O191" s="4"/>
     </row>
-    <row r="192" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
@@ -5377,7 +5374,7 @@
       <c r="N192" s="4"/>
       <c r="O192" s="4"/>
     </row>
-    <row r="193" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
@@ -5390,7 +5387,7 @@
       <c r="N193" s="4"/>
       <c r="O193" s="4"/>
     </row>
-    <row r="194" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
@@ -5403,7 +5400,7 @@
       <c r="N194" s="4"/>
       <c r="O194" s="4"/>
     </row>
-    <row r="195" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
@@ -5416,7 +5413,7 @@
       <c r="N195" s="4"/>
       <c r="O195" s="4"/>
     </row>
-    <row r="196" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
@@ -5429,7 +5426,7 @@
       <c r="N196" s="4"/>
       <c r="O196" s="4"/>
     </row>
-    <row r="197" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
@@ -5442,7 +5439,7 @@
       <c r="N197" s="4"/>
       <c r="O197" s="4"/>
     </row>
-    <row r="198" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
@@ -5455,7 +5452,7 @@
       <c r="N198" s="4"/>
       <c r="O198" s="4"/>
     </row>
-    <row r="199" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
@@ -5468,7 +5465,7 @@
       <c r="N199" s="4"/>
       <c r="O199" s="4"/>
     </row>
-    <row r="200" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
@@ -5481,7 +5478,7 @@
       <c r="N200" s="4"/>
       <c r="O200" s="4"/>
     </row>
-    <row r="201" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
@@ -5494,7 +5491,7 @@
       <c r="N201" s="4"/>
       <c r="O201" s="4"/>
     </row>
-    <row r="202" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
       <c r="F202" s="4"/>
@@ -5507,7 +5504,7 @@
       <c r="N202" s="4"/>
       <c r="O202" s="4"/>
     </row>
-    <row r="203" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
       <c r="F203" s="4"/>
@@ -5520,7 +5517,7 @@
       <c r="N203" s="4"/>
       <c r="O203" s="4"/>
     </row>
-    <row r="204" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
       <c r="F204" s="4"/>
@@ -5533,7 +5530,7 @@
       <c r="N204" s="4"/>
       <c r="O204" s="4"/>
     </row>
-    <row r="205" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
       <c r="F205" s="4"/>
@@ -5546,7 +5543,7 @@
       <c r="N205" s="4"/>
       <c r="O205" s="4"/>
     </row>
-    <row r="206" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
       <c r="F206" s="4"/>
@@ -5559,7 +5556,7 @@
       <c r="N206" s="4"/>
       <c r="O206" s="4"/>
     </row>
-    <row r="207" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
       <c r="F207" s="4"/>
@@ -5572,7 +5569,7 @@
       <c r="N207" s="4"/>
       <c r="O207" s="4"/>
     </row>
-    <row r="208" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
@@ -5585,7 +5582,7 @@
       <c r="N208" s="4"/>
       <c r="O208" s="4"/>
     </row>
-    <row r="209" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
@@ -5598,7 +5595,7 @@
       <c r="N209" s="4"/>
       <c r="O209" s="4"/>
     </row>
-    <row r="210" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
@@ -5611,7 +5608,7 @@
       <c r="N210" s="4"/>
       <c r="O210" s="4"/>
     </row>
-    <row r="211" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
@@ -5624,7 +5621,7 @@
       <c r="N211" s="4"/>
       <c r="O211" s="4"/>
     </row>
-    <row r="212" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
@@ -5637,7 +5634,7 @@
       <c r="N212" s="4"/>
       <c r="O212" s="4"/>
     </row>
-    <row r="213" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
@@ -5650,7 +5647,7 @@
       <c r="N213" s="4"/>
       <c r="O213" s="4"/>
     </row>
-    <row r="214" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
@@ -5663,7 +5660,7 @@
       <c r="N214" s="4"/>
       <c r="O214" s="4"/>
     </row>
-    <row r="215" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
@@ -5676,7 +5673,7 @@
       <c r="N215" s="4"/>
       <c r="O215" s="4"/>
     </row>
-    <row r="216" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
@@ -5689,7 +5686,7 @@
       <c r="N216" s="4"/>
       <c r="O216" s="4"/>
     </row>
-    <row r="217" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
@@ -5702,7 +5699,7 @@
       <c r="N217" s="4"/>
       <c r="O217" s="4"/>
     </row>
-    <row r="218" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
@@ -5715,7 +5712,7 @@
       <c r="N218" s="4"/>
       <c r="O218" s="4"/>
     </row>
-    <row r="219" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
@@ -5728,7 +5725,7 @@
       <c r="N219" s="4"/>
       <c r="O219" s="4"/>
     </row>
-    <row r="220" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
@@ -5741,7 +5738,7 @@
       <c r="N220" s="4"/>
       <c r="O220" s="4"/>
     </row>
-    <row r="221" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
@@ -5754,7 +5751,7 @@
       <c r="N221" s="4"/>
       <c r="O221" s="4"/>
     </row>
-    <row r="222" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
@@ -5767,7 +5764,7 @@
       <c r="N222" s="4"/>
       <c r="O222" s="4"/>
     </row>
-    <row r="223" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
@@ -5780,7 +5777,7 @@
       <c r="N223" s="4"/>
       <c r="O223" s="4"/>
     </row>
-    <row r="224" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
@@ -5793,7 +5790,7 @@
       <c r="N224" s="4"/>
       <c r="O224" s="4"/>
     </row>
-    <row r="225" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
@@ -5806,7 +5803,7 @@
       <c r="N225" s="4"/>
       <c r="O225" s="4"/>
     </row>
-    <row r="226" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
@@ -5819,7 +5816,7 @@
       <c r="N226" s="4"/>
       <c r="O226" s="4"/>
     </row>
-    <row r="227" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
@@ -5832,7 +5829,7 @@
       <c r="N227" s="4"/>
       <c r="O227" s="4"/>
     </row>
-    <row r="228" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
@@ -5845,7 +5842,7 @@
       <c r="N228" s="4"/>
       <c r="O228" s="4"/>
     </row>
-    <row r="229" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
@@ -5858,7 +5855,7 @@
       <c r="N229" s="4"/>
       <c r="O229" s="4"/>
     </row>
-    <row r="230" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="4"/>
@@ -5871,7 +5868,7 @@
       <c r="N230" s="4"/>
       <c r="O230" s="4"/>
     </row>
-    <row r="231" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
@@ -5884,7 +5881,7 @@
       <c r="N231" s="4"/>
       <c r="O231" s="4"/>
     </row>
-    <row r="232" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
@@ -5897,7 +5894,7 @@
       <c r="N232" s="4"/>
       <c r="O232" s="4"/>
     </row>
-    <row r="233" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
@@ -5910,7 +5907,7 @@
       <c r="N233" s="4"/>
       <c r="O233" s="4"/>
     </row>
-    <row r="234" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
@@ -5923,7 +5920,7 @@
       <c r="N234" s="4"/>
       <c r="O234" s="4"/>
     </row>
-    <row r="235" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
@@ -5936,7 +5933,7 @@
       <c r="N235" s="4"/>
       <c r="O235" s="4"/>
     </row>
-    <row r="236" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
@@ -5949,7 +5946,7 @@
       <c r="N236" s="4"/>
       <c r="O236" s="4"/>
     </row>
-    <row r="237" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
@@ -5962,7 +5959,7 @@
       <c r="N237" s="4"/>
       <c r="O237" s="4"/>
     </row>
-    <row r="238" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
@@ -5975,7 +5972,7 @@
       <c r="N238" s="4"/>
       <c r="O238" s="4"/>
     </row>
-    <row r="239" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
@@ -5988,7 +5985,7 @@
       <c r="N239" s="4"/>
       <c r="O239" s="4"/>
     </row>
-    <row r="240" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
       <c r="F240" s="4"/>
@@ -6001,7 +5998,7 @@
       <c r="N240" s="4"/>
       <c r="O240" s="4"/>
     </row>
-    <row r="241" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
@@ -6014,7 +6011,7 @@
       <c r="N241" s="4"/>
       <c r="O241" s="4"/>
     </row>
-    <row r="242" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
       <c r="F242" s="4"/>
@@ -6027,7 +6024,7 @@
       <c r="N242" s="4"/>
       <c r="O242" s="4"/>
     </row>
-    <row r="243" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="4"/>
@@ -6040,7 +6037,7 @@
       <c r="N243" s="4"/>
       <c r="O243" s="4"/>
     </row>
-    <row r="244" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
       <c r="F244" s="4"/>
@@ -6053,7 +6050,7 @@
       <c r="N244" s="4"/>
       <c r="O244" s="4"/>
     </row>
-    <row r="245" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
       <c r="F245" s="4"/>
@@ -6066,7 +6063,7 @@
       <c r="N245" s="4"/>
       <c r="O245" s="4"/>
     </row>
-    <row r="246" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
       <c r="F246" s="4"/>
@@ -6079,7 +6076,7 @@
       <c r="N246" s="4"/>
       <c r="O246" s="4"/>
     </row>
-    <row r="247" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
       <c r="F247" s="4"/>
@@ -6092,7 +6089,7 @@
       <c r="N247" s="4"/>
       <c r="O247" s="4"/>
     </row>
-    <row r="248" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
       <c r="F248" s="4"/>
@@ -6105,7 +6102,7 @@
       <c r="N248" s="4"/>
       <c r="O248" s="4"/>
     </row>
-    <row r="249" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
       <c r="F249" s="4"/>
@@ -6118,7 +6115,7 @@
       <c r="N249" s="4"/>
       <c r="O249" s="4"/>
     </row>
-    <row r="250" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
       <c r="F250" s="4"/>
@@ -6131,7 +6128,7 @@
       <c r="N250" s="4"/>
       <c r="O250" s="4"/>
     </row>
-    <row r="251" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
       <c r="F251" s="4"/>
@@ -6144,7 +6141,7 @@
       <c r="N251" s="4"/>
       <c r="O251" s="4"/>
     </row>
-    <row r="252" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
       <c r="F252" s="4"/>
@@ -6157,7 +6154,7 @@
       <c r="N252" s="4"/>
       <c r="O252" s="4"/>
     </row>
-    <row r="253" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
       <c r="F253" s="4"/>
@@ -6170,7 +6167,7 @@
       <c r="N253" s="4"/>
       <c r="O253" s="4"/>
     </row>
-    <row r="254" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
       <c r="F254" s="4"/>
@@ -6183,7 +6180,7 @@
       <c r="N254" s="4"/>
       <c r="O254" s="4"/>
     </row>
-    <row r="255" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
       <c r="F255" s="4"/>
@@ -6196,7 +6193,7 @@
       <c r="N255" s="4"/>
       <c r="O255" s="4"/>
     </row>
-    <row r="256" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
       <c r="F256" s="4"/>
@@ -6209,7 +6206,7 @@
       <c r="N256" s="4"/>
       <c r="O256" s="4"/>
     </row>
-    <row r="257" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
       <c r="F257" s="4"/>
@@ -6222,7 +6219,7 @@
       <c r="N257" s="4"/>
       <c r="O257" s="4"/>
     </row>
-    <row r="258" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
       <c r="F258" s="4"/>
@@ -6235,7 +6232,7 @@
       <c r="N258" s="4"/>
       <c r="O258" s="4"/>
     </row>
-    <row r="259" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
       <c r="F259" s="4"/>
@@ -6248,7 +6245,7 @@
       <c r="N259" s="4"/>
       <c r="O259" s="4"/>
     </row>
-    <row r="260" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
       <c r="F260" s="4"/>
@@ -6261,7 +6258,7 @@
       <c r="N260" s="4"/>
       <c r="O260" s="4"/>
     </row>
-    <row r="261" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
       <c r="F261" s="4"/>
@@ -6274,7 +6271,7 @@
       <c r="N261" s="4"/>
       <c r="O261" s="4"/>
     </row>
-    <row r="262" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
       <c r="F262" s="4"/>
@@ -6287,7 +6284,7 @@
       <c r="N262" s="4"/>
       <c r="O262" s="4"/>
     </row>
-    <row r="263" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
       <c r="F263" s="4"/>
@@ -6300,7 +6297,7 @@
       <c r="N263" s="4"/>
       <c r="O263" s="4"/>
     </row>
-    <row r="264" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
       <c r="F264" s="4"/>
@@ -6313,7 +6310,7 @@
       <c r="N264" s="4"/>
       <c r="O264" s="4"/>
     </row>
-    <row r="265" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
       <c r="F265" s="4"/>
@@ -6326,7 +6323,7 @@
       <c r="N265" s="4"/>
       <c r="O265" s="4"/>
     </row>
-    <row r="266" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
       <c r="F266" s="4"/>
@@ -6339,7 +6336,7 @@
       <c r="N266" s="4"/>
       <c r="O266" s="4"/>
     </row>
-    <row r="267" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
       <c r="F267" s="4"/>
@@ -6352,7 +6349,7 @@
       <c r="N267" s="4"/>
       <c r="O267" s="4"/>
     </row>
-    <row r="268" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
       <c r="F268" s="4"/>
@@ -6365,7 +6362,7 @@
       <c r="N268" s="4"/>
       <c r="O268" s="4"/>
     </row>
-    <row r="269" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
       <c r="F269" s="4"/>
@@ -6378,7 +6375,7 @@
       <c r="N269" s="4"/>
       <c r="O269" s="4"/>
     </row>
-    <row r="270" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
       <c r="F270" s="4"/>
@@ -6391,7 +6388,7 @@
       <c r="N270" s="4"/>
       <c r="O270" s="4"/>
     </row>
-    <row r="271" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
       <c r="F271" s="4"/>
@@ -6404,7 +6401,7 @@
       <c r="N271" s="4"/>
       <c r="O271" s="4"/>
     </row>
-    <row r="272" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
       <c r="F272" s="4"/>
@@ -6417,7 +6414,7 @@
       <c r="N272" s="4"/>
       <c r="O272" s="4"/>
     </row>
-    <row r="273" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
       <c r="F273" s="4"/>
@@ -6430,7 +6427,7 @@
       <c r="N273" s="4"/>
       <c r="O273" s="4"/>
     </row>
-    <row r="274" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
       <c r="F274" s="4"/>
@@ -6443,7 +6440,7 @@
       <c r="N274" s="4"/>
       <c r="O274" s="4"/>
     </row>
-    <row r="275" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
       <c r="F275" s="4"/>
@@ -6456,7 +6453,7 @@
       <c r="N275" s="4"/>
       <c r="O275" s="4"/>
     </row>
-    <row r="276" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
       <c r="F276" s="4"/>
@@ -6469,7 +6466,7 @@
       <c r="N276" s="4"/>
       <c r="O276" s="4"/>
     </row>
-    <row r="277" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
       <c r="F277" s="4"/>
@@ -6482,7 +6479,7 @@
       <c r="N277" s="4"/>
       <c r="O277" s="4"/>
     </row>
-    <row r="278" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
       <c r="F278" s="4"/>
@@ -6495,7 +6492,7 @@
       <c r="N278" s="4"/>
       <c r="O278" s="4"/>
     </row>
-    <row r="279" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
       <c r="F279" s="4"/>
@@ -6508,7 +6505,7 @@
       <c r="N279" s="4"/>
       <c r="O279" s="4"/>
     </row>
-    <row r="280" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
       <c r="F280" s="4"/>
@@ -6521,7 +6518,7 @@
       <c r="N280" s="4"/>
       <c r="O280" s="4"/>
     </row>
-    <row r="281" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
       <c r="F281" s="4"/>
@@ -6534,7 +6531,7 @@
       <c r="N281" s="4"/>
       <c r="O281" s="4"/>
     </row>
-    <row r="282" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
       <c r="F282" s="4"/>
@@ -6547,7 +6544,7 @@
       <c r="N282" s="4"/>
       <c r="O282" s="4"/>
     </row>
-    <row r="283" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
       <c r="F283" s="4"/>
@@ -6560,7 +6557,7 @@
       <c r="N283" s="4"/>
       <c r="O283" s="4"/>
     </row>
-    <row r="284" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
       <c r="F284" s="4"/>
@@ -6573,7 +6570,7 @@
       <c r="N284" s="4"/>
       <c r="O284" s="4"/>
     </row>
-    <row r="285" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
       <c r="F285" s="4"/>
@@ -6586,7 +6583,7 @@
       <c r="N285" s="4"/>
       <c r="O285" s="4"/>
     </row>
-    <row r="286" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
       <c r="F286" s="4"/>
@@ -6599,7 +6596,7 @@
       <c r="N286" s="4"/>
       <c r="O286" s="4"/>
     </row>
-    <row r="287" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
       <c r="F287" s="4"/>
@@ -6612,7 +6609,7 @@
       <c r="N287" s="4"/>
       <c r="O287" s="4"/>
     </row>
-    <row r="288" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
       <c r="F288" s="4"/>
@@ -6625,7 +6622,7 @@
       <c r="N288" s="4"/>
       <c r="O288" s="4"/>
     </row>
-    <row r="289" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
       <c r="F289" s="4"/>
@@ -6638,7 +6635,7 @@
       <c r="N289" s="4"/>
       <c r="O289" s="4"/>
     </row>
-    <row r="290" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D290" s="4"/>
       <c r="E290" s="4"/>
       <c r="F290" s="4"/>
@@ -6651,7 +6648,7 @@
       <c r="N290" s="4"/>
       <c r="O290" s="4"/>
     </row>
-    <row r="291" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
       <c r="F291" s="4"/>
@@ -6664,7 +6661,7 @@
       <c r="N291" s="4"/>
       <c r="O291" s="4"/>
     </row>
-    <row r="292" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
       <c r="F292" s="4"/>
@@ -6677,7 +6674,7 @@
       <c r="N292" s="4"/>
       <c r="O292" s="4"/>
     </row>
-    <row r="293" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
       <c r="F293" s="4"/>
@@ -6690,7 +6687,7 @@
       <c r="N293" s="4"/>
       <c r="O293" s="4"/>
     </row>
-    <row r="294" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
       <c r="F294" s="4"/>
@@ -6703,7 +6700,7 @@
       <c r="N294" s="4"/>
       <c r="O294" s="4"/>
     </row>
-    <row r="295" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D295" s="4"/>
       <c r="E295" s="4"/>
       <c r="F295" s="4"/>
@@ -6716,7 +6713,7 @@
       <c r="N295" s="4"/>
       <c r="O295" s="4"/>
     </row>
-    <row r="296" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
       <c r="F296" s="4"/>
@@ -6729,7 +6726,7 @@
       <c r="N296" s="4"/>
       <c r="O296" s="4"/>
     </row>
-    <row r="297" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
       <c r="F297" s="4"/>
@@ -6742,7 +6739,7 @@
       <c r="N297" s="4"/>
       <c r="O297" s="4"/>
     </row>
-    <row r="298" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D298" s="4"/>
       <c r="E298" s="4"/>
       <c r="F298" s="4"/>
@@ -6755,7 +6752,7 @@
       <c r="N298" s="4"/>
       <c r="O298" s="4"/>
     </row>
-    <row r="299" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D299" s="4"/>
       <c r="E299" s="4"/>
       <c r="F299" s="4"/>
@@ -6768,7 +6765,7 @@
       <c r="N299" s="4"/>
       <c r="O299" s="4"/>
     </row>
-    <row r="300" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
       <c r="F300" s="4"/>
@@ -6781,7 +6778,7 @@
       <c r="N300" s="4"/>
       <c r="O300" s="4"/>
     </row>
-    <row r="301" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
       <c r="F301" s="4"/>
@@ -6794,7 +6791,7 @@
       <c r="N301" s="4"/>
       <c r="O301" s="4"/>
     </row>
-    <row r="302" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D302" s="4"/>
       <c r="E302" s="4"/>
       <c r="F302" s="4"/>
@@ -6807,7 +6804,7 @@
       <c r="N302" s="4"/>
       <c r="O302" s="4"/>
     </row>
-    <row r="303" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D303" s="4"/>
       <c r="E303" s="4"/>
       <c r="F303" s="4"/>
@@ -6820,7 +6817,7 @@
       <c r="N303" s="4"/>
       <c r="O303" s="4"/>
     </row>
-    <row r="304" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D304" s="4"/>
       <c r="E304" s="4"/>
       <c r="F304" s="4"/>
@@ -6833,7 +6830,7 @@
       <c r="N304" s="4"/>
       <c r="O304" s="4"/>
     </row>
-    <row r="305" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D305" s="4"/>
       <c r="E305" s="4"/>
       <c r="F305" s="4"/>
@@ -6846,7 +6843,7 @@
       <c r="N305" s="4"/>
       <c r="O305" s="4"/>
     </row>
-    <row r="306" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D306" s="4"/>
       <c r="E306" s="4"/>
       <c r="F306" s="4"/>
@@ -6859,7 +6856,7 @@
       <c r="N306" s="4"/>
       <c r="O306" s="4"/>
     </row>
-    <row r="307" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D307" s="4"/>
       <c r="E307" s="4"/>
       <c r="F307" s="4"/>
@@ -6872,7 +6869,7 @@
       <c r="N307" s="4"/>
       <c r="O307" s="4"/>
     </row>
-    <row r="308" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
       <c r="F308" s="4"/>
@@ -6885,7 +6882,7 @@
       <c r="N308" s="4"/>
       <c r="O308" s="4"/>
     </row>
-    <row r="309" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D309" s="4"/>
       <c r="E309" s="4"/>
       <c r="F309" s="4"/>
@@ -6898,7 +6895,7 @@
       <c r="N309" s="4"/>
       <c r="O309" s="4"/>
     </row>
-    <row r="310" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D310" s="4"/>
       <c r="E310" s="4"/>
       <c r="F310" s="4"/>
@@ -6911,7 +6908,7 @@
       <c r="N310" s="4"/>
       <c r="O310" s="4"/>
     </row>
-    <row r="311" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D311" s="4"/>
       <c r="E311" s="4"/>
       <c r="F311" s="4"/>
@@ -6924,7 +6921,7 @@
       <c r="N311" s="4"/>
       <c r="O311" s="4"/>
     </row>
-    <row r="312" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D312" s="4"/>
       <c r="E312" s="4"/>
       <c r="F312" s="4"/>
@@ -6937,7 +6934,7 @@
       <c r="N312" s="4"/>
       <c r="O312" s="4"/>
     </row>
-    <row r="313" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
       <c r="F313" s="4"/>
@@ -6950,7 +6947,7 @@
       <c r="N313" s="4"/>
       <c r="O313" s="4"/>
     </row>
-    <row r="314" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D314" s="4"/>
       <c r="E314" s="4"/>
       <c r="F314" s="4"/>
@@ -6963,7 +6960,7 @@
       <c r="N314" s="4"/>
       <c r="O314" s="4"/>
     </row>
-    <row r="315" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D315" s="4"/>
       <c r="E315" s="4"/>
       <c r="F315" s="4"/>
@@ -6976,7 +6973,7 @@
       <c r="N315" s="4"/>
       <c r="O315" s="4"/>
     </row>
-    <row r="316" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D316" s="4"/>
       <c r="E316" s="4"/>
       <c r="F316" s="4"/>
@@ -6989,7 +6986,7 @@
       <c r="N316" s="4"/>
       <c r="O316" s="4"/>
     </row>
-    <row r="317" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
       <c r="F317" s="4"/>
@@ -7002,7 +6999,7 @@
       <c r="N317" s="4"/>
       <c r="O317" s="4"/>
     </row>
-    <row r="318" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
       <c r="F318" s="4"/>
@@ -7015,7 +7012,7 @@
       <c r="N318" s="4"/>
       <c r="O318" s="4"/>
     </row>
-    <row r="319" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
       <c r="F319" s="4"/>
@@ -7028,7 +7025,7 @@
       <c r="N319" s="4"/>
       <c r="O319" s="4"/>
     </row>
-    <row r="320" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
       <c r="F320" s="4"/>
@@ -7041,7 +7038,7 @@
       <c r="N320" s="4"/>
       <c r="O320" s="4"/>
     </row>
-    <row r="321" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
       <c r="F321" s="4"/>
@@ -7054,7 +7051,7 @@
       <c r="N321" s="4"/>
       <c r="O321" s="4"/>
     </row>
-    <row r="322" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D322" s="4"/>
       <c r="E322" s="4"/>
       <c r="F322" s="4"/>
@@ -7067,7 +7064,7 @@
       <c r="N322" s="4"/>
       <c r="O322" s="4"/>
     </row>
-    <row r="323" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
       <c r="F323" s="4"/>
@@ -7080,7 +7077,7 @@
       <c r="N323" s="4"/>
       <c r="O323" s="4"/>
     </row>
-    <row r="324" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D324" s="4"/>
       <c r="E324" s="4"/>
       <c r="F324" s="4"/>
@@ -7093,7 +7090,7 @@
       <c r="N324" s="4"/>
       <c r="O324" s="4"/>
     </row>
-    <row r="325" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
       <c r="F325" s="4"/>
@@ -7106,7 +7103,7 @@
       <c r="N325" s="4"/>
       <c r="O325" s="4"/>
     </row>
-    <row r="326" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
       <c r="F326" s="4"/>
@@ -7119,7 +7116,7 @@
       <c r="N326" s="4"/>
       <c r="O326" s="4"/>
     </row>
-    <row r="327" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
       <c r="F327" s="4"/>
@@ -7132,7 +7129,7 @@
       <c r="N327" s="4"/>
       <c r="O327" s="4"/>
     </row>
-    <row r="328" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D328" s="4"/>
       <c r="E328" s="4"/>
       <c r="F328" s="4"/>
@@ -7145,7 +7142,7 @@
       <c r="N328" s="4"/>
       <c r="O328" s="4"/>
     </row>
-    <row r="329" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D329" s="4"/>
       <c r="E329" s="4"/>
       <c r="F329" s="4"/>
@@ -7158,7 +7155,7 @@
       <c r="N329" s="4"/>
       <c r="O329" s="4"/>
     </row>
-    <row r="330" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
       <c r="F330" s="4"/>
@@ -7171,7 +7168,7 @@
       <c r="N330" s="4"/>
       <c r="O330" s="4"/>
     </row>
-    <row r="331" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
       <c r="F331" s="4"/>
@@ -7184,7 +7181,7 @@
       <c r="N331" s="4"/>
       <c r="O331" s="4"/>
     </row>
-    <row r="332" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
       <c r="F332" s="4"/>
@@ -7197,7 +7194,7 @@
       <c r="N332" s="4"/>
       <c r="O332" s="4"/>
     </row>
-    <row r="333" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
       <c r="F333" s="4"/>
@@ -7210,7 +7207,7 @@
       <c r="N333" s="4"/>
       <c r="O333" s="4"/>
     </row>
-    <row r="334" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
       <c r="F334" s="4"/>
@@ -7223,7 +7220,7 @@
       <c r="N334" s="4"/>
       <c r="O334" s="4"/>
     </row>
-    <row r="335" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
       <c r="F335" s="4"/>
@@ -7236,7 +7233,7 @@
       <c r="N335" s="4"/>
       <c r="O335" s="4"/>
     </row>
-    <row r="336" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
       <c r="F336" s="4"/>
@@ -7249,7 +7246,7 @@
       <c r="N336" s="4"/>
       <c r="O336" s="4"/>
     </row>
-    <row r="337" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
       <c r="F337" s="4"/>
@@ -7262,7 +7259,7 @@
       <c r="N337" s="4"/>
       <c r="O337" s="4"/>
     </row>
-    <row r="338" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D338" s="4"/>
       <c r="E338" s="4"/>
       <c r="F338" s="4"/>
@@ -7275,7 +7272,7 @@
       <c r="N338" s="4"/>
       <c r="O338" s="4"/>
     </row>
-    <row r="339" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
       <c r="F339" s="4"/>
@@ -7288,7 +7285,7 @@
       <c r="N339" s="4"/>
       <c r="O339" s="4"/>
     </row>
-    <row r="340" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
       <c r="F340" s="4"/>
@@ -7301,7 +7298,7 @@
       <c r="N340" s="4"/>
       <c r="O340" s="4"/>
     </row>
-    <row r="341" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
       <c r="F341" s="4"/>
@@ -7314,7 +7311,7 @@
       <c r="N341" s="4"/>
       <c r="O341" s="4"/>
     </row>
-    <row r="342" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
       <c r="F342" s="4"/>
@@ -7327,7 +7324,7 @@
       <c r="N342" s="4"/>
       <c r="O342" s="4"/>
     </row>
-    <row r="343" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D343" s="4"/>
       <c r="E343" s="4"/>
       <c r="F343" s="4"/>
@@ -7340,7 +7337,7 @@
       <c r="N343" s="4"/>
       <c r="O343" s="4"/>
     </row>
-    <row r="344" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D344" s="4"/>
       <c r="E344" s="4"/>
       <c r="F344" s="4"/>
@@ -7353,7 +7350,7 @@
       <c r="N344" s="4"/>
       <c r="O344" s="4"/>
     </row>
-    <row r="345" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D345" s="4"/>
       <c r="E345" s="4"/>
       <c r="F345" s="4"/>
@@ -7366,7 +7363,7 @@
       <c r="N345" s="4"/>
       <c r="O345" s="4"/>
     </row>
-    <row r="346" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D346" s="4"/>
       <c r="E346" s="4"/>
       <c r="F346" s="4"/>
@@ -7379,7 +7376,7 @@
       <c r="N346" s="4"/>
       <c r="O346" s="4"/>
     </row>
-    <row r="347" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
       <c r="F347" s="4"/>
@@ -7392,7 +7389,7 @@
       <c r="N347" s="4"/>
       <c r="O347" s="4"/>
     </row>
-    <row r="348" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D348" s="4"/>
       <c r="E348" s="4"/>
       <c r="F348" s="4"/>
@@ -7405,7 +7402,7 @@
       <c r="N348" s="4"/>
       <c r="O348" s="4"/>
     </row>
-    <row r="349" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
       <c r="F349" s="4"/>
@@ -7418,7 +7415,7 @@
       <c r="N349" s="4"/>
       <c r="O349" s="4"/>
     </row>
-    <row r="350" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D350" s="4"/>
       <c r="E350" s="4"/>
       <c r="F350" s="4"/>
@@ -7431,7 +7428,7 @@
       <c r="N350" s="4"/>
       <c r="O350" s="4"/>
     </row>
-    <row r="351" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
       <c r="F351" s="4"/>
@@ -7444,7 +7441,7 @@
       <c r="N351" s="4"/>
       <c r="O351" s="4"/>
     </row>
-    <row r="352" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
       <c r="F352" s="4"/>
@@ -7457,7 +7454,7 @@
       <c r="N352" s="4"/>
       <c r="O352" s="4"/>
     </row>
-    <row r="353" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D353" s="4"/>
       <c r="E353" s="4"/>
       <c r="F353" s="4"/>
@@ -7470,7 +7467,7 @@
       <c r="N353" s="4"/>
       <c r="O353" s="4"/>
     </row>
-    <row r="354" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D354" s="4"/>
       <c r="E354" s="4"/>
       <c r="F354" s="4"/>
@@ -7483,7 +7480,7 @@
       <c r="N354" s="4"/>
       <c r="O354" s="4"/>
     </row>
-    <row r="355" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D355" s="4"/>
       <c r="E355" s="4"/>
       <c r="F355" s="4"/>
@@ -7496,7 +7493,7 @@
       <c r="N355" s="4"/>
       <c r="O355" s="4"/>
     </row>
-    <row r="356" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D356" s="4"/>
       <c r="E356" s="4"/>
       <c r="F356" s="4"/>
@@ -7509,7 +7506,7 @@
       <c r="N356" s="4"/>
       <c r="O356" s="4"/>
     </row>
-    <row r="357" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D357" s="4"/>
       <c r="E357" s="4"/>
       <c r="F357" s="4"/>
@@ -7522,7 +7519,7 @@
       <c r="N357" s="4"/>
       <c r="O357" s="4"/>
     </row>
-    <row r="358" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D358" s="4"/>
       <c r="E358" s="4"/>
       <c r="F358" s="4"/>
@@ -7535,7 +7532,7 @@
       <c r="N358" s="4"/>
       <c r="O358" s="4"/>
     </row>
-    <row r="359" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D359" s="4"/>
       <c r="E359" s="4"/>
       <c r="F359" s="4"/>
@@ -7548,7 +7545,7 @@
       <c r="N359" s="4"/>
       <c r="O359" s="4"/>
     </row>
-    <row r="360" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D360" s="4"/>
       <c r="E360" s="4"/>
       <c r="F360" s="4"/>
@@ -7561,7 +7558,7 @@
       <c r="N360" s="4"/>
       <c r="O360" s="4"/>
     </row>
-    <row r="361" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
       <c r="F361" s="4"/>
@@ -7574,7 +7571,7 @@
       <c r="N361" s="4"/>
       <c r="O361" s="4"/>
     </row>
-    <row r="362" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D362" s="4"/>
       <c r="E362" s="4"/>
       <c r="F362" s="4"/>
@@ -7587,7 +7584,7 @@
       <c r="N362" s="4"/>
       <c r="O362" s="4"/>
     </row>
-    <row r="363" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
       <c r="F363" s="4"/>
@@ -7600,7 +7597,7 @@
       <c r="N363" s="4"/>
       <c r="O363" s="4"/>
     </row>
-    <row r="364" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
       <c r="F364" s="4"/>
@@ -7613,7 +7610,7 @@
       <c r="N364" s="4"/>
       <c r="O364" s="4"/>
     </row>
-    <row r="365" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D365" s="4"/>
       <c r="E365" s="4"/>
       <c r="F365" s="4"/>
@@ -7626,7 +7623,7 @@
       <c r="N365" s="4"/>
       <c r="O365" s="4"/>
     </row>
-    <row r="366" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
       <c r="F366" s="4"/>
@@ -7639,7 +7636,7 @@
       <c r="N366" s="4"/>
       <c r="O366" s="4"/>
     </row>
-    <row r="367" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
       <c r="F367" s="4"/>
@@ -7652,7 +7649,7 @@
       <c r="N367" s="4"/>
       <c r="O367" s="4"/>
     </row>
-    <row r="368" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
       <c r="F368" s="4"/>
@@ -7665,7 +7662,7 @@
       <c r="N368" s="4"/>
       <c r="O368" s="4"/>
     </row>
-    <row r="369" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
       <c r="F369" s="4"/>
@@ -7678,7 +7675,7 @@
       <c r="N369" s="4"/>
       <c r="O369" s="4"/>
     </row>
-    <row r="370" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
       <c r="F370" s="4"/>
@@ -7691,7 +7688,7 @@
       <c r="N370" s="4"/>
       <c r="O370" s="4"/>
     </row>
-    <row r="371" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
       <c r="F371" s="4"/>
@@ -7704,7 +7701,7 @@
       <c r="N371" s="4"/>
       <c r="O371" s="4"/>
     </row>
-    <row r="372" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
       <c r="F372" s="4"/>
@@ -7717,7 +7714,7 @@
       <c r="N372" s="4"/>
       <c r="O372" s="4"/>
     </row>
-    <row r="373" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
       <c r="F373" s="4"/>
@@ -7730,7 +7727,7 @@
       <c r="N373" s="4"/>
       <c r="O373" s="4"/>
     </row>
-    <row r="374" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
       <c r="F374" s="4"/>
@@ -7743,7 +7740,7 @@
       <c r="N374" s="4"/>
       <c r="O374" s="4"/>
     </row>
-    <row r="375" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
       <c r="F375" s="4"/>
@@ -7756,7 +7753,7 @@
       <c r="N375" s="4"/>
       <c r="O375" s="4"/>
     </row>
-    <row r="376" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
       <c r="F376" s="4"/>
@@ -7769,7 +7766,7 @@
       <c r="N376" s="4"/>
       <c r="O376" s="4"/>
     </row>
-    <row r="377" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
       <c r="F377" s="4"/>
@@ -7782,7 +7779,7 @@
       <c r="N377" s="4"/>
       <c r="O377" s="4"/>
     </row>
-    <row r="378" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
       <c r="F378" s="4"/>
@@ -7795,7 +7792,7 @@
       <c r="N378" s="4"/>
       <c r="O378" s="4"/>
     </row>
-    <row r="379" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
       <c r="F379" s="4"/>
@@ -7808,7 +7805,7 @@
       <c r="N379" s="4"/>
       <c r="O379" s="4"/>
     </row>
-    <row r="380" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
       <c r="F380" s="4"/>
@@ -7821,7 +7818,7 @@
       <c r="N380" s="4"/>
       <c r="O380" s="4"/>
     </row>
-    <row r="381" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
       <c r="F381" s="4"/>
@@ -7834,7 +7831,7 @@
       <c r="N381" s="4"/>
       <c r="O381" s="4"/>
     </row>
-    <row r="382" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
       <c r="F382" s="4"/>
@@ -7847,7 +7844,7 @@
       <c r="N382" s="4"/>
       <c r="O382" s="4"/>
     </row>
-    <row r="383" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
       <c r="F383" s="4"/>
@@ -7860,7 +7857,7 @@
       <c r="N383" s="4"/>
       <c r="O383" s="4"/>
     </row>
-    <row r="384" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
       <c r="F384" s="4"/>
@@ -7873,7 +7870,7 @@
       <c r="N384" s="4"/>
       <c r="O384" s="4"/>
     </row>
-    <row r="385" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
       <c r="F385" s="4"/>
@@ -7886,7 +7883,7 @@
       <c r="N385" s="4"/>
       <c r="O385" s="4"/>
     </row>
-    <row r="386" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
       <c r="F386" s="4"/>
@@ -7899,7 +7896,7 @@
       <c r="N386" s="4"/>
       <c r="O386" s="4"/>
     </row>
-    <row r="387" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
       <c r="F387" s="4"/>
@@ -7912,7 +7909,7 @@
       <c r="N387" s="4"/>
       <c r="O387" s="4"/>
     </row>
-    <row r="388" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
       <c r="F388" s="4"/>
@@ -7925,7 +7922,7 @@
       <c r="N388" s="4"/>
       <c r="O388" s="4"/>
     </row>
-    <row r="389" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
       <c r="F389" s="4"/>
@@ -7938,7 +7935,7 @@
       <c r="N389" s="4"/>
       <c r="O389" s="4"/>
     </row>
-    <row r="390" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
       <c r="F390" s="4"/>
@@ -7951,7 +7948,7 @@
       <c r="N390" s="4"/>
       <c r="O390" s="4"/>
     </row>
-    <row r="391" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
       <c r="F391" s="4"/>
@@ -7964,7 +7961,7 @@
       <c r="N391" s="4"/>
       <c r="O391" s="4"/>
     </row>
-    <row r="392" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
       <c r="F392" s="4"/>
@@ -7977,7 +7974,7 @@
       <c r="N392" s="4"/>
       <c r="O392" s="4"/>
     </row>
-    <row r="393" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
       <c r="F393" s="4"/>
@@ -7990,7 +7987,7 @@
       <c r="N393" s="4"/>
       <c r="O393" s="4"/>
     </row>
-    <row r="394" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
       <c r="F394" s="4"/>
@@ -8003,7 +8000,7 @@
       <c r="N394" s="4"/>
       <c r="O394" s="4"/>
     </row>
-    <row r="395" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
       <c r="F395" s="4"/>
@@ -8016,7 +8013,7 @@
       <c r="N395" s="4"/>
       <c r="O395" s="4"/>
     </row>
-    <row r="396" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
       <c r="F396" s="4"/>
@@ -8029,7 +8026,7 @@
       <c r="N396" s="4"/>
       <c r="O396" s="4"/>
     </row>
-    <row r="397" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
       <c r="F397" s="4"/>
@@ -8042,7 +8039,7 @@
       <c r="N397" s="4"/>
       <c r="O397" s="4"/>
     </row>
-    <row r="398" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
       <c r="F398" s="4"/>
@@ -8055,7 +8052,7 @@
       <c r="N398" s="4"/>
       <c r="O398" s="4"/>
     </row>
-    <row r="399" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D399" s="4"/>
       <c r="E399" s="4"/>
       <c r="F399" s="4"/>
@@ -8068,7 +8065,7 @@
       <c r="N399" s="4"/>
       <c r="O399" s="4"/>
     </row>
-    <row r="400" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D400" s="4"/>
       <c r="E400" s="4"/>
       <c r="F400" s="4"/>
@@ -8081,7 +8078,7 @@
       <c r="N400" s="4"/>
       <c r="O400" s="4"/>
     </row>
-    <row r="401" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
       <c r="F401" s="4"/>
@@ -8094,7 +8091,7 @@
       <c r="N401" s="4"/>
       <c r="O401" s="4"/>
     </row>
-    <row r="402" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
       <c r="F402" s="4"/>
@@ -8107,7 +8104,7 @@
       <c r="N402" s="4"/>
       <c r="O402" s="4"/>
     </row>
-    <row r="403" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D403" s="4"/>
       <c r="E403" s="4"/>
       <c r="F403" s="4"/>
@@ -8120,7 +8117,7 @@
       <c r="N403" s="4"/>
       <c r="O403" s="4"/>
     </row>
-    <row r="404" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D404" s="4"/>
       <c r="E404" s="4"/>
       <c r="F404" s="4"/>
@@ -8133,7 +8130,7 @@
       <c r="N404" s="4"/>
       <c r="O404" s="4"/>
     </row>
-    <row r="405" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D405" s="4"/>
       <c r="E405" s="4"/>
       <c r="F405" s="4"/>
@@ -8146,7 +8143,7 @@
       <c r="N405" s="4"/>
       <c r="O405" s="4"/>
     </row>
-    <row r="406" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
       <c r="F406" s="4"/>
@@ -8159,7 +8156,7 @@
       <c r="N406" s="4"/>
       <c r="O406" s="4"/>
     </row>
-    <row r="407" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D407" s="4"/>
       <c r="E407" s="4"/>
       <c r="F407" s="4"/>
@@ -8172,7 +8169,7 @@
       <c r="N407" s="4"/>
       <c r="O407" s="4"/>
     </row>
-    <row r="408" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
       <c r="F408" s="4"/>
@@ -8185,7 +8182,7 @@
       <c r="N408" s="4"/>
       <c r="O408" s="4"/>
     </row>
-    <row r="409" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
       <c r="F409" s="4"/>
@@ -8198,7 +8195,7 @@
       <c r="N409" s="4"/>
       <c r="O409" s="4"/>
     </row>
-    <row r="410" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D410" s="4"/>
       <c r="E410" s="4"/>
       <c r="F410" s="4"/>
@@ -8211,7 +8208,7 @@
       <c r="N410" s="4"/>
       <c r="O410" s="4"/>
     </row>
-    <row r="411" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
       <c r="F411" s="4"/>
@@ -8224,7 +8221,7 @@
       <c r="N411" s="4"/>
       <c r="O411" s="4"/>
     </row>
-    <row r="412" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D412" s="4"/>
       <c r="E412" s="4"/>
       <c r="F412" s="4"/>
@@ -8237,7 +8234,7 @@
       <c r="N412" s="4"/>
       <c r="O412" s="4"/>
     </row>
-    <row r="413" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
       <c r="F413" s="4"/>
@@ -8250,7 +8247,7 @@
       <c r="N413" s="4"/>
       <c r="O413" s="4"/>
     </row>
-    <row r="414" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D414" s="4"/>
       <c r="E414" s="4"/>
       <c r="F414" s="4"/>
@@ -8263,7 +8260,7 @@
       <c r="N414" s="4"/>
       <c r="O414" s="4"/>
     </row>
-    <row r="415" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
       <c r="F415" s="4"/>
@@ -8276,7 +8273,7 @@
       <c r="N415" s="4"/>
       <c r="O415" s="4"/>
     </row>
-    <row r="416" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
       <c r="F416" s="4"/>
@@ -8289,7 +8286,7 @@
       <c r="N416" s="4"/>
       <c r="O416" s="4"/>
     </row>
-    <row r="417" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
       <c r="F417" s="4"/>
@@ -8302,7 +8299,7 @@
       <c r="N417" s="4"/>
       <c r="O417" s="4"/>
     </row>
-    <row r="418" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
       <c r="F418" s="4"/>
@@ -8315,7 +8312,7 @@
       <c r="N418" s="4"/>
       <c r="O418" s="4"/>
     </row>
-    <row r="419" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
       <c r="F419" s="4"/>
@@ -8328,7 +8325,7 @@
       <c r="N419" s="4"/>
       <c r="O419" s="4"/>
     </row>
-    <row r="420" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
       <c r="F420" s="4"/>
@@ -8341,7 +8338,7 @@
       <c r="N420" s="4"/>
       <c r="O420" s="4"/>
     </row>
-    <row r="421" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
       <c r="F421" s="4"/>
@@ -8354,7 +8351,7 @@
       <c r="N421" s="4"/>
       <c r="O421" s="4"/>
     </row>
-    <row r="422" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
       <c r="F422" s="4"/>
@@ -8367,7 +8364,7 @@
       <c r="N422" s="4"/>
       <c r="O422" s="4"/>
     </row>
-    <row r="423" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
       <c r="F423" s="4"/>
@@ -8380,7 +8377,7 @@
       <c r="N423" s="4"/>
       <c r="O423" s="4"/>
     </row>
-    <row r="424" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
       <c r="F424" s="4"/>
@@ -8393,7 +8390,7 @@
       <c r="N424" s="4"/>
       <c r="O424" s="4"/>
     </row>
-    <row r="425" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
       <c r="F425" s="4"/>
@@ -8406,7 +8403,7 @@
       <c r="N425" s="4"/>
       <c r="O425" s="4"/>
     </row>
-    <row r="426" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
       <c r="F426" s="4"/>
@@ -8419,7 +8416,7 @@
       <c r="N426" s="4"/>
       <c r="O426" s="4"/>
     </row>
-    <row r="427" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
       <c r="F427" s="4"/>
@@ -8432,7 +8429,7 @@
       <c r="N427" s="4"/>
       <c r="O427" s="4"/>
     </row>
-    <row r="428" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
       <c r="F428" s="4"/>
@@ -8445,7 +8442,7 @@
       <c r="N428" s="4"/>
       <c r="O428" s="4"/>
     </row>
-    <row r="429" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
       <c r="F429" s="4"/>
@@ -8458,7 +8455,7 @@
       <c r="N429" s="4"/>
       <c r="O429" s="4"/>
     </row>
-    <row r="430" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D430" s="4"/>
       <c r="E430" s="4"/>
       <c r="F430" s="4"/>
@@ -8471,7 +8468,7 @@
       <c r="N430" s="4"/>
       <c r="O430" s="4"/>
     </row>
-    <row r="431" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
       <c r="F431" s="4"/>
@@ -8484,7 +8481,7 @@
       <c r="N431" s="4"/>
       <c r="O431" s="4"/>
     </row>
-    <row r="432" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
       <c r="F432" s="4"/>
@@ -8497,7 +8494,7 @@
       <c r="N432" s="4"/>
       <c r="O432" s="4"/>
     </row>
-    <row r="433" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
       <c r="F433" s="4"/>
@@ -8510,7 +8507,7 @@
       <c r="N433" s="4"/>
       <c r="O433" s="4"/>
     </row>
-    <row r="434" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
       <c r="F434" s="4"/>
@@ -8523,7 +8520,7 @@
       <c r="N434" s="4"/>
       <c r="O434" s="4"/>
     </row>
-    <row r="435" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
       <c r="F435" s="4"/>
@@ -8536,7 +8533,7 @@
       <c r="N435" s="4"/>
       <c r="O435" s="4"/>
     </row>
-    <row r="436" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
       <c r="F436" s="4"/>
@@ -8549,7 +8546,7 @@
       <c r="N436" s="4"/>
       <c r="O436" s="4"/>
     </row>
-    <row r="437" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
       <c r="F437" s="4"/>
@@ -8562,7 +8559,7 @@
       <c r="N437" s="4"/>
       <c r="O437" s="4"/>
     </row>
-    <row r="438" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
       <c r="F438" s="4"/>
@@ -8575,7 +8572,7 @@
       <c r="N438" s="4"/>
       <c r="O438" s="4"/>
     </row>
-    <row r="439" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
       <c r="F439" s="4"/>
@@ -8588,7 +8585,7 @@
       <c r="N439" s="4"/>
       <c r="O439" s="4"/>
     </row>
-    <row r="440" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
       <c r="F440" s="4"/>
@@ -8601,7 +8598,7 @@
       <c r="N440" s="4"/>
       <c r="O440" s="4"/>
     </row>
-    <row r="441" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
       <c r="F441" s="4"/>
@@ -8614,7 +8611,7 @@
       <c r="N441" s="4"/>
       <c r="O441" s="4"/>
     </row>
-    <row r="442" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
       <c r="F442" s="4"/>
@@ -8627,7 +8624,7 @@
       <c r="N442" s="4"/>
       <c r="O442" s="4"/>
     </row>
-    <row r="443" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
       <c r="F443" s="4"/>
@@ -8640,7 +8637,7 @@
       <c r="N443" s="4"/>
       <c r="O443" s="4"/>
     </row>
-    <row r="444" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
       <c r="F444" s="4"/>
@@ -8653,7 +8650,7 @@
       <c r="N444" s="4"/>
       <c r="O444" s="4"/>
     </row>
-    <row r="445" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
       <c r="F445" s="4"/>
@@ -8666,7 +8663,7 @@
       <c r="N445" s="4"/>
       <c r="O445" s="4"/>
     </row>
-    <row r="446" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
       <c r="F446" s="4"/>
@@ -8679,7 +8676,7 @@
       <c r="N446" s="4"/>
       <c r="O446" s="4"/>
     </row>
-    <row r="447" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
       <c r="F447" s="4"/>
@@ -8692,7 +8689,7 @@
       <c r="N447" s="4"/>
       <c r="O447" s="4"/>
     </row>
-    <row r="448" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
       <c r="F448" s="4"/>
@@ -8705,7 +8702,7 @@
       <c r="N448" s="4"/>
       <c r="O448" s="4"/>
     </row>
-    <row r="449" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
       <c r="F449" s="4"/>
@@ -8718,7 +8715,7 @@
       <c r="N449" s="4"/>
       <c r="O449" s="4"/>
     </row>
-    <row r="450" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
       <c r="F450" s="4"/>
@@ -8731,7 +8728,7 @@
       <c r="N450" s="4"/>
       <c r="O450" s="4"/>
     </row>
-    <row r="451" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D451" s="4"/>
       <c r="E451" s="4"/>
       <c r="F451" s="4"/>
@@ -8744,7 +8741,7 @@
       <c r="N451" s="4"/>
       <c r="O451" s="4"/>
     </row>
-    <row r="452" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
       <c r="F452" s="4"/>
@@ -8757,7 +8754,7 @@
       <c r="N452" s="4"/>
       <c r="O452" s="4"/>
     </row>
-    <row r="453" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
       <c r="F453" s="4"/>
@@ -8770,7 +8767,7 @@
       <c r="N453" s="4"/>
       <c r="O453" s="4"/>
     </row>
-    <row r="454" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
       <c r="F454" s="4"/>
@@ -8783,7 +8780,7 @@
       <c r="N454" s="4"/>
       <c r="O454" s="4"/>
     </row>
-    <row r="455" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
       <c r="F455" s="4"/>
@@ -8796,7 +8793,7 @@
       <c r="N455" s="4"/>
       <c r="O455" s="4"/>
     </row>
-    <row r="456" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
       <c r="F456" s="4"/>
@@ -8809,7 +8806,7 @@
       <c r="N456" s="4"/>
       <c r="O456" s="4"/>
     </row>
-    <row r="457" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D457" s="4"/>
       <c r="E457" s="4"/>
       <c r="F457" s="4"/>
@@ -8822,7 +8819,7 @@
       <c r="N457" s="4"/>
       <c r="O457" s="4"/>
     </row>
-    <row r="458" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D458" s="4"/>
       <c r="E458" s="4"/>
       <c r="F458" s="4"/>
@@ -8835,7 +8832,7 @@
       <c r="N458" s="4"/>
       <c r="O458" s="4"/>
     </row>
-    <row r="459" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D459" s="4"/>
       <c r="E459" s="4"/>
       <c r="F459" s="4"/>
@@ -8848,7 +8845,7 @@
       <c r="N459" s="4"/>
       <c r="O459" s="4"/>
     </row>
-    <row r="460" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
       <c r="F460" s="4"/>
@@ -8861,7 +8858,7 @@
       <c r="N460" s="4"/>
       <c r="O460" s="4"/>
     </row>
-    <row r="461" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
       <c r="F461" s="4"/>
@@ -8874,7 +8871,7 @@
       <c r="N461" s="4"/>
       <c r="O461" s="4"/>
     </row>
-    <row r="462" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
       <c r="F462" s="4"/>
@@ -8887,7 +8884,7 @@
       <c r="N462" s="4"/>
       <c r="O462" s="4"/>
     </row>
-    <row r="463" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
       <c r="F463" s="4"/>
@@ -8900,7 +8897,7 @@
       <c r="N463" s="4"/>
       <c r="O463" s="4"/>
     </row>
-    <row r="464" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D464" s="4"/>
       <c r="E464" s="4"/>
       <c r="F464" s="4"/>
@@ -8913,7 +8910,7 @@
       <c r="N464" s="4"/>
       <c r="O464" s="4"/>
     </row>
-    <row r="465" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D465" s="4"/>
       <c r="E465" s="4"/>
       <c r="F465" s="4"/>
@@ -8926,7 +8923,7 @@
       <c r="N465" s="4"/>
       <c r="O465" s="4"/>
     </row>
-    <row r="466" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D466" s="4"/>
       <c r="E466" s="4"/>
       <c r="F466" s="4"/>
@@ -8939,7 +8936,7 @@
       <c r="N466" s="4"/>
       <c r="O466" s="4"/>
     </row>
-    <row r="467" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D467" s="4"/>
       <c r="E467" s="4"/>
       <c r="F467" s="4"/>
@@ -8952,7 +8949,7 @@
       <c r="N467" s="4"/>
       <c r="O467" s="4"/>
     </row>
-    <row r="468" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D468" s="4"/>
       <c r="E468" s="4"/>
       <c r="F468" s="4"/>
@@ -8965,7 +8962,7 @@
       <c r="N468" s="4"/>
       <c r="O468" s="4"/>
     </row>
-    <row r="469" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D469" s="4"/>
       <c r="E469" s="4"/>
       <c r="F469" s="4"/>
@@ -8978,7 +8975,7 @@
       <c r="N469" s="4"/>
       <c r="O469" s="4"/>
     </row>
-    <row r="470" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D470" s="4"/>
       <c r="E470" s="4"/>
       <c r="F470" s="4"/>
@@ -8991,7 +8988,7 @@
       <c r="N470" s="4"/>
       <c r="O470" s="4"/>
     </row>
-    <row r="471" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D471" s="4"/>
       <c r="E471" s="4"/>
       <c r="F471" s="4"/>
@@ -9004,7 +9001,7 @@
       <c r="N471" s="4"/>
       <c r="O471" s="4"/>
     </row>
-    <row r="472" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D472" s="4"/>
       <c r="E472" s="4"/>
       <c r="F472" s="4"/>
@@ -9017,7 +9014,7 @@
       <c r="N472" s="4"/>
       <c r="O472" s="4"/>
     </row>
-    <row r="473" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D473" s="4"/>
       <c r="E473" s="4"/>
       <c r="F473" s="4"/>
@@ -9030,7 +9027,7 @@
       <c r="N473" s="4"/>
       <c r="O473" s="4"/>
     </row>
-    <row r="474" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
       <c r="F474" s="4"/>
@@ -9043,7 +9040,7 @@
       <c r="N474" s="4"/>
       <c r="O474" s="4"/>
     </row>
-    <row r="475" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D475" s="4"/>
       <c r="E475" s="4"/>
       <c r="F475" s="4"/>
@@ -9056,7 +9053,7 @@
       <c r="N475" s="4"/>
       <c r="O475" s="4"/>
     </row>
-    <row r="476" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D476" s="4"/>
       <c r="E476" s="4"/>
       <c r="F476" s="4"/>
@@ -9069,7 +9066,7 @@
       <c r="N476" s="4"/>
       <c r="O476" s="4"/>
     </row>
-    <row r="477" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D477" s="4"/>
       <c r="E477" s="4"/>
       <c r="F477" s="4"/>
@@ -9082,7 +9079,7 @@
       <c r="N477" s="4"/>
       <c r="O477" s="4"/>
     </row>
-    <row r="478" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D478" s="4"/>
       <c r="E478" s="4"/>
       <c r="F478" s="4"/>
@@ -9095,7 +9092,7 @@
       <c r="N478" s="4"/>
       <c r="O478" s="4"/>
     </row>
-    <row r="479" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D479" s="4"/>
       <c r="E479" s="4"/>
       <c r="F479" s="4"/>
@@ -9108,7 +9105,7 @@
       <c r="N479" s="4"/>
       <c r="O479" s="4"/>
     </row>
-    <row r="480" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
       <c r="F480" s="4"/>
@@ -9121,7 +9118,7 @@
       <c r="N480" s="4"/>
       <c r="O480" s="4"/>
     </row>
-    <row r="481" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D481" s="4"/>
       <c r="E481" s="4"/>
       <c r="F481" s="4"/>
@@ -9134,7 +9131,7 @@
       <c r="N481" s="4"/>
       <c r="O481" s="4"/>
     </row>
-    <row r="482" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D482" s="4"/>
       <c r="E482" s="4"/>
       <c r="F482" s="4"/>
@@ -9147,7 +9144,7 @@
       <c r="N482" s="4"/>
       <c r="O482" s="4"/>
     </row>
-    <row r="483" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D483" s="4"/>
       <c r="E483" s="4"/>
       <c r="F483" s="4"/>
@@ -9160,7 +9157,7 @@
       <c r="N483" s="4"/>
       <c r="O483" s="4"/>
     </row>
-    <row r="484" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D484" s="4"/>
       <c r="E484" s="4"/>
       <c r="F484" s="4"/>
@@ -9173,7 +9170,7 @@
       <c r="N484" s="4"/>
       <c r="O484" s="4"/>
     </row>
-    <row r="485" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D485" s="4"/>
       <c r="E485" s="4"/>
       <c r="F485" s="4"/>
@@ -9186,7 +9183,7 @@
       <c r="N485" s="4"/>
       <c r="O485" s="4"/>
     </row>
-    <row r="486" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D486" s="4"/>
       <c r="E486" s="4"/>
       <c r="F486" s="4"/>
@@ -9199,7 +9196,7 @@
       <c r="N486" s="4"/>
       <c r="O486" s="4"/>
     </row>
-    <row r="487" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D487" s="4"/>
       <c r="E487" s="4"/>
       <c r="F487" s="4"/>
@@ -9212,7 +9209,7 @@
       <c r="N487" s="4"/>
       <c r="O487" s="4"/>
     </row>
-    <row r="488" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D488" s="4"/>
       <c r="E488" s="4"/>
       <c r="F488" s="4"/>
@@ -9225,7 +9222,7 @@
       <c r="N488" s="4"/>
       <c r="O488" s="4"/>
     </row>
-    <row r="489" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D489" s="4"/>
       <c r="E489" s="4"/>
       <c r="F489" s="4"/>
@@ -9238,7 +9235,7 @@
       <c r="N489" s="4"/>
       <c r="O489" s="4"/>
     </row>
-    <row r="490" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D490" s="4"/>
       <c r="E490" s="4"/>
       <c r="F490" s="4"/>
@@ -9251,7 +9248,7 @@
       <c r="N490" s="4"/>
       <c r="O490" s="4"/>
     </row>
-    <row r="491" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D491" s="4"/>
       <c r="E491" s="4"/>
       <c r="F491" s="4"/>
@@ -9264,7 +9261,7 @@
       <c r="N491" s="4"/>
       <c r="O491" s="4"/>
     </row>
-    <row r="492" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D492" s="4"/>
       <c r="E492" s="4"/>
       <c r="F492" s="4"/>
@@ -9277,7 +9274,7 @@
       <c r="N492" s="4"/>
       <c r="O492" s="4"/>
     </row>
-    <row r="493" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D493" s="4"/>
       <c r="E493" s="4"/>
       <c r="F493" s="4"/>
@@ -9290,7 +9287,7 @@
       <c r="N493" s="4"/>
       <c r="O493" s="4"/>
     </row>
-    <row r="494" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D494" s="4"/>
       <c r="E494" s="4"/>
       <c r="F494" s="4"/>
@@ -9303,7 +9300,7 @@
       <c r="N494" s="4"/>
       <c r="O494" s="4"/>
     </row>
-    <row r="495" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D495" s="4"/>
       <c r="E495" s="4"/>
       <c r="F495" s="4"/>
@@ -9316,7 +9313,7 @@
       <c r="N495" s="4"/>
       <c r="O495" s="4"/>
     </row>
-    <row r="496" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D496" s="4"/>
       <c r="E496" s="4"/>
       <c r="F496" s="4"/>
@@ -9329,7 +9326,7 @@
       <c r="N496" s="4"/>
       <c r="O496" s="4"/>
     </row>
-    <row r="497" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D497" s="4"/>
       <c r="E497" s="4"/>
       <c r="F497" s="4"/>
@@ -9342,7 +9339,7 @@
       <c r="N497" s="4"/>
       <c r="O497" s="4"/>
     </row>
-    <row r="498" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D498" s="4"/>
       <c r="E498" s="4"/>
       <c r="F498" s="4"/>
@@ -9355,7 +9352,7 @@
       <c r="N498" s="4"/>
       <c r="O498" s="4"/>
     </row>
-    <row r="499" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D499" s="4"/>
       <c r="E499" s="4"/>
       <c r="F499" s="4"/>
@@ -9368,7 +9365,7 @@
       <c r="N499" s="4"/>
       <c r="O499" s="4"/>
     </row>
-    <row r="500" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D500" s="4"/>
       <c r="E500" s="4"/>
       <c r="F500" s="4"/>
@@ -9381,7 +9378,7 @@
       <c r="N500" s="4"/>
       <c r="O500" s="4"/>
     </row>
-    <row r="501" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D501" s="4"/>
       <c r="E501" s="4"/>
       <c r="F501" s="4"/>
@@ -9394,7 +9391,7 @@
       <c r="N501" s="4"/>
       <c r="O501" s="4"/>
     </row>
-    <row r="502" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D502" s="4"/>
       <c r="E502" s="4"/>
       <c r="F502" s="4"/>
@@ -9407,7 +9404,7 @@
       <c r="N502" s="4"/>
       <c r="O502" s="4"/>
     </row>
-    <row r="503" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D503" s="4"/>
       <c r="E503" s="4"/>
       <c r="F503" s="4"/>
@@ -9420,7 +9417,7 @@
       <c r="N503" s="4"/>
       <c r="O503" s="4"/>
     </row>
-    <row r="504" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D504" s="4"/>
       <c r="E504" s="4"/>
       <c r="F504" s="4"/>
@@ -9433,7 +9430,7 @@
       <c r="N504" s="4"/>
       <c r="O504" s="4"/>
     </row>
-    <row r="505" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D505" s="4"/>
       <c r="E505" s="4"/>
       <c r="F505" s="4"/>
@@ -9446,7 +9443,7 @@
       <c r="N505" s="4"/>
       <c r="O505" s="4"/>
     </row>
-    <row r="506" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D506" s="4"/>
       <c r="E506" s="4"/>
       <c r="F506" s="4"/>
@@ -9459,7 +9456,7 @@
       <c r="N506" s="4"/>
       <c r="O506" s="4"/>
     </row>
-    <row r="507" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="507" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D507" s="4"/>
       <c r="E507" s="4"/>
       <c r="F507" s="4"/>
@@ -9472,7 +9469,7 @@
       <c r="N507" s="4"/>
       <c r="O507" s="4"/>
     </row>
-    <row r="508" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="508" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D508" s="4"/>
       <c r="E508" s="4"/>
       <c r="F508" s="4"/>
@@ -9485,7 +9482,7 @@
       <c r="N508" s="4"/>
       <c r="O508" s="4"/>
     </row>
-    <row r="509" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="509" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D509" s="4"/>
       <c r="E509" s="4"/>
       <c r="F509" s="4"/>
@@ -9498,7 +9495,7 @@
       <c r="N509" s="4"/>
       <c r="O509" s="4"/>
     </row>
-    <row r="510" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="510" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D510" s="4"/>
       <c r="E510" s="4"/>
       <c r="F510" s="4"/>
@@ -9511,7 +9508,7 @@
       <c r="N510" s="4"/>
       <c r="O510" s="4"/>
     </row>
-    <row r="511" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="511" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D511" s="4"/>
       <c r="E511" s="4"/>
       <c r="F511" s="4"/>
@@ -9524,7 +9521,7 @@
       <c r="N511" s="4"/>
       <c r="O511" s="4"/>
     </row>
-    <row r="512" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="512" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D512" s="4"/>
       <c r="E512" s="4"/>
       <c r="F512" s="4"/>
@@ -9537,7 +9534,7 @@
       <c r="N512" s="4"/>
       <c r="O512" s="4"/>
     </row>
-    <row r="513" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="513" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D513" s="4"/>
       <c r="E513" s="4"/>
       <c r="F513" s="4"/>
@@ -9550,7 +9547,7 @@
       <c r="N513" s="4"/>
       <c r="O513" s="4"/>
     </row>
-    <row r="514" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="514" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D514" s="4"/>
       <c r="E514" s="4"/>
       <c r="F514" s="4"/>
@@ -9563,7 +9560,7 @@
       <c r="N514" s="4"/>
       <c r="O514" s="4"/>
     </row>
-    <row r="515" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="515" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D515" s="4"/>
       <c r="E515" s="4"/>
       <c r="F515" s="4"/>
@@ -9576,7 +9573,7 @@
       <c r="N515" s="4"/>
       <c r="O515" s="4"/>
     </row>
-    <row r="516" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="516" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D516" s="4"/>
       <c r="E516" s="4"/>
       <c r="F516" s="4"/>
@@ -9589,7 +9586,7 @@
       <c r="N516" s="4"/>
       <c r="O516" s="4"/>
     </row>
-    <row r="517" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="517" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D517" s="4"/>
       <c r="E517" s="4"/>
       <c r="F517" s="4"/>
@@ -9602,7 +9599,7 @@
       <c r="N517" s="4"/>
       <c r="O517" s="4"/>
     </row>
-    <row r="518" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="518" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D518" s="4"/>
       <c r="E518" s="4"/>
       <c r="F518" s="4"/>
@@ -9615,7 +9612,7 @@
       <c r="N518" s="4"/>
       <c r="O518" s="4"/>
     </row>
-    <row r="519" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="519" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D519" s="4"/>
       <c r="E519" s="4"/>
       <c r="F519" s="4"/>
@@ -9628,7 +9625,7 @@
       <c r="N519" s="4"/>
       <c r="O519" s="4"/>
     </row>
-    <row r="520" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="520" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D520" s="4"/>
       <c r="E520" s="4"/>
       <c r="F520" s="4"/>
@@ -9641,7 +9638,7 @@
       <c r="N520" s="4"/>
       <c r="O520" s="4"/>
     </row>
-    <row r="521" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="521" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D521" s="4"/>
       <c r="E521" s="4"/>
       <c r="F521" s="4"/>
@@ -9654,7 +9651,7 @@
       <c r="N521" s="4"/>
       <c r="O521" s="4"/>
     </row>
-    <row r="522" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="522" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D522" s="4"/>
       <c r="E522" s="4"/>
       <c r="F522" s="4"/>
@@ -9667,7 +9664,7 @@
       <c r="N522" s="4"/>
       <c r="O522" s="4"/>
     </row>
-    <row r="523" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="523" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D523" s="4"/>
       <c r="E523" s="4"/>
       <c r="F523" s="4"/>
@@ -9680,7 +9677,7 @@
       <c r="N523" s="4"/>
       <c r="O523" s="4"/>
     </row>
-    <row r="524" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="524" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D524" s="4"/>
       <c r="E524" s="4"/>
       <c r="F524" s="4"/>
@@ -9693,7 +9690,7 @@
       <c r="N524" s="4"/>
       <c r="O524" s="4"/>
     </row>
-    <row r="525" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="525" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D525" s="4"/>
       <c r="E525" s="4"/>
       <c r="F525" s="4"/>
@@ -9706,7 +9703,7 @@
       <c r="N525" s="4"/>
       <c r="O525" s="4"/>
     </row>
-    <row r="526" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="526" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D526" s="4"/>
       <c r="E526" s="4"/>
       <c r="F526" s="4"/>
@@ -9719,7 +9716,7 @@
       <c r="N526" s="4"/>
       <c r="O526" s="4"/>
     </row>
-    <row r="527" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="527" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D527" s="4"/>
       <c r="E527" s="4"/>
       <c r="F527" s="4"/>
@@ -9732,7 +9729,7 @@
       <c r="N527" s="4"/>
       <c r="O527" s="4"/>
     </row>
-    <row r="528" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="528" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D528" s="4"/>
       <c r="E528" s="4"/>
       <c r="F528" s="4"/>
@@ -9745,7 +9742,7 @@
       <c r="N528" s="4"/>
       <c r="O528" s="4"/>
     </row>
-    <row r="529" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="529" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D529" s="4"/>
       <c r="E529" s="4"/>
       <c r="F529" s="4"/>
@@ -9758,7 +9755,7 @@
       <c r="N529" s="4"/>
       <c r="O529" s="4"/>
     </row>
-    <row r="530" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="530" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D530" s="4"/>
       <c r="E530" s="4"/>
       <c r="F530" s="4"/>
@@ -9771,7 +9768,7 @@
       <c r="N530" s="4"/>
       <c r="O530" s="4"/>
     </row>
-    <row r="531" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="531" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D531" s="4"/>
       <c r="E531" s="4"/>
       <c r="F531" s="4"/>
@@ -9784,7 +9781,7 @@
       <c r="N531" s="4"/>
       <c r="O531" s="4"/>
     </row>
-    <row r="532" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="532" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D532" s="4"/>
       <c r="E532" s="4"/>
       <c r="F532" s="4"/>
@@ -9797,7 +9794,7 @@
       <c r="N532" s="4"/>
       <c r="O532" s="4"/>
     </row>
-    <row r="533" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="533" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D533" s="4"/>
       <c r="E533" s="4"/>
       <c r="F533" s="4"/>
@@ -9810,7 +9807,7 @@
       <c r="N533" s="4"/>
       <c r="O533" s="4"/>
     </row>
-    <row r="534" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="534" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D534" s="4"/>
       <c r="E534" s="4"/>
       <c r="F534" s="4"/>
@@ -9823,7 +9820,7 @@
       <c r="N534" s="4"/>
       <c r="O534" s="4"/>
     </row>
-    <row r="535" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="535" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D535" s="4"/>
       <c r="E535" s="4"/>
       <c r="F535" s="4"/>
@@ -9836,7 +9833,7 @@
       <c r="N535" s="4"/>
       <c r="O535" s="4"/>
     </row>
-    <row r="536" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="536" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D536" s="4"/>
       <c r="E536" s="4"/>
       <c r="F536" s="4"/>
@@ -9849,7 +9846,7 @@
       <c r="N536" s="4"/>
       <c r="O536" s="4"/>
     </row>
-    <row r="537" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="537" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D537" s="4"/>
       <c r="E537" s="4"/>
       <c r="F537" s="4"/>
@@ -9862,7 +9859,7 @@
       <c r="N537" s="4"/>
       <c r="O537" s="4"/>
     </row>
-    <row r="538" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="538" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D538" s="4"/>
       <c r="E538" s="4"/>
       <c r="F538" s="4"/>
@@ -9875,7 +9872,7 @@
       <c r="N538" s="4"/>
       <c r="O538" s="4"/>
     </row>
-    <row r="539" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="539" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D539" s="4"/>
       <c r="E539" s="4"/>
       <c r="F539" s="4"/>
@@ -9888,7 +9885,7 @@
       <c r="N539" s="4"/>
       <c r="O539" s="4"/>
     </row>
-    <row r="540" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="540" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D540" s="4"/>
       <c r="E540" s="4"/>
       <c r="F540" s="4"/>
@@ -9901,7 +9898,7 @@
       <c r="N540" s="4"/>
       <c r="O540" s="4"/>
     </row>
-    <row r="541" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="541" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D541" s="4"/>
       <c r="E541" s="4"/>
       <c r="F541" s="4"/>
@@ -9914,7 +9911,7 @@
       <c r="N541" s="4"/>
       <c r="O541" s="4"/>
     </row>
-    <row r="542" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="542" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D542" s="4"/>
       <c r="E542" s="4"/>
       <c r="F542" s="4"/>
@@ -9927,7 +9924,7 @@
       <c r="N542" s="4"/>
       <c r="O542" s="4"/>
     </row>
-    <row r="543" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="543" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D543" s="4"/>
       <c r="E543" s="4"/>
       <c r="F543" s="4"/>
@@ -9940,7 +9937,7 @@
       <c r="N543" s="4"/>
       <c r="O543" s="4"/>
     </row>
-    <row r="544" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="544" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D544" s="4"/>
       <c r="E544" s="4"/>
       <c r="F544" s="4"/>
@@ -9953,7 +9950,7 @@
       <c r="N544" s="4"/>
       <c r="O544" s="4"/>
     </row>
-    <row r="545" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="545" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D545" s="4"/>
       <c r="E545" s="4"/>
       <c r="F545" s="4"/>
@@ -9966,7 +9963,7 @@
       <c r="N545" s="4"/>
       <c r="O545" s="4"/>
     </row>
-    <row r="546" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="546" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D546" s="4"/>
       <c r="E546" s="4"/>
       <c r="F546" s="4"/>
@@ -9979,7 +9976,7 @@
       <c r="N546" s="4"/>
       <c r="O546" s="4"/>
     </row>
-    <row r="547" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="547" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D547" s="4"/>
       <c r="E547" s="4"/>
       <c r="F547" s="4"/>
@@ -9992,7 +9989,7 @@
       <c r="N547" s="4"/>
       <c r="O547" s="4"/>
     </row>
-    <row r="548" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="548" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D548" s="4"/>
       <c r="E548" s="4"/>
       <c r="F548" s="4"/>
@@ -10005,7 +10002,7 @@
       <c r="N548" s="4"/>
       <c r="O548" s="4"/>
     </row>
-    <row r="549" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="549" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D549" s="4"/>
       <c r="E549" s="4"/>
       <c r="F549" s="4"/>
@@ -10018,7 +10015,7 @@
       <c r="N549" s="4"/>
       <c r="O549" s="4"/>
     </row>
-    <row r="550" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="550" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D550" s="4"/>
       <c r="E550" s="4"/>
       <c r="F550" s="4"/>
@@ -10031,7 +10028,7 @@
       <c r="N550" s="4"/>
       <c r="O550" s="4"/>
     </row>
-    <row r="551" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="551" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D551" s="4"/>
       <c r="E551" s="4"/>
       <c r="F551" s="4"/>
@@ -10044,7 +10041,7 @@
       <c r="N551" s="4"/>
       <c r="O551" s="4"/>
     </row>
-    <row r="552" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="552" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D552" s="4"/>
       <c r="E552" s="4"/>
       <c r="F552" s="4"/>
@@ -10057,7 +10054,7 @@
       <c r="N552" s="4"/>
       <c r="O552" s="4"/>
     </row>
-    <row r="553" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="553" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D553" s="4"/>
       <c r="E553" s="4"/>
       <c r="F553" s="4"/>
@@ -10070,7 +10067,7 @@
       <c r="N553" s="4"/>
       <c r="O553" s="4"/>
     </row>
-    <row r="554" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="554" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D554" s="4"/>
       <c r="E554" s="4"/>
       <c r="F554" s="4"/>
@@ -10083,7 +10080,7 @@
       <c r="N554" s="4"/>
       <c r="O554" s="4"/>
     </row>
-    <row r="555" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="555" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D555" s="4"/>
       <c r="E555" s="4"/>
       <c r="F555" s="4"/>
@@ -10096,7 +10093,7 @@
       <c r="N555" s="4"/>
       <c r="O555" s="4"/>
     </row>
-    <row r="556" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="556" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D556" s="4"/>
       <c r="E556" s="4"/>
       <c r="F556" s="4"/>
@@ -10109,7 +10106,7 @@
       <c r="N556" s="4"/>
       <c r="O556" s="4"/>
     </row>
-    <row r="557" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="557" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D557" s="4"/>
       <c r="E557" s="4"/>
       <c r="F557" s="4"/>
@@ -10122,7 +10119,7 @@
       <c r="N557" s="4"/>
       <c r="O557" s="4"/>
     </row>
-    <row r="558" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="558" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D558" s="4"/>
       <c r="E558" s="4"/>
       <c r="F558" s="4"/>
@@ -10135,7 +10132,7 @@
       <c r="N558" s="4"/>
       <c r="O558" s="4"/>
     </row>
-    <row r="559" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="559" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D559" s="4"/>
       <c r="E559" s="4"/>
       <c r="F559" s="4"/>
@@ -10148,7 +10145,7 @@
       <c r="N559" s="4"/>
       <c r="O559" s="4"/>
     </row>
-    <row r="560" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="560" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D560" s="4"/>
       <c r="E560" s="4"/>
       <c r="F560" s="4"/>
@@ -10161,7 +10158,7 @@
       <c r="N560" s="4"/>
       <c r="O560" s="4"/>
     </row>
-    <row r="561" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="561" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D561" s="4"/>
       <c r="E561" s="4"/>
       <c r="F561" s="4"/>
@@ -10174,7 +10171,7 @@
       <c r="N561" s="4"/>
       <c r="O561" s="4"/>
     </row>
-    <row r="562" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="562" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D562" s="4"/>
       <c r="E562" s="4"/>
       <c r="F562" s="4"/>
@@ -10187,7 +10184,7 @@
       <c r="N562" s="4"/>
       <c r="O562" s="4"/>
     </row>
-    <row r="563" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="563" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D563" s="4"/>
       <c r="E563" s="4"/>
       <c r="F563" s="4"/>
@@ -10200,7 +10197,7 @@
       <c r="N563" s="4"/>
       <c r="O563" s="4"/>
     </row>
-    <row r="564" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="564" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D564" s="4"/>
       <c r="E564" s="4"/>
       <c r="F564" s="4"/>
@@ -10213,7 +10210,7 @@
       <c r="N564" s="4"/>
       <c r="O564" s="4"/>
     </row>
-    <row r="565" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="565" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D565" s="4"/>
       <c r="E565" s="4"/>
       <c r="F565" s="4"/>
@@ -10226,7 +10223,7 @@
       <c r="N565" s="4"/>
       <c r="O565" s="4"/>
     </row>
-    <row r="566" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="566" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D566" s="4"/>
       <c r="E566" s="4"/>
       <c r="F566" s="4"/>
@@ -10239,7 +10236,7 @@
       <c r="N566" s="4"/>
       <c r="O566" s="4"/>
     </row>
-    <row r="567" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="567" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D567" s="4"/>
       <c r="E567" s="4"/>
       <c r="F567" s="4"/>
@@ -10252,7 +10249,7 @@
       <c r="N567" s="4"/>
       <c r="O567" s="4"/>
     </row>
-    <row r="568" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="568" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D568" s="4"/>
       <c r="E568" s="4"/>
       <c r="F568" s="4"/>
@@ -10265,7 +10262,7 @@
       <c r="N568" s="4"/>
       <c r="O568" s="4"/>
     </row>
-    <row r="569" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="569" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D569" s="4"/>
       <c r="E569" s="4"/>
       <c r="F569" s="4"/>
@@ -10278,7 +10275,7 @@
       <c r="N569" s="4"/>
       <c r="O569" s="4"/>
     </row>
-    <row r="570" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="570" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D570" s="4"/>
       <c r="E570" s="4"/>
       <c r="F570" s="4"/>
@@ -10291,7 +10288,7 @@
       <c r="N570" s="4"/>
       <c r="O570" s="4"/>
     </row>
-    <row r="571" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="571" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D571" s="4"/>
       <c r="E571" s="4"/>
       <c r="F571" s="4"/>
@@ -10304,7 +10301,7 @@
       <c r="N571" s="4"/>
       <c r="O571" s="4"/>
     </row>
-    <row r="572" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="572" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D572" s="4"/>
       <c r="E572" s="4"/>
       <c r="F572" s="4"/>
@@ -10317,7 +10314,7 @@
       <c r="N572" s="4"/>
       <c r="O572" s="4"/>
     </row>
-    <row r="573" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="573" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D573" s="4"/>
       <c r="E573" s="4"/>
       <c r="F573" s="4"/>
@@ -10330,7 +10327,7 @@
       <c r="N573" s="4"/>
       <c r="O573" s="4"/>
     </row>
-    <row r="574" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="574" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D574" s="4"/>
       <c r="E574" s="4"/>
       <c r="F574" s="4"/>
@@ -10343,7 +10340,7 @@
       <c r="N574" s="4"/>
       <c r="O574" s="4"/>
     </row>
-    <row r="575" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="575" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D575" s="4"/>
       <c r="E575" s="4"/>
       <c r="F575" s="4"/>
@@ -10356,7 +10353,7 @@
       <c r="N575" s="4"/>
       <c r="O575" s="4"/>
     </row>
-    <row r="576" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="576" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D576" s="4"/>
       <c r="E576" s="4"/>
       <c r="F576" s="4"/>
@@ -10369,7 +10366,7 @@
       <c r="N576" s="4"/>
       <c r="O576" s="4"/>
     </row>
-    <row r="577" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="577" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D577" s="4"/>
       <c r="E577" s="4"/>
       <c r="F577" s="4"/>
@@ -10382,7 +10379,7 @@
       <c r="N577" s="4"/>
       <c r="O577" s="4"/>
     </row>
-    <row r="578" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="578" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D578" s="4"/>
       <c r="E578" s="4"/>
       <c r="F578" s="4"/>
@@ -10395,7 +10392,7 @@
       <c r="N578" s="4"/>
       <c r="O578" s="4"/>
     </row>
-    <row r="579" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="579" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D579" s="4"/>
       <c r="E579" s="4"/>
       <c r="F579" s="4"/>
@@ -10408,7 +10405,7 @@
       <c r="N579" s="4"/>
       <c r="O579" s="4"/>
     </row>
-    <row r="580" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="580" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D580" s="4"/>
       <c r="E580" s="4"/>
       <c r="F580" s="4"/>
@@ -10421,7 +10418,7 @@
       <c r="N580" s="4"/>
       <c r="O580" s="4"/>
     </row>
-    <row r="581" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="581" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D581" s="4"/>
       <c r="E581" s="4"/>
       <c r="F581" s="4"/>
@@ -10434,7 +10431,7 @@
       <c r="N581" s="4"/>
       <c r="O581" s="4"/>
     </row>
-    <row r="582" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="582" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D582" s="4"/>
       <c r="E582" s="4"/>
       <c r="F582" s="4"/>
@@ -10447,7 +10444,7 @@
       <c r="N582" s="4"/>
       <c r="O582" s="4"/>
     </row>
-    <row r="583" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="583" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D583" s="4"/>
       <c r="E583" s="4"/>
       <c r="F583" s="4"/>
@@ -10460,7 +10457,7 @@
       <c r="N583" s="4"/>
       <c r="O583" s="4"/>
     </row>
-    <row r="584" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="584" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D584" s="4"/>
       <c r="E584" s="4"/>
       <c r="F584" s="4"/>
@@ -10473,7 +10470,7 @@
       <c r="N584" s="4"/>
       <c r="O584" s="4"/>
     </row>
-    <row r="585" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="585" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D585" s="4"/>
       <c r="E585" s="4"/>
       <c r="F585" s="4"/>
@@ -10486,7 +10483,7 @@
       <c r="N585" s="4"/>
       <c r="O585" s="4"/>
     </row>
-    <row r="586" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="586" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D586" s="4"/>
       <c r="E586" s="4"/>
       <c r="F586" s="4"/>
@@ -10499,7 +10496,7 @@
       <c r="N586" s="4"/>
       <c r="O586" s="4"/>
     </row>
-    <row r="587" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="587" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D587" s="4"/>
       <c r="E587" s="4"/>
       <c r="F587" s="4"/>
@@ -10512,7 +10509,7 @@
       <c r="N587" s="4"/>
       <c r="O587" s="4"/>
     </row>
-    <row r="588" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="588" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D588" s="4"/>
       <c r="E588" s="4"/>
       <c r="F588" s="4"/>
@@ -10525,7 +10522,7 @@
       <c r="N588" s="4"/>
       <c r="O588" s="4"/>
     </row>
-    <row r="589" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D589" s="4"/>
       <c r="E589" s="4"/>
       <c r="F589" s="4"/>
@@ -10538,7 +10535,7 @@
       <c r="N589" s="4"/>
       <c r="O589" s="4"/>
     </row>
-    <row r="590" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D590" s="4"/>
       <c r="E590" s="4"/>
       <c r="F590" s="4"/>
@@ -10551,7 +10548,7 @@
       <c r="N590" s="4"/>
       <c r="O590" s="4"/>
     </row>
-    <row r="591" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D591" s="4"/>
       <c r="E591" s="4"/>
       <c r="F591" s="4"/>
@@ -10564,7 +10561,7 @@
       <c r="N591" s="4"/>
       <c r="O591" s="4"/>
     </row>
-    <row r="592" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D592" s="4"/>
       <c r="E592" s="4"/>
       <c r="F592" s="4"/>
@@ -10577,7 +10574,7 @@
       <c r="N592" s="4"/>
       <c r="O592" s="4"/>
     </row>
-    <row r="593" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D593" s="4"/>
       <c r="E593" s="4"/>
       <c r="F593" s="4"/>
@@ -10590,7 +10587,7 @@
       <c r="N593" s="4"/>
       <c r="O593" s="4"/>
     </row>
-    <row r="594" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D594" s="4"/>
       <c r="E594" s="4"/>
       <c r="F594" s="4"/>
@@ -10603,7 +10600,7 @@
       <c r="N594" s="4"/>
       <c r="O594" s="4"/>
     </row>
-    <row r="595" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D595" s="4"/>
       <c r="E595" s="4"/>
       <c r="F595" s="4"/>
@@ -10616,7 +10613,7 @@
       <c r="N595" s="4"/>
       <c r="O595" s="4"/>
     </row>
-    <row r="596" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D596" s="4"/>
       <c r="E596" s="4"/>
       <c r="F596" s="4"/>
@@ -10629,7 +10626,7 @@
       <c r="N596" s="4"/>
       <c r="O596" s="4"/>
     </row>
-    <row r="597" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D597" s="4"/>
       <c r="E597" s="4"/>
       <c r="F597" s="4"/>
@@ -10642,7 +10639,7 @@
       <c r="N597" s="4"/>
       <c r="O597" s="4"/>
     </row>
-    <row r="598" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D598" s="4"/>
       <c r="E598" s="4"/>
       <c r="F598" s="4"/>
@@ -10655,7 +10652,7 @@
       <c r="N598" s="4"/>
       <c r="O598" s="4"/>
     </row>
-    <row r="599" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="599" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D599" s="4"/>
       <c r="E599" s="4"/>
       <c r="F599" s="4"/>
@@ -10668,7 +10665,7 @@
       <c r="N599" s="4"/>
       <c r="O599" s="4"/>
     </row>
-    <row r="600" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="600" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D600" s="4"/>
       <c r="E600" s="4"/>
       <c r="F600" s="4"/>
@@ -10681,7 +10678,7 @@
       <c r="N600" s="4"/>
       <c r="O600" s="4"/>
     </row>
-    <row r="601" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="601" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D601" s="4"/>
       <c r="E601" s="4"/>
       <c r="F601" s="4"/>
@@ -10694,7 +10691,7 @@
       <c r="N601" s="4"/>
       <c r="O601" s="4"/>
     </row>
-    <row r="602" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="602" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D602" s="4"/>
       <c r="E602" s="4"/>
       <c r="F602" s="4"/>
@@ -10707,7 +10704,7 @@
       <c r="N602" s="4"/>
       <c r="O602" s="4"/>
     </row>
-    <row r="603" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="603" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D603" s="4"/>
       <c r="E603" s="4"/>
       <c r="F603" s="4"/>
@@ -10720,7 +10717,7 @@
       <c r="N603" s="4"/>
       <c r="O603" s="4"/>
     </row>
-    <row r="604" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="604" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D604" s="4"/>
       <c r="E604" s="4"/>
       <c r="F604" s="4"/>
@@ -10733,7 +10730,7 @@
       <c r="N604" s="4"/>
       <c r="O604" s="4"/>
     </row>
-    <row r="605" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="605" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D605" s="4"/>
       <c r="E605" s="4"/>
       <c r="F605" s="4"/>
@@ -10746,7 +10743,7 @@
       <c r="N605" s="4"/>
       <c r="O605" s="4"/>
     </row>
-    <row r="606" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="606" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D606" s="4"/>
       <c r="E606" s="4"/>
       <c r="F606" s="4"/>
@@ -10759,7 +10756,7 @@
       <c r="N606" s="4"/>
       <c r="O606" s="4"/>
     </row>
-    <row r="607" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="607" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D607" s="4"/>
       <c r="E607" s="4"/>
       <c r="F607" s="4"/>
@@ -10772,7 +10769,7 @@
       <c r="N607" s="4"/>
       <c r="O607" s="4"/>
     </row>
-    <row r="608" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="608" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D608" s="4"/>
       <c r="E608" s="4"/>
       <c r="F608" s="4"/>
@@ -10785,7 +10782,7 @@
       <c r="N608" s="4"/>
       <c r="O608" s="4"/>
     </row>
-    <row r="609" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="609" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D609" s="4"/>
       <c r="E609" s="4"/>
       <c r="F609" s="4"/>
@@ -10798,7 +10795,7 @@
       <c r="N609" s="4"/>
       <c r="O609" s="4"/>
     </row>
-    <row r="610" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="610" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D610" s="4"/>
       <c r="E610" s="4"/>
       <c r="F610" s="4"/>
@@ -10811,7 +10808,7 @@
       <c r="N610" s="4"/>
       <c r="O610" s="4"/>
     </row>
-    <row r="611" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="611" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D611" s="4"/>
       <c r="E611" s="4"/>
       <c r="F611" s="4"/>
@@ -10824,7 +10821,7 @@
       <c r="N611" s="4"/>
       <c r="O611" s="4"/>
     </row>
-    <row r="612" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="612" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D612" s="4"/>
       <c r="E612" s="4"/>
       <c r="F612" s="4"/>
@@ -10837,7 +10834,7 @@
       <c r="N612" s="4"/>
       <c r="O612" s="4"/>
     </row>
-    <row r="613" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="613" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D613" s="4"/>
       <c r="E613" s="4"/>
       <c r="F613" s="4"/>
@@ -10850,7 +10847,7 @@
       <c r="N613" s="4"/>
       <c r="O613" s="4"/>
     </row>
-    <row r="614" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="614" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D614" s="4"/>
       <c r="E614" s="4"/>
       <c r="F614" s="4"/>
@@ -10863,7 +10860,7 @@
       <c r="N614" s="4"/>
       <c r="O614" s="4"/>
     </row>
-    <row r="615" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="615" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D615" s="4"/>
       <c r="E615" s="4"/>
       <c r="F615" s="4"/>
@@ -10876,7 +10873,7 @@
       <c r="N615" s="4"/>
       <c r="O615" s="4"/>
     </row>
-    <row r="616" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="616" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D616" s="4"/>
       <c r="E616" s="4"/>
       <c r="F616" s="4"/>
@@ -10889,7 +10886,7 @@
       <c r="N616" s="4"/>
       <c r="O616" s="4"/>
     </row>
-    <row r="617" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="617" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D617" s="4"/>
       <c r="E617" s="4"/>
       <c r="F617" s="4"/>
@@ -10902,7 +10899,7 @@
       <c r="N617" s="4"/>
       <c r="O617" s="4"/>
     </row>
-    <row r="618" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="618" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D618" s="4"/>
       <c r="E618" s="4"/>
       <c r="F618" s="4"/>
@@ -10915,7 +10912,7 @@
       <c r="N618" s="4"/>
       <c r="O618" s="4"/>
     </row>
-    <row r="619" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="619" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D619" s="4"/>
       <c r="E619" s="4"/>
       <c r="F619" s="4"/>
@@ -10928,7 +10925,7 @@
       <c r="N619" s="4"/>
       <c r="O619" s="4"/>
     </row>
-    <row r="620" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="620" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D620" s="4"/>
       <c r="E620" s="4"/>
       <c r="F620" s="4"/>
@@ -10941,7 +10938,7 @@
       <c r="N620" s="4"/>
       <c r="O620" s="4"/>
     </row>
-    <row r="621" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="621" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D621" s="4"/>
       <c r="E621" s="4"/>
       <c r="F621" s="4"/>
@@ -10954,7 +10951,7 @@
       <c r="N621" s="4"/>
       <c r="O621" s="4"/>
     </row>
-    <row r="622" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="622" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D622" s="4"/>
       <c r="E622" s="4"/>
       <c r="F622" s="4"/>
@@ -10967,7 +10964,7 @@
       <c r="N622" s="4"/>
       <c r="O622" s="4"/>
     </row>
-    <row r="623" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="623" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D623" s="4"/>
       <c r="E623" s="4"/>
       <c r="F623" s="4"/>
@@ -10980,7 +10977,7 @@
       <c r="N623" s="4"/>
       <c r="O623" s="4"/>
     </row>
-    <row r="624" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="624" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D624" s="4"/>
       <c r="E624" s="4"/>
       <c r="F624" s="4"/>
@@ -10993,7 +10990,7 @@
       <c r="N624" s="4"/>
       <c r="O624" s="4"/>
     </row>
-    <row r="625" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="625" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D625" s="4"/>
       <c r="E625" s="4"/>
       <c r="F625" s="4"/>
@@ -11006,7 +11003,7 @@
       <c r="N625" s="4"/>
       <c r="O625" s="4"/>
     </row>
-    <row r="626" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="626" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D626" s="4"/>
       <c r="E626" s="4"/>
       <c r="F626" s="4"/>
@@ -11019,7 +11016,7 @@
       <c r="N626" s="4"/>
       <c r="O626" s="4"/>
     </row>
-    <row r="627" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="627" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D627" s="4"/>
       <c r="E627" s="4"/>
       <c r="F627" s="4"/>
@@ -11032,7 +11029,7 @@
       <c r="N627" s="4"/>
       <c r="O627" s="4"/>
     </row>
-    <row r="628" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="628" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D628" s="4"/>
       <c r="E628" s="4"/>
       <c r="F628" s="4"/>
@@ -11045,7 +11042,7 @@
       <c r="N628" s="4"/>
       <c r="O628" s="4"/>
     </row>
-    <row r="629" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="629" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D629" s="4"/>
       <c r="E629" s="4"/>
       <c r="F629" s="4"/>
@@ -11058,7 +11055,7 @@
       <c r="N629" s="4"/>
       <c r="O629" s="4"/>
     </row>
-    <row r="630" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="630" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D630" s="4"/>
       <c r="E630" s="4"/>
       <c r="F630" s="4"/>
@@ -11071,7 +11068,7 @@
       <c r="N630" s="4"/>
       <c r="O630" s="4"/>
     </row>
-    <row r="631" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="631" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D631" s="4"/>
       <c r="E631" s="4"/>
       <c r="F631" s="4"/>
@@ -11084,7 +11081,7 @@
       <c r="N631" s="4"/>
       <c r="O631" s="4"/>
     </row>
-    <row r="632" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="632" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D632" s="4"/>
       <c r="E632" s="4"/>
       <c r="F632" s="4"/>
@@ -11097,7 +11094,7 @@
       <c r="N632" s="4"/>
       <c r="O632" s="4"/>
     </row>
-    <row r="633" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="633" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D633" s="4"/>
       <c r="E633" s="4"/>
       <c r="F633" s="4"/>
@@ -11110,7 +11107,7 @@
       <c r="N633" s="4"/>
       <c r="O633" s="4"/>
     </row>
-    <row r="634" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="634" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D634" s="4"/>
       <c r="E634" s="4"/>
       <c r="F634" s="4"/>
@@ -11123,7 +11120,7 @@
       <c r="N634" s="4"/>
       <c r="O634" s="4"/>
     </row>
-    <row r="635" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="635" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D635" s="4"/>
       <c r="E635" s="4"/>
       <c r="F635" s="4"/>
@@ -11136,7 +11133,7 @@
       <c r="N635" s="4"/>
       <c r="O635" s="4"/>
     </row>
-    <row r="636" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="636" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D636" s="4"/>
       <c r="E636" s="4"/>
       <c r="F636" s="4"/>
@@ -11149,7 +11146,7 @@
       <c r="N636" s="4"/>
       <c r="O636" s="4"/>
     </row>
-    <row r="637" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="637" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D637" s="4"/>
       <c r="E637" s="4"/>
       <c r="F637" s="4"/>
@@ -11162,7 +11159,7 @@
       <c r="N637" s="4"/>
       <c r="O637" s="4"/>
     </row>
-    <row r="638" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="638" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D638" s="4"/>
       <c r="E638" s="4"/>
       <c r="F638" s="4"/>
@@ -11175,7 +11172,7 @@
       <c r="N638" s="4"/>
       <c r="O638" s="4"/>
     </row>
-    <row r="639" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="639" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D639" s="4"/>
       <c r="E639" s="4"/>
       <c r="F639" s="4"/>
@@ -11188,7 +11185,7 @@
       <c r="N639" s="4"/>
       <c r="O639" s="4"/>
     </row>
-    <row r="640" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="640" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D640" s="4"/>
       <c r="E640" s="4"/>
       <c r="F640" s="4"/>
@@ -11201,7 +11198,7 @@
       <c r="N640" s="4"/>
       <c r="O640" s="4"/>
     </row>
-    <row r="641" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="641" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D641" s="4"/>
       <c r="E641" s="4"/>
       <c r="F641" s="4"/>
@@ -11214,7 +11211,7 @@
       <c r="N641" s="4"/>
       <c r="O641" s="4"/>
     </row>
-    <row r="642" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="642" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D642" s="4"/>
       <c r="E642" s="4"/>
       <c r="F642" s="4"/>
@@ -11227,7 +11224,7 @@
       <c r="N642" s="4"/>
       <c r="O642" s="4"/>
     </row>
-    <row r="643" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="643" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D643" s="4"/>
       <c r="E643" s="4"/>
       <c r="F643" s="4"/>
@@ -11240,7 +11237,7 @@
       <c r="N643" s="4"/>
       <c r="O643" s="4"/>
     </row>
-    <row r="644" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="644" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D644" s="4"/>
       <c r="E644" s="4"/>
       <c r="F644" s="4"/>
@@ -11253,7 +11250,7 @@
       <c r="N644" s="4"/>
       <c r="O644" s="4"/>
     </row>
-    <row r="645" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="645" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D645" s="4"/>
       <c r="E645" s="4"/>
       <c r="F645" s="4"/>
@@ -11266,7 +11263,7 @@
       <c r="N645" s="4"/>
       <c r="O645" s="4"/>
     </row>
-    <row r="646" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="646" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D646" s="4"/>
       <c r="E646" s="4"/>
       <c r="F646" s="4"/>
@@ -11279,7 +11276,7 @@
       <c r="N646" s="4"/>
       <c r="O646" s="4"/>
     </row>
-    <row r="647" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="647" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D647" s="4"/>
       <c r="E647" s="4"/>
       <c r="F647" s="4"/>
@@ -11292,7 +11289,7 @@
       <c r="N647" s="4"/>
       <c r="O647" s="4"/>
     </row>
-    <row r="648" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="648" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D648" s="4"/>
       <c r="E648" s="4"/>
       <c r="F648" s="4"/>
@@ -11305,7 +11302,7 @@
       <c r="N648" s="4"/>
       <c r="O648" s="4"/>
     </row>
-    <row r="649" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="649" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D649" s="4"/>
       <c r="E649" s="4"/>
       <c r="F649" s="4"/>
@@ -11318,7 +11315,7 @@
       <c r="N649" s="4"/>
       <c r="O649" s="4"/>
     </row>
-    <row r="650" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="650" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D650" s="4"/>
       <c r="E650" s="4"/>
       <c r="F650" s="4"/>
@@ -11331,7 +11328,7 @@
       <c r="N650" s="4"/>
       <c r="O650" s="4"/>
     </row>
-    <row r="651" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="651" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D651" s="4"/>
       <c r="E651" s="4"/>
       <c r="F651" s="4"/>
@@ -11344,7 +11341,7 @@
       <c r="N651" s="4"/>
       <c r="O651" s="4"/>
     </row>
-    <row r="652" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="652" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D652" s="4"/>
       <c r="E652" s="4"/>
       <c r="F652" s="4"/>
@@ -11357,7 +11354,7 @@
       <c r="N652" s="4"/>
       <c r="O652" s="4"/>
     </row>
-    <row r="653" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="653" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D653" s="4"/>
       <c r="E653" s="4"/>
       <c r="F653" s="4"/>
@@ -11370,7 +11367,7 @@
       <c r="N653" s="4"/>
       <c r="O653" s="4"/>
     </row>
-    <row r="654" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="654" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D654" s="4"/>
       <c r="E654" s="4"/>
       <c r="F654" s="4"/>
@@ -11383,7 +11380,7 @@
       <c r="N654" s="4"/>
       <c r="O654" s="4"/>
     </row>
-    <row r="655" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="655" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D655" s="4"/>
       <c r="E655" s="4"/>
       <c r="F655" s="4"/>
@@ -11396,7 +11393,7 @@
       <c r="N655" s="4"/>
       <c r="O655" s="4"/>
     </row>
-    <row r="656" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="656" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D656" s="4"/>
       <c r="E656" s="4"/>
       <c r="F656" s="4"/>
@@ -11409,7 +11406,7 @@
       <c r="N656" s="4"/>
       <c r="O656" s="4"/>
     </row>
-    <row r="657" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="657" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D657" s="4"/>
       <c r="E657" s="4"/>
       <c r="F657" s="4"/>
@@ -11422,7 +11419,7 @@
       <c r="N657" s="4"/>
       <c r="O657" s="4"/>
     </row>
-    <row r="658" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="658" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D658" s="4"/>
       <c r="E658" s="4"/>
       <c r="F658" s="4"/>
@@ -11435,7 +11432,7 @@
       <c r="N658" s="4"/>
       <c r="O658" s="4"/>
     </row>
-    <row r="659" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="659" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D659" s="4"/>
       <c r="E659" s="4"/>
       <c r="F659" s="4"/>
@@ -11448,7 +11445,7 @@
       <c r="N659" s="4"/>
       <c r="O659" s="4"/>
     </row>
-    <row r="660" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="660" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D660" s="4"/>
       <c r="E660" s="4"/>
       <c r="F660" s="4"/>
@@ -11461,7 +11458,7 @@
       <c r="N660" s="4"/>
       <c r="O660" s="4"/>
     </row>
-    <row r="661" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="661" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D661" s="4"/>
       <c r="E661" s="4"/>
       <c r="F661" s="4"/>
@@ -11474,7 +11471,7 @@
       <c r="N661" s="4"/>
       <c r="O661" s="4"/>
     </row>
-    <row r="662" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="662" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D662" s="4"/>
       <c r="E662" s="4"/>
       <c r="F662" s="4"/>
@@ -11487,7 +11484,7 @@
       <c r="N662" s="4"/>
       <c r="O662" s="4"/>
     </row>
-    <row r="663" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="663" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D663" s="4"/>
       <c r="E663" s="4"/>
       <c r="F663" s="4"/>
@@ -11500,7 +11497,7 @@
       <c r="N663" s="4"/>
       <c r="O663" s="4"/>
     </row>
-    <row r="664" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="664" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D664" s="4"/>
       <c r="E664" s="4"/>
       <c r="F664" s="4"/>
@@ -11513,7 +11510,7 @@
       <c r="N664" s="4"/>
       <c r="O664" s="4"/>
     </row>
-    <row r="665" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="665" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D665" s="4"/>
       <c r="E665" s="4"/>
       <c r="F665" s="4"/>
@@ -11526,7 +11523,7 @@
       <c r="N665" s="4"/>
       <c r="O665" s="4"/>
     </row>
-    <row r="666" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="666" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D666" s="4"/>
       <c r="E666" s="4"/>
       <c r="F666" s="4"/>
@@ -11539,7 +11536,7 @@
       <c r="N666" s="4"/>
       <c r="O666" s="4"/>
     </row>
-    <row r="667" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="667" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D667" s="4"/>
       <c r="E667" s="4"/>
       <c r="F667" s="4"/>
@@ -11552,7 +11549,7 @@
       <c r="N667" s="4"/>
       <c r="O667" s="4"/>
     </row>
-    <row r="668" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="668" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D668" s="4"/>
       <c r="E668" s="4"/>
       <c r="F668" s="4"/>
@@ -11565,7 +11562,7 @@
       <c r="N668" s="4"/>
       <c r="O668" s="4"/>
     </row>
-    <row r="669" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="669" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D669" s="4"/>
       <c r="E669" s="4"/>
       <c r="F669" s="4"/>
@@ -11578,7 +11575,7 @@
       <c r="N669" s="4"/>
       <c r="O669" s="4"/>
     </row>
-    <row r="670" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="670" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D670" s="4"/>
       <c r="E670" s="4"/>
       <c r="F670" s="4"/>
@@ -11591,7 +11588,7 @@
       <c r="N670" s="4"/>
       <c r="O670" s="4"/>
     </row>
-    <row r="671" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="671" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D671" s="4"/>
       <c r="E671" s="4"/>
       <c r="F671" s="4"/>
@@ -11604,7 +11601,7 @@
       <c r="N671" s="4"/>
       <c r="O671" s="4"/>
     </row>
-    <row r="672" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="672" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D672" s="4"/>
       <c r="E672" s="4"/>
       <c r="F672" s="4"/>
@@ -11617,7 +11614,7 @@
       <c r="N672" s="4"/>
       <c r="O672" s="4"/>
     </row>
-    <row r="673" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="673" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D673" s="4"/>
       <c r="E673" s="4"/>
       <c r="F673" s="4"/>
@@ -11630,7 +11627,7 @@
       <c r="N673" s="4"/>
       <c r="O673" s="4"/>
     </row>
-    <row r="674" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="674" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D674" s="4"/>
       <c r="E674" s="4"/>
       <c r="F674" s="4"/>
@@ -11643,7 +11640,7 @@
       <c r="N674" s="4"/>
       <c r="O674" s="4"/>
     </row>
-    <row r="675" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="675" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D675" s="4"/>
       <c r="E675" s="4"/>
       <c r="F675" s="4"/>
@@ -11656,7 +11653,7 @@
       <c r="N675" s="4"/>
       <c r="O675" s="4"/>
     </row>
-    <row r="676" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="676" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D676" s="4"/>
       <c r="E676" s="4"/>
       <c r="F676" s="4"/>
@@ -11669,7 +11666,7 @@
       <c r="N676" s="4"/>
       <c r="O676" s="4"/>
     </row>
-    <row r="677" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="677" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D677" s="4"/>
       <c r="E677" s="4"/>
       <c r="F677" s="4"/>
@@ -11682,7 +11679,7 @@
       <c r="N677" s="4"/>
       <c r="O677" s="4"/>
     </row>
-    <row r="678" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="678" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D678" s="4"/>
       <c r="E678" s="4"/>
       <c r="F678" s="4"/>
@@ -11695,7 +11692,7 @@
       <c r="N678" s="4"/>
       <c r="O678" s="4"/>
     </row>
-    <row r="679" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="679" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D679" s="4"/>
       <c r="E679" s="4"/>
       <c r="F679" s="4"/>
@@ -11708,7 +11705,7 @@
       <c r="N679" s="4"/>
       <c r="O679" s="4"/>
     </row>
-    <row r="680" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="680" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D680" s="4"/>
       <c r="E680" s="4"/>
       <c r="F680" s="4"/>
@@ -11721,7 +11718,7 @@
       <c r="N680" s="4"/>
       <c r="O680" s="4"/>
     </row>
-    <row r="681" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="681" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D681" s="4"/>
       <c r="E681" s="4"/>
       <c r="F681" s="4"/>
@@ -11734,7 +11731,7 @@
       <c r="N681" s="4"/>
       <c r="O681" s="4"/>
     </row>
-    <row r="682" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="682" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D682" s="4"/>
       <c r="E682" s="4"/>
       <c r="F682" s="4"/>
@@ -11747,7 +11744,7 @@
       <c r="N682" s="4"/>
       <c r="O682" s="4"/>
     </row>
-    <row r="683" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="683" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D683" s="4"/>
       <c r="E683" s="4"/>
       <c r="F683" s="4"/>
@@ -11760,7 +11757,7 @@
       <c r="N683" s="4"/>
       <c r="O683" s="4"/>
     </row>
-    <row r="684" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="684" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D684" s="4"/>
       <c r="E684" s="4"/>
       <c r="F684" s="4"/>
@@ -11773,7 +11770,7 @@
       <c r="N684" s="4"/>
       <c r="O684" s="4"/>
     </row>
-    <row r="685" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="685" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D685" s="4"/>
       <c r="E685" s="4"/>
       <c r="F685" s="4"/>
@@ -11786,7 +11783,7 @@
       <c r="N685" s="4"/>
       <c r="O685" s="4"/>
     </row>
-    <row r="686" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="686" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D686" s="4"/>
       <c r="E686" s="4"/>
       <c r="F686" s="4"/>
@@ -11799,7 +11796,7 @@
       <c r="N686" s="4"/>
       <c r="O686" s="4"/>
     </row>
-    <row r="687" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="687" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D687" s="4"/>
       <c r="E687" s="4"/>
       <c r="F687" s="4"/>
@@ -11812,7 +11809,7 @@
       <c r="N687" s="4"/>
       <c r="O687" s="4"/>
     </row>
-    <row r="688" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="688" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D688" s="4"/>
       <c r="E688" s="4"/>
       <c r="F688" s="4"/>
@@ -11825,7 +11822,7 @@
       <c r="N688" s="4"/>
       <c r="O688" s="4"/>
     </row>
-    <row r="689" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="689" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D689" s="4"/>
       <c r="E689" s="4"/>
       <c r="F689" s="4"/>
@@ -11838,7 +11835,7 @@
       <c r="N689" s="4"/>
       <c r="O689" s="4"/>
     </row>
-    <row r="690" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="690" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D690" s="4"/>
       <c r="E690" s="4"/>
       <c r="F690" s="4"/>
@@ -11851,7 +11848,7 @@
       <c r="N690" s="4"/>
       <c r="O690" s="4"/>
     </row>
-    <row r="691" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="691" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D691" s="4"/>
       <c r="E691" s="4"/>
       <c r="F691" s="4"/>
@@ -11864,7 +11861,7 @@
       <c r="N691" s="4"/>
       <c r="O691" s="4"/>
     </row>
-    <row r="692" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="692" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D692" s="4"/>
       <c r="E692" s="4"/>
       <c r="F692" s="4"/>
@@ -11877,7 +11874,7 @@
       <c r="N692" s="4"/>
       <c r="O692" s="4"/>
     </row>
-    <row r="693" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="693" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D693" s="4"/>
       <c r="E693" s="4"/>
       <c r="F693" s="4"/>
@@ -11890,7 +11887,7 @@
       <c r="N693" s="4"/>
       <c r="O693" s="4"/>
     </row>
-    <row r="694" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="694" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D694" s="4"/>
       <c r="E694" s="4"/>
       <c r="F694" s="4"/>
@@ -11903,7 +11900,7 @@
       <c r="N694" s="4"/>
       <c r="O694" s="4"/>
     </row>
-    <row r="695" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="695" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D695" s="4"/>
       <c r="E695" s="4"/>
       <c r="F695" s="4"/>
@@ -11916,7 +11913,7 @@
       <c r="N695" s="4"/>
       <c r="O695" s="4"/>
     </row>
-    <row r="696" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="696" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D696" s="4"/>
       <c r="E696" s="4"/>
       <c r="F696" s="4"/>
@@ -11929,7 +11926,7 @@
       <c r="N696" s="4"/>
       <c r="O696" s="4"/>
     </row>
-    <row r="697" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="697" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D697" s="4"/>
       <c r="E697" s="4"/>
       <c r="F697" s="4"/>
@@ -11942,7 +11939,7 @@
       <c r="N697" s="4"/>
       <c r="O697" s="4"/>
     </row>
-    <row r="698" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="698" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D698" s="4"/>
       <c r="E698" s="4"/>
       <c r="F698" s="4"/>
@@ -11955,7 +11952,7 @@
       <c r="N698" s="4"/>
       <c r="O698" s="4"/>
     </row>
-    <row r="699" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="699" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D699" s="4"/>
       <c r="E699" s="4"/>
       <c r="F699" s="4"/>
@@ -11968,7 +11965,7 @@
       <c r="N699" s="4"/>
       <c r="O699" s="4"/>
     </row>
-    <row r="700" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="700" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D700" s="4"/>
       <c r="E700" s="4"/>
       <c r="F700" s="4"/>
@@ -11981,7 +11978,7 @@
       <c r="N700" s="4"/>
       <c r="O700" s="4"/>
     </row>
-    <row r="701" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="701" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D701" s="4"/>
       <c r="E701" s="4"/>
       <c r="F701" s="4"/>
@@ -11994,7 +11991,7 @@
       <c r="N701" s="4"/>
       <c r="O701" s="4"/>
     </row>
-    <row r="702" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="702" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D702" s="4"/>
       <c r="E702" s="4"/>
       <c r="F702" s="4"/>
@@ -12007,7 +12004,7 @@
       <c r="N702" s="4"/>
       <c r="O702" s="4"/>
     </row>
-    <row r="703" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="703" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D703" s="4"/>
       <c r="E703" s="4"/>
       <c r="F703" s="4"/>
@@ -12020,7 +12017,7 @@
       <c r="N703" s="4"/>
       <c r="O703" s="4"/>
     </row>
-    <row r="704" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="704" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D704" s="4"/>
       <c r="E704" s="4"/>
       <c r="F704" s="4"/>
@@ -12033,7 +12030,7 @@
       <c r="N704" s="4"/>
       <c r="O704" s="4"/>
     </row>
-    <row r="705" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="705" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D705" s="4"/>
       <c r="E705" s="4"/>
       <c r="F705" s="4"/>
@@ -12046,7 +12043,7 @@
       <c r="N705" s="4"/>
       <c r="O705" s="4"/>
     </row>
-    <row r="706" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="706" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D706" s="4"/>
       <c r="E706" s="4"/>
       <c r="F706" s="4"/>
@@ -12059,7 +12056,7 @@
       <c r="N706" s="4"/>
       <c r="O706" s="4"/>
     </row>
-    <row r="707" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="707" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D707" s="4"/>
       <c r="E707" s="4"/>
       <c r="F707" s="4"/>
@@ -12072,7 +12069,7 @@
       <c r="N707" s="4"/>
       <c r="O707" s="4"/>
     </row>
-    <row r="708" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="708" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D708" s="4"/>
       <c r="E708" s="4"/>
       <c r="F708" s="4"/>
@@ -12085,7 +12082,7 @@
       <c r="N708" s="4"/>
       <c r="O708" s="4"/>
     </row>
-    <row r="709" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="709" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D709" s="4"/>
       <c r="E709" s="4"/>
       <c r="F709" s="4"/>
@@ -12098,7 +12095,7 @@
       <c r="N709" s="4"/>
       <c r="O709" s="4"/>
     </row>
-    <row r="710" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="710" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D710" s="4"/>
       <c r="E710" s="4"/>
       <c r="F710" s="4"/>
@@ -12111,7 +12108,7 @@
       <c r="N710" s="4"/>
       <c r="O710" s="4"/>
     </row>
-    <row r="711" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="711" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D711" s="4"/>
       <c r="E711" s="4"/>
       <c r="F711" s="4"/>
@@ -12124,7 +12121,7 @@
       <c r="N711" s="4"/>
       <c r="O711" s="4"/>
     </row>
-    <row r="712" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="712" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D712" s="4"/>
       <c r="E712" s="4"/>
       <c r="F712" s="4"/>
@@ -12137,7 +12134,7 @@
       <c r="N712" s="4"/>
       <c r="O712" s="4"/>
     </row>
-    <row r="713" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="713" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D713" s="4"/>
       <c r="E713" s="4"/>
       <c r="F713" s="4"/>
@@ -12150,7 +12147,7 @@
       <c r="N713" s="4"/>
       <c r="O713" s="4"/>
     </row>
-    <row r="714" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="714" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D714" s="4"/>
       <c r="E714" s="4"/>
       <c r="F714" s="4"/>
@@ -12163,7 +12160,7 @@
       <c r="N714" s="4"/>
       <c r="O714" s="4"/>
     </row>
-    <row r="715" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="715" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D715" s="4"/>
       <c r="E715" s="4"/>
       <c r="F715" s="4"/>
@@ -12176,7 +12173,7 @@
       <c r="N715" s="4"/>
       <c r="O715" s="4"/>
     </row>
-    <row r="716" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="716" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D716" s="4"/>
       <c r="E716" s="4"/>
       <c r="F716" s="4"/>
@@ -12189,7 +12186,7 @@
       <c r="N716" s="4"/>
       <c r="O716" s="4"/>
     </row>
-    <row r="717" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="717" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D717" s="4"/>
       <c r="E717" s="4"/>
       <c r="F717" s="4"/>
@@ -12202,7 +12199,7 @@
       <c r="N717" s="4"/>
       <c r="O717" s="4"/>
     </row>
-    <row r="718" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="718" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D718" s="4"/>
       <c r="E718" s="4"/>
       <c r="F718" s="4"/>
@@ -12215,7 +12212,7 @@
       <c r="N718" s="4"/>
       <c r="O718" s="4"/>
     </row>
-    <row r="719" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="719" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D719" s="4"/>
       <c r="E719" s="4"/>
       <c r="F719" s="4"/>
@@ -12228,7 +12225,7 @@
       <c r="N719" s="4"/>
       <c r="O719" s="4"/>
     </row>
-    <row r="720" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="720" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D720" s="4"/>
       <c r="E720" s="4"/>
       <c r="F720" s="4"/>
@@ -12241,7 +12238,7 @@
       <c r="N720" s="4"/>
       <c r="O720" s="4"/>
     </row>
-    <row r="721" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="721" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D721" s="4"/>
       <c r="E721" s="4"/>
       <c r="F721" s="4"/>
@@ -12254,7 +12251,7 @@
       <c r="N721" s="4"/>
       <c r="O721" s="4"/>
     </row>
-    <row r="722" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="722" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D722" s="4"/>
       <c r="E722" s="4"/>
       <c r="F722" s="4"/>
@@ -12267,7 +12264,7 @@
       <c r="N722" s="4"/>
       <c r="O722" s="4"/>
     </row>
-    <row r="723" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="723" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D723" s="4"/>
       <c r="E723" s="4"/>
       <c r="F723" s="4"/>
@@ -12280,7 +12277,7 @@
       <c r="N723" s="4"/>
       <c r="O723" s="4"/>
     </row>
-    <row r="724" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="724" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D724" s="4"/>
       <c r="E724" s="4"/>
       <c r="F724" s="4"/>
@@ -12293,7 +12290,7 @@
       <c r="N724" s="4"/>
       <c r="O724" s="4"/>
     </row>
-    <row r="725" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="725" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D725" s="4"/>
       <c r="E725" s="4"/>
       <c r="F725" s="4"/>
@@ -12306,7 +12303,7 @@
       <c r="N725" s="4"/>
       <c r="O725" s="4"/>
     </row>
-    <row r="726" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="726" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D726" s="4"/>
       <c r="E726" s="4"/>
       <c r="F726" s="4"/>
@@ -12319,7 +12316,7 @@
       <c r="N726" s="4"/>
       <c r="O726" s="4"/>
     </row>
-    <row r="727" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="727" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D727" s="4"/>
       <c r="E727" s="4"/>
       <c r="F727" s="4"/>
@@ -12332,7 +12329,7 @@
       <c r="N727" s="4"/>
       <c r="O727" s="4"/>
     </row>
-    <row r="728" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="728" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D728" s="4"/>
       <c r="E728" s="4"/>
       <c r="F728" s="4"/>
@@ -12345,7 +12342,7 @@
       <c r="N728" s="4"/>
       <c r="O728" s="4"/>
     </row>
-    <row r="729" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="729" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D729" s="4"/>
       <c r="E729" s="4"/>
       <c r="F729" s="4"/>
@@ -12358,7 +12355,7 @@
       <c r="N729" s="4"/>
       <c r="O729" s="4"/>
     </row>
-    <row r="730" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="730" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D730" s="4"/>
       <c r="E730" s="4"/>
       <c r="F730" s="4"/>
@@ -12371,7 +12368,7 @@
       <c r="N730" s="4"/>
       <c r="O730" s="4"/>
     </row>
-    <row r="731" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="731" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D731" s="4"/>
       <c r="E731" s="4"/>
       <c r="F731" s="4"/>
@@ -12384,7 +12381,7 @@
       <c r="N731" s="4"/>
       <c r="O731" s="4"/>
     </row>
-    <row r="732" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="732" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D732" s="4"/>
       <c r="E732" s="4"/>
       <c r="F732" s="4"/>
@@ -12397,7 +12394,7 @@
       <c r="N732" s="4"/>
       <c r="O732" s="4"/>
     </row>
-    <row r="733" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="733" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D733" s="4"/>
       <c r="E733" s="4"/>
       <c r="F733" s="4"/>
@@ -12410,7 +12407,7 @@
       <c r="N733" s="4"/>
       <c r="O733" s="4"/>
     </row>
-    <row r="734" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="734" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D734" s="4"/>
       <c r="E734" s="4"/>
       <c r="F734" s="4"/>
@@ -12423,7 +12420,7 @@
       <c r="N734" s="4"/>
       <c r="O734" s="4"/>
     </row>
-    <row r="735" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="735" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D735" s="4"/>
       <c r="E735" s="4"/>
       <c r="F735" s="4"/>
@@ -12436,7 +12433,7 @@
       <c r="N735" s="4"/>
       <c r="O735" s="4"/>
     </row>
-    <row r="736" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="736" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D736" s="4"/>
       <c r="E736" s="4"/>
       <c r="F736" s="4"/>
@@ -12449,7 +12446,7 @@
       <c r="N736" s="4"/>
       <c r="O736" s="4"/>
     </row>
-    <row r="737" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="737" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D737" s="4"/>
       <c r="E737" s="4"/>
       <c r="F737" s="4"/>
@@ -12462,7 +12459,7 @@
       <c r="N737" s="4"/>
       <c r="O737" s="4"/>
     </row>
-    <row r="738" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="738" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D738" s="4"/>
       <c r="E738" s="4"/>
       <c r="F738" s="4"/>
@@ -12475,7 +12472,7 @@
       <c r="N738" s="4"/>
       <c r="O738" s="4"/>
     </row>
-    <row r="739" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="739" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D739" s="4"/>
       <c r="E739" s="4"/>
       <c r="F739" s="4"/>
@@ -12488,7 +12485,7 @@
       <c r="N739" s="4"/>
       <c r="O739" s="4"/>
     </row>
-    <row r="740" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="740" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D740" s="4"/>
       <c r="E740" s="4"/>
       <c r="F740" s="4"/>
@@ -12501,7 +12498,7 @@
       <c r="N740" s="4"/>
       <c r="O740" s="4"/>
     </row>
-    <row r="741" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="741" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D741" s="4"/>
       <c r="E741" s="4"/>
       <c r="F741" s="4"/>
@@ -12514,7 +12511,7 @@
       <c r="N741" s="4"/>
       <c r="O741" s="4"/>
     </row>
-    <row r="742" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="742" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D742" s="4"/>
       <c r="E742" s="4"/>
       <c r="F742" s="4"/>
@@ -12527,7 +12524,7 @@
       <c r="N742" s="4"/>
       <c r="O742" s="4"/>
     </row>
-    <row r="743" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="743" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D743" s="4"/>
       <c r="E743" s="4"/>
       <c r="F743" s="4"/>
@@ -12540,7 +12537,7 @@
       <c r="N743" s="4"/>
       <c r="O743" s="4"/>
     </row>
-    <row r="744" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="744" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D744" s="4"/>
       <c r="E744" s="4"/>
       <c r="F744" s="4"/>
@@ -12553,7 +12550,7 @@
       <c r="N744" s="4"/>
       <c r="O744" s="4"/>
     </row>
-    <row r="745" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="745" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D745" s="4"/>
       <c r="E745" s="4"/>
       <c r="F745" s="4"/>
@@ -12566,7 +12563,7 @@
       <c r="N745" s="4"/>
       <c r="O745" s="4"/>
     </row>
-    <row r="746" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="746" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D746" s="4"/>
       <c r="E746" s="4"/>
       <c r="F746" s="4"/>
@@ -12579,7 +12576,7 @@
       <c r="N746" s="4"/>
       <c r="O746" s="4"/>
     </row>
-    <row r="747" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="747" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D747" s="4"/>
       <c r="E747" s="4"/>
       <c r="F747" s="4"/>
@@ -12592,7 +12589,7 @@
       <c r="N747" s="4"/>
       <c r="O747" s="4"/>
     </row>
-    <row r="748" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="748" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D748" s="4"/>
       <c r="E748" s="4"/>
       <c r="F748" s="4"/>
@@ -12605,7 +12602,7 @@
       <c r="N748" s="4"/>
       <c r="O748" s="4"/>
     </row>
-    <row r="749" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="749" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D749" s="4"/>
       <c r="E749" s="4"/>
       <c r="F749" s="4"/>
@@ -12618,7 +12615,7 @@
       <c r="N749" s="4"/>
       <c r="O749" s="4"/>
     </row>
-    <row r="750" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="750" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D750" s="4"/>
       <c r="E750" s="4"/>
       <c r="F750" s="4"/>
@@ -12631,7 +12628,7 @@
       <c r="N750" s="4"/>
       <c r="O750" s="4"/>
     </row>
-    <row r="751" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="751" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D751" s="4"/>
       <c r="E751" s="4"/>
       <c r="F751" s="4"/>
@@ -12644,7 +12641,7 @@
       <c r="N751" s="4"/>
       <c r="O751" s="4"/>
     </row>
-    <row r="752" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="752" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D752" s="4"/>
       <c r="E752" s="4"/>
       <c r="F752" s="4"/>
@@ -12657,7 +12654,7 @@
       <c r="N752" s="4"/>
       <c r="O752" s="4"/>
     </row>
-    <row r="753" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="753" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D753" s="4"/>
       <c r="E753" s="4"/>
       <c r="F753" s="4"/>
@@ -12670,7 +12667,7 @@
       <c r="N753" s="4"/>
       <c r="O753" s="4"/>
     </row>
-    <row r="754" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="754" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D754" s="4"/>
       <c r="E754" s="4"/>
       <c r="F754" s="4"/>
@@ -12683,7 +12680,7 @@
       <c r="N754" s="4"/>
       <c r="O754" s="4"/>
     </row>
-    <row r="755" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="755" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D755" s="4"/>
       <c r="E755" s="4"/>
       <c r="F755" s="4"/>
@@ -12696,7 +12693,7 @@
       <c r="N755" s="4"/>
       <c r="O755" s="4"/>
     </row>
-    <row r="756" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="756" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D756" s="4"/>
       <c r="E756" s="4"/>
       <c r="F756" s="4"/>
@@ -12709,7 +12706,7 @@
       <c r="N756" s="4"/>
       <c r="O756" s="4"/>
     </row>
-    <row r="757" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="757" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D757" s="4"/>
       <c r="E757" s="4"/>
       <c r="F757" s="4"/>
@@ -12722,7 +12719,7 @@
       <c r="N757" s="4"/>
       <c r="O757" s="4"/>
     </row>
-    <row r="758" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="758" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D758" s="4"/>
       <c r="E758" s="4"/>
       <c r="F758" s="4"/>
@@ -12735,7 +12732,7 @@
       <c r="N758" s="4"/>
       <c r="O758" s="4"/>
     </row>
-    <row r="759" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="759" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D759" s="4"/>
       <c r="E759" s="4"/>
       <c r="F759" s="4"/>
@@ -12748,7 +12745,7 @@
       <c r="N759" s="4"/>
       <c r="O759" s="4"/>
     </row>
-    <row r="760" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="760" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D760" s="4"/>
       <c r="E760" s="4"/>
       <c r="F760" s="4"/>
@@ -12761,7 +12758,7 @@
       <c r="N760" s="4"/>
       <c r="O760" s="4"/>
     </row>
-    <row r="761" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="761" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D761" s="4"/>
       <c r="E761" s="4"/>
       <c r="F761" s="4"/>
@@ -12774,7 +12771,7 @@
       <c r="N761" s="4"/>
       <c r="O761" s="4"/>
     </row>
-    <row r="762" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="762" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D762" s="4"/>
       <c r="E762" s="4"/>
       <c r="F762" s="4"/>
@@ -12787,7 +12784,7 @@
       <c r="N762" s="4"/>
       <c r="O762" s="4"/>
     </row>
-    <row r="763" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="763" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D763" s="4"/>
       <c r="E763" s="4"/>
       <c r="F763" s="4"/>
@@ -12800,7 +12797,7 @@
       <c r="N763" s="4"/>
       <c r="O763" s="4"/>
     </row>
-    <row r="764" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="764" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D764" s="4"/>
       <c r="E764" s="4"/>
       <c r="F764" s="4"/>
@@ -12813,7 +12810,7 @@
       <c r="N764" s="4"/>
       <c r="O764" s="4"/>
     </row>
-    <row r="765" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="765" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D765" s="4"/>
       <c r="E765" s="4"/>
       <c r="F765" s="4"/>
@@ -12826,7 +12823,7 @@
       <c r="N765" s="4"/>
       <c r="O765" s="4"/>
     </row>
-    <row r="766" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="766" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D766" s="4"/>
       <c r="E766" s="4"/>
       <c r="F766" s="4"/>
@@ -12839,7 +12836,7 @@
       <c r="N766" s="4"/>
       <c r="O766" s="4"/>
     </row>
-    <row r="767" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="767" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D767" s="4"/>
       <c r="E767" s="4"/>
       <c r="F767" s="4"/>
@@ -12852,7 +12849,7 @@
       <c r="N767" s="4"/>
       <c r="O767" s="4"/>
     </row>
-    <row r="768" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="768" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D768" s="4"/>
       <c r="E768" s="4"/>
       <c r="F768" s="4"/>
@@ -12865,7 +12862,7 @@
       <c r="N768" s="4"/>
       <c r="O768" s="4"/>
     </row>
-    <row r="769" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="769" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D769" s="4"/>
       <c r="E769" s="4"/>
       <c r="F769" s="4"/>
@@ -12878,7 +12875,7 @@
       <c r="N769" s="4"/>
       <c r="O769" s="4"/>
     </row>
-    <row r="770" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="770" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D770" s="4"/>
       <c r="E770" s="4"/>
       <c r="F770" s="4"/>
@@ -12891,7 +12888,7 @@
       <c r="N770" s="4"/>
       <c r="O770" s="4"/>
     </row>
-    <row r="771" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="771" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D771" s="4"/>
       <c r="E771" s="4"/>
       <c r="F771" s="4"/>
@@ -12904,7 +12901,7 @@
       <c r="N771" s="4"/>
       <c r="O771" s="4"/>
     </row>
-    <row r="772" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="772" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D772" s="4"/>
       <c r="E772" s="4"/>
       <c r="F772" s="4"/>
@@ -12917,7 +12914,7 @@
       <c r="N772" s="4"/>
       <c r="O772" s="4"/>
     </row>
-    <row r="773" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="773" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D773" s="4"/>
       <c r="E773" s="4"/>
       <c r="F773" s="4"/>
@@ -12930,7 +12927,7 @@
       <c r="N773" s="4"/>
       <c r="O773" s="4"/>
     </row>
-    <row r="774" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="774" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D774" s="4"/>
       <c r="E774" s="4"/>
       <c r="F774" s="4"/>
@@ -12943,7 +12940,7 @@
       <c r="N774" s="4"/>
       <c r="O774" s="4"/>
     </row>
-    <row r="775" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="775" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D775" s="4"/>
       <c r="E775" s="4"/>
       <c r="F775" s="4"/>
@@ -12956,7 +12953,7 @@
       <c r="N775" s="4"/>
       <c r="O775" s="4"/>
     </row>
-    <row r="776" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="776" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D776" s="4"/>
       <c r="E776" s="4"/>
       <c r="F776" s="4"/>
@@ -12969,7 +12966,7 @@
       <c r="N776" s="4"/>
       <c r="O776" s="4"/>
     </row>
-    <row r="777" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="777" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D777" s="4"/>
       <c r="E777" s="4"/>
       <c r="F777" s="4"/>
@@ -12982,7 +12979,7 @@
       <c r="N777" s="4"/>
       <c r="O777" s="4"/>
     </row>
-    <row r="778" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="778" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D778" s="4"/>
       <c r="E778" s="4"/>
       <c r="F778" s="4"/>
@@ -12995,7 +12992,7 @@
       <c r="N778" s="4"/>
       <c r="O778" s="4"/>
     </row>
-    <row r="779" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="779" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D779" s="4"/>
       <c r="E779" s="4"/>
       <c r="F779" s="4"/>
@@ -13008,7 +13005,7 @@
       <c r="N779" s="4"/>
       <c r="O779" s="4"/>
     </row>
-    <row r="780" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="780" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D780" s="4"/>
       <c r="E780" s="4"/>
       <c r="F780" s="4"/>
@@ -13021,7 +13018,7 @@
       <c r="N780" s="4"/>
       <c r="O780" s="4"/>
     </row>
-    <row r="781" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="781" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D781" s="4"/>
       <c r="E781" s="4"/>
       <c r="F781" s="4"/>
@@ -13034,7 +13031,7 @@
       <c r="N781" s="4"/>
       <c r="O781" s="4"/>
     </row>
-    <row r="782" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="782" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D782" s="4"/>
       <c r="E782" s="4"/>
       <c r="F782" s="4"/>
@@ -13047,7 +13044,7 @@
       <c r="N782" s="4"/>
       <c r="O782" s="4"/>
     </row>
-    <row r="783" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="783" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D783" s="4"/>
       <c r="E783" s="4"/>
       <c r="F783" s="4"/>
@@ -13060,7 +13057,7 @@
       <c r="N783" s="4"/>
       <c r="O783" s="4"/>
     </row>
-    <row r="784" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="784" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D784" s="4"/>
       <c r="E784" s="4"/>
       <c r="F784" s="4"/>
@@ -13073,7 +13070,7 @@
       <c r="N784" s="4"/>
       <c r="O784" s="4"/>
     </row>
-    <row r="785" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="785" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D785" s="4"/>
       <c r="E785" s="4"/>
       <c r="F785" s="4"/>
@@ -13086,7 +13083,7 @@
       <c r="N785" s="4"/>
       <c r="O785" s="4"/>
     </row>
-    <row r="786" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="786" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D786" s="4"/>
       <c r="E786" s="4"/>
       <c r="F786" s="4"/>
@@ -13099,7 +13096,7 @@
       <c r="N786" s="4"/>
       <c r="O786" s="4"/>
     </row>
-    <row r="787" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="787" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D787" s="4"/>
       <c r="E787" s="4"/>
       <c r="F787" s="4"/>
@@ -13112,7 +13109,7 @@
       <c r="N787" s="4"/>
       <c r="O787" s="4"/>
     </row>
-    <row r="788" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="788" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D788" s="4"/>
       <c r="E788" s="4"/>
       <c r="F788" s="4"/>
@@ -13125,7 +13122,7 @@
       <c r="N788" s="4"/>
       <c r="O788" s="4"/>
     </row>
-    <row r="789" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="789" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D789" s="4"/>
       <c r="E789" s="4"/>
       <c r="F789" s="4"/>
@@ -13138,7 +13135,7 @@
       <c r="N789" s="4"/>
       <c r="O789" s="4"/>
     </row>
-    <row r="790" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="790" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D790" s="4"/>
       <c r="E790" s="4"/>
       <c r="F790" s="4"/>
@@ -13151,7 +13148,7 @@
       <c r="N790" s="4"/>
       <c r="O790" s="4"/>
     </row>
-    <row r="791" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="791" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D791" s="4"/>
       <c r="E791" s="4"/>
       <c r="F791" s="4"/>
@@ -13164,7 +13161,7 @@
       <c r="N791" s="4"/>
       <c r="O791" s="4"/>
     </row>
-    <row r="792" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="792" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D792" s="4"/>
       <c r="E792" s="4"/>
       <c r="F792" s="4"/>
@@ -13177,7 +13174,7 @@
       <c r="N792" s="4"/>
       <c r="O792" s="4"/>
     </row>
-    <row r="793" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="793" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D793" s="4"/>
       <c r="E793" s="4"/>
       <c r="F793" s="4"/>
@@ -13190,7 +13187,7 @@
       <c r="N793" s="4"/>
       <c r="O793" s="4"/>
     </row>
-    <row r="794" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="794" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D794" s="4"/>
       <c r="E794" s="4"/>
       <c r="F794" s="4"/>
@@ -13203,7 +13200,7 @@
       <c r="N794" s="4"/>
       <c r="O794" s="4"/>
     </row>
-    <row r="795" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="795" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D795" s="4"/>
       <c r="E795" s="4"/>
       <c r="F795" s="4"/>
@@ -13216,7 +13213,7 @@
       <c r="N795" s="4"/>
       <c r="O795" s="4"/>
     </row>
-    <row r="796" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="796" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D796" s="4"/>
       <c r="E796" s="4"/>
       <c r="F796" s="4"/>
@@ -13229,7 +13226,7 @@
       <c r="N796" s="4"/>
       <c r="O796" s="4"/>
     </row>
-    <row r="797" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="797" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D797" s="4"/>
       <c r="E797" s="4"/>
       <c r="F797" s="4"/>
@@ -13242,7 +13239,7 @@
       <c r="N797" s="4"/>
       <c r="O797" s="4"/>
     </row>
-    <row r="798" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="798" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D798" s="4"/>
       <c r="E798" s="4"/>
       <c r="F798" s="4"/>
@@ -13255,7 +13252,7 @@
       <c r="N798" s="4"/>
       <c r="O798" s="4"/>
     </row>
-    <row r="799" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="799" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D799" s="4"/>
       <c r="E799" s="4"/>
       <c r="F799" s="4"/>
@@ -13268,7 +13265,7 @@
       <c r="N799" s="4"/>
       <c r="O799" s="4"/>
     </row>
-    <row r="800" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="800" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D800" s="4"/>
       <c r="E800" s="4"/>
       <c r="F800" s="4"/>
@@ -13281,7 +13278,7 @@
       <c r="N800" s="4"/>
       <c r="O800" s="4"/>
     </row>
-    <row r="801" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="801" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D801" s="4"/>
       <c r="E801" s="4"/>
       <c r="F801" s="4"/>
@@ -13294,7 +13291,7 @@
       <c r="N801" s="4"/>
       <c r="O801" s="4"/>
     </row>
-    <row r="802" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="802" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D802" s="4"/>
       <c r="E802" s="4"/>
       <c r="F802" s="4"/>
@@ -13307,7 +13304,7 @@
       <c r="N802" s="4"/>
       <c r="O802" s="4"/>
     </row>
-    <row r="803" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="803" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D803" s="4"/>
       <c r="E803" s="4"/>
       <c r="F803" s="4"/>
@@ -13320,7 +13317,7 @@
       <c r="N803" s="4"/>
       <c r="O803" s="4"/>
     </row>
-    <row r="804" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="804" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D804" s="4"/>
       <c r="E804" s="4"/>
       <c r="F804" s="4"/>
@@ -13333,7 +13330,7 @@
       <c r="N804" s="4"/>
       <c r="O804" s="4"/>
     </row>
-    <row r="805" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="805" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D805" s="4"/>
       <c r="E805" s="4"/>
       <c r="F805" s="4"/>
@@ -13346,7 +13343,7 @@
       <c r="N805" s="4"/>
       <c r="O805" s="4"/>
     </row>
-    <row r="806" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="806" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D806" s="4"/>
       <c r="E806" s="4"/>
       <c r="F806" s="4"/>
@@ -13359,7 +13356,7 @@
       <c r="N806" s="4"/>
       <c r="O806" s="4"/>
     </row>
-    <row r="807" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="807" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D807" s="4"/>
       <c r="E807" s="4"/>
       <c r="F807" s="4"/>
@@ -13372,7 +13369,7 @@
       <c r="N807" s="4"/>
       <c r="O807" s="4"/>
     </row>
-    <row r="808" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="808" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D808" s="4"/>
       <c r="E808" s="4"/>
       <c r="F808" s="4"/>
@@ -13385,7 +13382,7 @@
       <c r="N808" s="4"/>
       <c r="O808" s="4"/>
     </row>
-    <row r="809" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="809" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D809" s="4"/>
       <c r="E809" s="4"/>
       <c r="F809" s="4"/>
@@ -13398,7 +13395,7 @@
       <c r="N809" s="4"/>
       <c r="O809" s="4"/>
     </row>
-    <row r="810" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="810" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D810" s="4"/>
       <c r="E810" s="4"/>
       <c r="F810" s="4"/>
@@ -13411,7 +13408,7 @@
       <c r="N810" s="4"/>
       <c r="O810" s="4"/>
     </row>
-    <row r="811" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="811" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D811" s="4"/>
       <c r="E811" s="4"/>
       <c r="F811" s="4"/>
@@ -13424,7 +13421,7 @@
       <c r="N811" s="4"/>
       <c r="O811" s="4"/>
     </row>
-    <row r="812" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="812" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D812" s="4"/>
       <c r="E812" s="4"/>
       <c r="F812" s="4"/>
@@ -13437,7 +13434,7 @@
       <c r="N812" s="4"/>
       <c r="O812" s="4"/>
     </row>
-    <row r="813" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="813" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D813" s="4"/>
       <c r="E813" s="4"/>
       <c r="F813" s="4"/>
@@ -13450,7 +13447,7 @@
       <c r="N813" s="4"/>
       <c r="O813" s="4"/>
     </row>
-    <row r="814" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="814" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D814" s="4"/>
       <c r="E814" s="4"/>
       <c r="F814" s="4"/>
@@ -13463,7 +13460,7 @@
       <c r="N814" s="4"/>
       <c r="O814" s="4"/>
     </row>
-    <row r="815" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="815" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D815" s="4"/>
       <c r="E815" s="4"/>
       <c r="F815" s="4"/>
@@ -13476,7 +13473,7 @@
       <c r="N815" s="4"/>
       <c r="O815" s="4"/>
     </row>
-    <row r="816" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="816" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D816" s="4"/>
       <c r="E816" s="4"/>
       <c r="F816" s="4"/>
@@ -13489,7 +13486,7 @@
       <c r="N816" s="4"/>
       <c r="O816" s="4"/>
     </row>
-    <row r="817" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="817" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D817" s="4"/>
       <c r="E817" s="4"/>
       <c r="F817" s="4"/>
@@ -13502,7 +13499,7 @@
       <c r="N817" s="4"/>
       <c r="O817" s="4"/>
     </row>
-    <row r="818" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="818" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D818" s="4"/>
       <c r="E818" s="4"/>
       <c r="F818" s="4"/>
@@ -13515,7 +13512,7 @@
       <c r="N818" s="4"/>
       <c r="O818" s="4"/>
     </row>
-    <row r="819" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="819" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D819" s="4"/>
       <c r="E819" s="4"/>
       <c r="F819" s="4"/>
@@ -13528,7 +13525,7 @@
       <c r="N819" s="4"/>
       <c r="O819" s="4"/>
     </row>
-    <row r="820" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="820" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D820" s="4"/>
       <c r="E820" s="4"/>
       <c r="F820" s="4"/>
@@ -13541,7 +13538,7 @@
       <c r="N820" s="4"/>
       <c r="O820" s="4"/>
     </row>
-    <row r="821" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="821" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D821" s="4"/>
       <c r="E821" s="4"/>
       <c r="F821" s="4"/>
@@ -13554,7 +13551,7 @@
       <c r="N821" s="4"/>
       <c r="O821" s="4"/>
     </row>
-    <row r="822" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="822" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D822" s="4"/>
       <c r="E822" s="4"/>
       <c r="F822" s="4"/>
@@ -13567,7 +13564,7 @@
       <c r="N822" s="4"/>
       <c r="O822" s="4"/>
     </row>
-    <row r="823" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="823" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D823" s="4"/>
       <c r="E823" s="4"/>
       <c r="F823" s="4"/>
@@ -13580,7 +13577,7 @@
       <c r="N823" s="4"/>
       <c r="O823" s="4"/>
     </row>
-    <row r="824" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="824" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D824" s="4"/>
       <c r="E824" s="4"/>
       <c r="F824" s="4"/>
@@ -13593,7 +13590,7 @@
       <c r="N824" s="4"/>
       <c r="O824" s="4"/>
     </row>
-    <row r="825" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="825" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D825" s="4"/>
       <c r="E825" s="4"/>
       <c r="F825" s="4"/>
@@ -13606,7 +13603,7 @@
       <c r="N825" s="4"/>
       <c r="O825" s="4"/>
     </row>
-    <row r="826" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="826" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D826" s="4"/>
       <c r="E826" s="4"/>
       <c r="F826" s="4"/>
@@ -13619,7 +13616,7 @@
       <c r="N826" s="4"/>
       <c r="O826" s="4"/>
     </row>
-    <row r="827" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="827" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D827" s="4"/>
       <c r="E827" s="4"/>
       <c r="F827" s="4"/>
@@ -13632,7 +13629,7 @@
       <c r="N827" s="4"/>
       <c r="O827" s="4"/>
     </row>
-    <row r="828" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="828" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D828" s="4"/>
       <c r="E828" s="4"/>
       <c r="F828" s="4"/>
@@ -13645,7 +13642,7 @@
       <c r="N828" s="4"/>
       <c r="O828" s="4"/>
     </row>
-    <row r="829" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="829" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D829" s="4"/>
       <c r="E829" s="4"/>
       <c r="F829" s="4"/>
@@ -13658,7 +13655,7 @@
       <c r="N829" s="4"/>
       <c r="O829" s="4"/>
     </row>
-    <row r="830" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="830" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D830" s="4"/>
       <c r="E830" s="4"/>
       <c r="F830" s="4"/>
@@ -13671,7 +13668,7 @@
       <c r="N830" s="4"/>
       <c r="O830" s="4"/>
     </row>
-    <row r="831" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="831" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D831" s="4"/>
       <c r="E831" s="4"/>
       <c r="F831" s="4"/>
@@ -13684,7 +13681,7 @@
       <c r="N831" s="4"/>
       <c r="O831" s="4"/>
     </row>
-    <row r="832" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="832" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D832" s="4"/>
       <c r="E832" s="4"/>
       <c r="F832" s="4"/>
@@ -13697,7 +13694,7 @@
       <c r="N832" s="4"/>
       <c r="O832" s="4"/>
     </row>
-    <row r="833" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="833" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D833" s="4"/>
       <c r="E833" s="4"/>
       <c r="F833" s="4"/>
@@ -13710,7 +13707,7 @@
       <c r="N833" s="4"/>
       <c r="O833" s="4"/>
     </row>
-    <row r="834" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="834" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D834" s="4"/>
       <c r="E834" s="4"/>
       <c r="F834" s="4"/>
@@ -13723,7 +13720,7 @@
       <c r="N834" s="4"/>
       <c r="O834" s="4"/>
     </row>
-    <row r="835" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="835" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D835" s="4"/>
       <c r="E835" s="4"/>
       <c r="F835" s="4"/>
@@ -13736,7 +13733,7 @@
       <c r="N835" s="4"/>
       <c r="O835" s="4"/>
     </row>
-    <row r="836" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="836" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D836" s="4"/>
       <c r="E836" s="4"/>
       <c r="F836" s="4"/>
@@ -13749,7 +13746,7 @@
       <c r="N836" s="4"/>
       <c r="O836" s="4"/>
     </row>
-    <row r="837" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="837" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D837" s="4"/>
       <c r="E837" s="4"/>
       <c r="F837" s="4"/>
@@ -13762,7 +13759,7 @@
       <c r="N837" s="4"/>
       <c r="O837" s="4"/>
     </row>
-    <row r="838" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="838" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D838" s="4"/>
       <c r="E838" s="4"/>
       <c r="F838" s="4"/>
@@ -13775,7 +13772,7 @@
       <c r="N838" s="4"/>
       <c r="O838" s="4"/>
     </row>
-    <row r="839" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="839" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D839" s="4"/>
       <c r="E839" s="4"/>
       <c r="F839" s="4"/>
@@ -13788,7 +13785,7 @@
       <c r="N839" s="4"/>
       <c r="O839" s="4"/>
     </row>
-    <row r="840" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="840" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D840" s="4"/>
       <c r="E840" s="4"/>
       <c r="F840" s="4"/>
@@ -13801,7 +13798,7 @@
       <c r="N840" s="4"/>
       <c r="O840" s="4"/>
     </row>
-    <row r="841" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="841" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D841" s="4"/>
       <c r="E841" s="4"/>
       <c r="F841" s="4"/>
@@ -13814,7 +13811,7 @@
       <c r="N841" s="4"/>
       <c r="O841" s="4"/>
     </row>
-    <row r="842" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="842" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D842" s="4"/>
       <c r="E842" s="4"/>
       <c r="F842" s="4"/>
@@ -13827,7 +13824,7 @@
       <c r="N842" s="4"/>
       <c r="O842" s="4"/>
     </row>
-    <row r="843" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="843" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D843" s="4"/>
       <c r="E843" s="4"/>
       <c r="F843" s="4"/>
@@ -13840,7 +13837,7 @@
       <c r="N843" s="4"/>
       <c r="O843" s="4"/>
     </row>
-    <row r="844" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="844" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D844" s="4"/>
       <c r="E844" s="4"/>
       <c r="F844" s="4"/>
@@ -13853,7 +13850,7 @@
       <c r="N844" s="4"/>
       <c r="O844" s="4"/>
     </row>
-    <row r="845" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="845" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D845" s="4"/>
       <c r="E845" s="4"/>
       <c r="F845" s="4"/>
@@ -13866,7 +13863,7 @@
       <c r="N845" s="4"/>
       <c r="O845" s="4"/>
     </row>
-    <row r="846" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="846" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D846" s="4"/>
       <c r="E846" s="4"/>
       <c r="F846" s="4"/>
@@ -13879,7 +13876,7 @@
       <c r="N846" s="4"/>
       <c r="O846" s="4"/>
     </row>
-    <row r="847" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="847" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D847" s="4"/>
       <c r="E847" s="4"/>
       <c r="F847" s="4"/>
@@ -13892,7 +13889,7 @@
       <c r="N847" s="4"/>
       <c r="O847" s="4"/>
     </row>
-    <row r="848" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="848" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D848" s="4"/>
       <c r="E848" s="4"/>
       <c r="F848" s="4"/>
@@ -13905,7 +13902,7 @@
       <c r="N848" s="4"/>
       <c r="O848" s="4"/>
     </row>
-    <row r="849" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="849" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D849" s="4"/>
       <c r="E849" s="4"/>
       <c r="F849" s="4"/>
@@ -13918,7 +13915,7 @@
       <c r="N849" s="4"/>
       <c r="O849" s="4"/>
     </row>
-    <row r="850" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="850" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D850" s="4"/>
       <c r="E850" s="4"/>
       <c r="F850" s="4"/>
@@ -13931,7 +13928,7 @@
       <c r="N850" s="4"/>
       <c r="O850" s="4"/>
     </row>
-    <row r="851" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="851" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D851" s="4"/>
       <c r="E851" s="4"/>
       <c r="F851" s="4"/>
@@ -13944,7 +13941,7 @@
       <c r="N851" s="4"/>
       <c r="O851" s="4"/>
     </row>
-    <row r="852" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="852" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D852" s="4"/>
       <c r="E852" s="4"/>
       <c r="F852" s="4"/>
@@ -13957,7 +13954,7 @@
       <c r="N852" s="4"/>
       <c r="O852" s="4"/>
     </row>
-    <row r="853" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="853" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D853" s="4"/>
       <c r="E853" s="4"/>
       <c r="F853" s="4"/>
@@ -13970,7 +13967,7 @@
       <c r="N853" s="4"/>
       <c r="O853" s="4"/>
     </row>
-    <row r="854" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="854" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D854" s="4"/>
       <c r="E854" s="4"/>
       <c r="F854" s="4"/>
@@ -13983,7 +13980,7 @@
       <c r="N854" s="4"/>
       <c r="O854" s="4"/>
     </row>
-    <row r="855" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="855" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D855" s="4"/>
       <c r="E855" s="4"/>
       <c r="F855" s="4"/>
@@ -13996,7 +13993,7 @@
       <c r="N855" s="4"/>
       <c r="O855" s="4"/>
     </row>
-    <row r="856" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="856" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D856" s="4"/>
       <c r="E856" s="4"/>
       <c r="F856" s="4"/>
@@ -14009,7 +14006,7 @@
       <c r="N856" s="4"/>
       <c r="O856" s="4"/>
     </row>
-    <row r="857" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="857" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D857" s="4"/>
       <c r="E857" s="4"/>
       <c r="F857" s="4"/>
@@ -14022,7 +14019,7 @@
       <c r="N857" s="4"/>
       <c r="O857" s="4"/>
     </row>
-    <row r="858" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="858" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D858" s="4"/>
       <c r="E858" s="4"/>
       <c r="F858" s="4"/>
@@ -14035,7 +14032,7 @@
       <c r="N858" s="4"/>
       <c r="O858" s="4"/>
     </row>
-    <row r="859" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="859" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D859" s="4"/>
       <c r="E859" s="4"/>
       <c r="F859" s="4"/>
@@ -14048,7 +14045,7 @@
       <c r="N859" s="4"/>
       <c r="O859" s="4"/>
     </row>
-    <row r="860" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="860" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D860" s="4"/>
       <c r="E860" s="4"/>
       <c r="F860" s="4"/>
@@ -14061,7 +14058,7 @@
       <c r="N860" s="4"/>
       <c r="O860" s="4"/>
     </row>
-    <row r="861" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="861" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D861" s="4"/>
       <c r="E861" s="4"/>
       <c r="F861" s="4"/>
@@ -14074,7 +14071,7 @@
       <c r="N861" s="4"/>
       <c r="O861" s="4"/>
     </row>
-    <row r="862" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="862" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D862" s="4"/>
       <c r="E862" s="4"/>
       <c r="F862" s="4"/>
@@ -14087,7 +14084,7 @@
       <c r="N862" s="4"/>
       <c r="O862" s="4"/>
     </row>
-    <row r="863" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="863" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D863" s="4"/>
       <c r="E863" s="4"/>
       <c r="F863" s="4"/>
@@ -14100,7 +14097,7 @@
       <c r="N863" s="4"/>
       <c r="O863" s="4"/>
     </row>
-    <row r="864" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="864" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D864" s="4"/>
       <c r="E864" s="4"/>
       <c r="F864" s="4"/>
@@ -14113,7 +14110,7 @@
       <c r="N864" s="4"/>
       <c r="O864" s="4"/>
     </row>
-    <row r="865" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="865" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D865" s="4"/>
       <c r="E865" s="4"/>
       <c r="F865" s="4"/>
@@ -14126,7 +14123,7 @@
       <c r="N865" s="4"/>
       <c r="O865" s="4"/>
     </row>
-    <row r="866" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="866" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D866" s="4"/>
       <c r="E866" s="4"/>
       <c r="F866" s="4"/>
@@ -14139,7 +14136,7 @@
       <c r="N866" s="4"/>
       <c r="O866" s="4"/>
     </row>
-    <row r="867" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="867" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D867" s="4"/>
       <c r="E867" s="4"/>
       <c r="F867" s="4"/>
@@ -14152,7 +14149,7 @@
       <c r="N867" s="4"/>
       <c r="O867" s="4"/>
     </row>
-    <row r="868" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="868" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D868" s="4"/>
       <c r="E868" s="4"/>
       <c r="F868" s="4"/>
@@ -14165,7 +14162,7 @@
       <c r="N868" s="4"/>
       <c r="O868" s="4"/>
     </row>
-    <row r="869" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="869" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D869" s="4"/>
       <c r="E869" s="4"/>
       <c r="F869" s="4"/>
@@ -14178,7 +14175,7 @@
       <c r="N869" s="4"/>
       <c r="O869" s="4"/>
     </row>
-    <row r="870" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="870" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D870" s="4"/>
       <c r="E870" s="4"/>
       <c r="F870" s="4"/>
@@ -14191,7 +14188,7 @@
       <c r="N870" s="4"/>
       <c r="O870" s="4"/>
     </row>
-    <row r="871" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="871" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D871" s="4"/>
       <c r="E871" s="4"/>
       <c r="F871" s="4"/>
@@ -14204,7 +14201,7 @@
       <c r="N871" s="4"/>
       <c r="O871" s="4"/>
     </row>
-    <row r="872" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="872" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D872" s="4"/>
       <c r="E872" s="4"/>
       <c r="F872" s="4"/>
@@ -14217,7 +14214,7 @@
       <c r="N872" s="4"/>
       <c r="O872" s="4"/>
     </row>
-    <row r="873" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="873" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D873" s="4"/>
       <c r="E873" s="4"/>
       <c r="F873" s="4"/>
@@ -14230,7 +14227,7 @@
       <c r="N873" s="4"/>
       <c r="O873" s="4"/>
     </row>
-    <row r="874" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="874" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D874" s="4"/>
       <c r="E874" s="4"/>
       <c r="F874" s="4"/>
@@ -14243,7 +14240,7 @@
       <c r="N874" s="4"/>
       <c r="O874" s="4"/>
     </row>
-    <row r="875" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="875" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D875" s="4"/>
       <c r="E875" s="4"/>
       <c r="F875" s="4"/>
@@ -14256,7 +14253,7 @@
       <c r="N875" s="4"/>
       <c r="O875" s="4"/>
     </row>
-    <row r="876" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="876" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D876" s="4"/>
       <c r="E876" s="4"/>
       <c r="F876" s="4"/>
@@ -14269,7 +14266,7 @@
       <c r="N876" s="4"/>
       <c r="O876" s="4"/>
     </row>
-    <row r="877" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="877" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D877" s="4"/>
       <c r="E877" s="4"/>
       <c r="F877" s="4"/>
@@ -14282,7 +14279,7 @@
       <c r="N877" s="4"/>
       <c r="O877" s="4"/>
     </row>
-    <row r="878" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="878" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D878" s="4"/>
       <c r="E878" s="4"/>
       <c r="F878" s="4"/>
@@ -14295,7 +14292,7 @@
       <c r="N878" s="4"/>
       <c r="O878" s="4"/>
     </row>
-    <row r="879" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="879" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D879" s="4"/>
       <c r="E879" s="4"/>
       <c r="F879" s="4"/>
@@ -14308,7 +14305,7 @@
       <c r="N879" s="4"/>
       <c r="O879" s="4"/>
     </row>
-    <row r="880" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="880" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D880" s="4"/>
       <c r="E880" s="4"/>
       <c r="F880" s="4"/>
@@ -14321,7 +14318,7 @@
       <c r="N880" s="4"/>
       <c r="O880" s="4"/>
     </row>
-    <row r="881" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="881" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D881" s="4"/>
       <c r="E881" s="4"/>
       <c r="F881" s="4"/>
@@ -14334,7 +14331,7 @@
       <c r="N881" s="4"/>
       <c r="O881" s="4"/>
     </row>
-    <row r="882" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="882" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D882" s="4"/>
       <c r="E882" s="4"/>
       <c r="F882" s="4"/>
@@ -14347,7 +14344,7 @@
       <c r="N882" s="4"/>
       <c r="O882" s="4"/>
     </row>
-    <row r="883" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="883" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D883" s="4"/>
       <c r="E883" s="4"/>
       <c r="F883" s="4"/>
@@ -14360,7 +14357,7 @@
       <c r="N883" s="4"/>
       <c r="O883" s="4"/>
     </row>
-    <row r="884" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="884" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D884" s="4"/>
       <c r="E884" s="4"/>
       <c r="F884" s="4"/>
@@ -14373,7 +14370,7 @@
       <c r="N884" s="4"/>
       <c r="O884" s="4"/>
     </row>
-    <row r="885" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="885" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D885" s="4"/>
       <c r="E885" s="4"/>
       <c r="F885" s="4"/>
@@ -14386,7 +14383,7 @@
       <c r="N885" s="4"/>
       <c r="O885" s="4"/>
     </row>
-    <row r="886" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="886" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D886" s="4"/>
       <c r="E886" s="4"/>
       <c r="F886" s="4"/>
@@ -14399,7 +14396,7 @@
       <c r="N886" s="4"/>
       <c r="O886" s="4"/>
     </row>
-    <row r="887" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="887" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D887" s="4"/>
       <c r="E887" s="4"/>
       <c r="F887" s="4"/>
@@ -14412,7 +14409,7 @@
       <c r="N887" s="4"/>
       <c r="O887" s="4"/>
     </row>
-    <row r="888" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="888" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D888" s="4"/>
       <c r="E888" s="4"/>
       <c r="F888" s="4"/>
@@ -14425,7 +14422,7 @@
       <c r="N888" s="4"/>
       <c r="O888" s="4"/>
     </row>
-    <row r="889" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="889" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D889" s="4"/>
       <c r="E889" s="4"/>
       <c r="F889" s="4"/>
@@ -14438,7 +14435,7 @@
       <c r="N889" s="4"/>
       <c r="O889" s="4"/>
     </row>
-    <row r="890" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="890" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D890" s="4"/>
       <c r="E890" s="4"/>
       <c r="F890" s="4"/>
@@ -14451,7 +14448,7 @@
       <c r="N890" s="4"/>
       <c r="O890" s="4"/>
     </row>
-    <row r="891" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="891" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D891" s="4"/>
       <c r="E891" s="4"/>
       <c r="F891" s="4"/>
@@ -14464,7 +14461,7 @@
       <c r="N891" s="4"/>
       <c r="O891" s="4"/>
     </row>
-    <row r="892" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="892" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D892" s="4"/>
       <c r="E892" s="4"/>
       <c r="F892" s="4"/>
@@ -14477,7 +14474,7 @@
       <c r="N892" s="4"/>
       <c r="O892" s="4"/>
     </row>
-    <row r="893" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="893" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D893" s="4"/>
       <c r="E893" s="4"/>
       <c r="F893" s="4"/>
@@ -14490,7 +14487,7 @@
       <c r="N893" s="4"/>
       <c r="O893" s="4"/>
     </row>
-    <row r="894" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="894" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D894" s="4"/>
       <c r="E894" s="4"/>
       <c r="F894" s="4"/>
@@ -14503,7 +14500,7 @@
       <c r="N894" s="4"/>
       <c r="O894" s="4"/>
     </row>
-    <row r="895" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="895" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D895" s="4"/>
       <c r="E895" s="4"/>
       <c r="F895" s="4"/>
@@ -14516,7 +14513,7 @@
       <c r="N895" s="4"/>
       <c r="O895" s="4"/>
     </row>
-    <row r="896" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="896" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D896" s="4"/>
       <c r="E896" s="4"/>
       <c r="F896" s="4"/>
@@ -14529,7 +14526,7 @@
       <c r="N896" s="4"/>
       <c r="O896" s="4"/>
     </row>
-    <row r="897" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="897" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D897" s="4"/>
       <c r="E897" s="4"/>
       <c r="F897" s="4"/>
@@ -14542,7 +14539,7 @@
       <c r="N897" s="4"/>
       <c r="O897" s="4"/>
     </row>
-    <row r="898" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="898" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D898" s="4"/>
       <c r="E898" s="4"/>
       <c r="F898" s="4"/>
@@ -14555,7 +14552,7 @@
       <c r="N898" s="4"/>
       <c r="O898" s="4"/>
     </row>
-    <row r="899" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="899" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D899" s="4"/>
       <c r="E899" s="4"/>
       <c r="F899" s="4"/>
@@ -14568,7 +14565,7 @@
       <c r="N899" s="4"/>
       <c r="O899" s="4"/>
     </row>
-    <row r="900" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="900" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D900" s="4"/>
       <c r="E900" s="4"/>
       <c r="F900" s="4"/>
@@ -14581,7 +14578,7 @@
       <c r="N900" s="4"/>
       <c r="O900" s="4"/>
     </row>
-    <row r="901" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="901" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D901" s="4"/>
       <c r="E901" s="4"/>
       <c r="F901" s="4"/>
@@ -14594,7 +14591,7 @@
       <c r="N901" s="4"/>
       <c r="O901" s="4"/>
     </row>
-    <row r="902" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="902" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D902" s="4"/>
       <c r="E902" s="4"/>
       <c r="F902" s="4"/>
@@ -14607,7 +14604,7 @@
       <c r="N902" s="4"/>
       <c r="O902" s="4"/>
     </row>
-    <row r="903" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="903" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D903" s="4"/>
       <c r="E903" s="4"/>
       <c r="F903" s="4"/>
@@ -14620,7 +14617,7 @@
       <c r="N903" s="4"/>
       <c r="O903" s="4"/>
     </row>
-    <row r="904" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="904" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D904" s="4"/>
       <c r="E904" s="4"/>
       <c r="F904" s="4"/>
@@ -14633,7 +14630,7 @@
       <c r="N904" s="4"/>
       <c r="O904" s="4"/>
     </row>
-    <row r="905" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="905" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D905" s="4"/>
       <c r="E905" s="4"/>
       <c r="F905" s="4"/>
@@ -14646,7 +14643,7 @@
       <c r="N905" s="4"/>
       <c r="O905" s="4"/>
     </row>
-    <row r="906" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="906" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D906" s="4"/>
       <c r="E906" s="4"/>
       <c r="F906" s="4"/>
@@ -14659,7 +14656,7 @@
       <c r="N906" s="4"/>
       <c r="O906" s="4"/>
     </row>
-    <row r="907" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="907" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D907" s="4"/>
       <c r="E907" s="4"/>
       <c r="F907" s="4"/>
@@ -14672,7 +14669,7 @@
       <c r="N907" s="4"/>
       <c r="O907" s="4"/>
     </row>
-    <row r="908" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="908" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D908" s="4"/>
       <c r="E908" s="4"/>
       <c r="F908" s="4"/>
@@ -14685,7 +14682,7 @@
       <c r="N908" s="4"/>
       <c r="O908" s="4"/>
     </row>
-    <row r="909" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="909" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D909" s="4"/>
       <c r="E909" s="4"/>
       <c r="F909" s="4"/>
@@ -14698,7 +14695,7 @@
       <c r="N909" s="4"/>
       <c r="O909" s="4"/>
     </row>
-    <row r="910" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="910" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D910" s="4"/>
       <c r="E910" s="4"/>
       <c r="F910" s="4"/>
@@ -14711,7 +14708,7 @@
       <c r="N910" s="4"/>
       <c r="O910" s="4"/>
     </row>
-    <row r="911" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="911" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D911" s="4"/>
       <c r="E911" s="4"/>
       <c r="F911" s="4"/>
@@ -14724,7 +14721,7 @@
       <c r="N911" s="4"/>
       <c r="O911" s="4"/>
     </row>
-    <row r="912" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="912" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D912" s="4"/>
       <c r="E912" s="4"/>
       <c r="F912" s="4"/>
@@ -14737,7 +14734,7 @@
       <c r="N912" s="4"/>
       <c r="O912" s="4"/>
     </row>
-    <row r="913" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="913" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D913" s="4"/>
       <c r="E913" s="4"/>
       <c r="F913" s="4"/>
@@ -14750,7 +14747,7 @@
       <c r="N913" s="4"/>
       <c r="O913" s="4"/>
     </row>
-    <row r="914" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="914" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D914" s="4"/>
       <c r="E914" s="4"/>
       <c r="F914" s="4"/>
@@ -14763,7 +14760,7 @@
       <c r="N914" s="4"/>
       <c r="O914" s="4"/>
     </row>
-    <row r="915" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="915" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D915" s="4"/>
       <c r="E915" s="4"/>
       <c r="F915" s="4"/>
@@ -14776,7 +14773,7 @@
       <c r="N915" s="4"/>
       <c r="O915" s="4"/>
     </row>
-    <row r="916" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="916" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D916" s="4"/>
       <c r="E916" s="4"/>
       <c r="F916" s="4"/>
@@ -14789,7 +14786,7 @@
       <c r="N916" s="4"/>
       <c r="O916" s="4"/>
     </row>
-    <row r="917" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="917" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D917" s="4"/>
       <c r="E917" s="4"/>
       <c r="F917" s="4"/>
@@ -14802,7 +14799,7 @@
       <c r="N917" s="4"/>
       <c r="O917" s="4"/>
     </row>
-    <row r="918" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="918" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D918" s="4"/>
       <c r="E918" s="4"/>
       <c r="F918" s="4"/>
@@ -14815,7 +14812,7 @@
       <c r="N918" s="4"/>
       <c r="O918" s="4"/>
     </row>
-    <row r="919" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="919" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D919" s="4"/>
       <c r="E919" s="4"/>
       <c r="F919" s="4"/>
@@ -14828,7 +14825,7 @@
       <c r="N919" s="4"/>
       <c r="O919" s="4"/>
     </row>
-    <row r="920" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="920" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D920" s="4"/>
       <c r="E920" s="4"/>
       <c r="F920" s="4"/>
@@ -14841,7 +14838,7 @@
       <c r="N920" s="4"/>
       <c r="O920" s="4"/>
     </row>
-    <row r="921" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="921" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D921" s="4"/>
       <c r="E921" s="4"/>
       <c r="F921" s="4"/>
@@ -14854,7 +14851,7 @@
       <c r="N921" s="4"/>
       <c r="O921" s="4"/>
     </row>
-    <row r="922" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="922" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D922" s="4"/>
       <c r="E922" s="4"/>
       <c r="F922" s="4"/>
@@ -14867,7 +14864,7 @@
       <c r="N922" s="4"/>
       <c r="O922" s="4"/>
     </row>
-    <row r="923" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="923" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D923" s="4"/>
       <c r="E923" s="4"/>
       <c r="F923" s="4"/>
@@ -14880,7 +14877,7 @@
       <c r="N923" s="4"/>
       <c r="O923" s="4"/>
     </row>
-    <row r="924" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="924" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D924" s="4"/>
       <c r="E924" s="4"/>
       <c r="F924" s="4"/>
@@ -14893,7 +14890,7 @@
       <c r="N924" s="4"/>
       <c r="O924" s="4"/>
     </row>
-    <row r="925" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="925" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D925" s="4"/>
       <c r="E925" s="4"/>
       <c r="F925" s="4"/>
@@ -14906,7 +14903,7 @@
       <c r="N925" s="4"/>
       <c r="O925" s="4"/>
     </row>
-    <row r="926" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="926" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D926" s="4"/>
       <c r="E926" s="4"/>
       <c r="F926" s="4"/>
@@ -14919,7 +14916,7 @@
       <c r="N926" s="4"/>
       <c r="O926" s="4"/>
     </row>
-    <row r="927" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="927" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D927" s="4"/>
       <c r="E927" s="4"/>
       <c r="F927" s="4"/>
@@ -14932,7 +14929,7 @@
       <c r="N927" s="4"/>
       <c r="O927" s="4"/>
     </row>
-    <row r="928" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="928" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D928" s="4"/>
       <c r="E928" s="4"/>
       <c r="F928" s="4"/>
@@ -14945,7 +14942,7 @@
       <c r="N928" s="4"/>
       <c r="O928" s="4"/>
     </row>
-    <row r="929" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="929" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D929" s="4"/>
       <c r="E929" s="4"/>
       <c r="F929" s="4"/>
@@ -14958,7 +14955,7 @@
       <c r="N929" s="4"/>
       <c r="O929" s="4"/>
     </row>
-    <row r="930" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="930" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D930" s="4"/>
       <c r="E930" s="4"/>
       <c r="F930" s="4"/>
@@ -14971,7 +14968,7 @@
       <c r="N930" s="4"/>
       <c r="O930" s="4"/>
     </row>
-    <row r="931" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="931" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D931" s="4"/>
       <c r="E931" s="4"/>
       <c r="F931" s="4"/>
@@ -14984,7 +14981,7 @@
       <c r="N931" s="4"/>
       <c r="O931" s="4"/>
     </row>
-    <row r="932" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="932" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D932" s="4"/>
       <c r="E932" s="4"/>
       <c r="F932" s="4"/>
@@ -14997,7 +14994,7 @@
       <c r="N932" s="4"/>
       <c r="O932" s="4"/>
     </row>
-    <row r="933" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="933" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D933" s="4"/>
       <c r="E933" s="4"/>
       <c r="F933" s="4"/>
@@ -15010,7 +15007,7 @@
       <c r="N933" s="4"/>
       <c r="O933" s="4"/>
     </row>
-    <row r="934" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="934" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D934" s="4"/>
       <c r="E934" s="4"/>
       <c r="F934" s="4"/>
@@ -15023,7 +15020,7 @@
       <c r="N934" s="4"/>
       <c r="O934" s="4"/>
     </row>
-    <row r="935" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="935" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D935" s="4"/>
       <c r="E935" s="4"/>
       <c r="F935" s="4"/>
@@ -15036,7 +15033,7 @@
       <c r="N935" s="4"/>
       <c r="O935" s="4"/>
     </row>
-    <row r="936" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="936" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D936" s="4"/>
       <c r="E936" s="4"/>
       <c r="F936" s="4"/>
@@ -15049,7 +15046,7 @@
       <c r="N936" s="4"/>
       <c r="O936" s="4"/>
     </row>
-    <row r="937" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="937" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D937" s="4"/>
       <c r="E937" s="4"/>
       <c r="F937" s="4"/>
@@ -15062,7 +15059,7 @@
       <c r="N937" s="4"/>
       <c r="O937" s="4"/>
     </row>
-    <row r="938" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="938" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D938" s="4"/>
       <c r="E938" s="4"/>
       <c r="F938" s="4"/>
@@ -15075,7 +15072,7 @@
       <c r="N938" s="4"/>
       <c r="O938" s="4"/>
     </row>
-    <row r="939" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="939" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D939" s="4"/>
       <c r="E939" s="4"/>
       <c r="F939" s="4"/>
@@ -15088,7 +15085,7 @@
       <c r="N939" s="4"/>
       <c r="O939" s="4"/>
     </row>
-    <row r="940" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="940" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D940" s="4"/>
       <c r="E940" s="4"/>
       <c r="F940" s="4"/>
@@ -15101,7 +15098,7 @@
       <c r="N940" s="4"/>
       <c r="O940" s="4"/>
     </row>
-    <row r="941" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="941" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D941" s="4"/>
       <c r="E941" s="4"/>
       <c r="F941" s="4"/>
@@ -15114,7 +15111,7 @@
       <c r="N941" s="4"/>
       <c r="O941" s="4"/>
     </row>
-    <row r="942" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="942" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D942" s="4"/>
       <c r="E942" s="4"/>
       <c r="F942" s="4"/>
@@ -15127,7 +15124,7 @@
       <c r="N942" s="4"/>
       <c r="O942" s="4"/>
     </row>
-    <row r="943" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="943" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D943" s="4"/>
       <c r="E943" s="4"/>
       <c r="F943" s="4"/>
@@ -15140,7 +15137,7 @@
       <c r="N943" s="4"/>
       <c r="O943" s="4"/>
     </row>
-    <row r="944" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="944" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D944" s="4"/>
       <c r="E944" s="4"/>
       <c r="F944" s="4"/>
@@ -15153,7 +15150,7 @@
       <c r="N944" s="4"/>
       <c r="O944" s="4"/>
     </row>
-    <row r="945" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="945" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D945" s="4"/>
       <c r="E945" s="4"/>
       <c r="F945" s="4"/>
@@ -15166,7 +15163,7 @@
       <c r="N945" s="4"/>
       <c r="O945" s="4"/>
     </row>
-    <row r="946" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="946" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D946" s="4"/>
       <c r="E946" s="4"/>
       <c r="F946" s="4"/>
@@ -15179,7 +15176,7 @@
       <c r="N946" s="4"/>
       <c r="O946" s="4"/>
     </row>
-    <row r="947" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="947" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D947" s="4"/>
       <c r="E947" s="4"/>
       <c r="F947" s="4"/>
@@ -15192,7 +15189,7 @@
       <c r="N947" s="4"/>
       <c r="O947" s="4"/>
     </row>
-    <row r="948" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="948" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D948" s="4"/>
       <c r="E948" s="4"/>
       <c r="F948" s="4"/>
@@ -15205,7 +15202,7 @@
       <c r="N948" s="4"/>
       <c r="O948" s="4"/>
     </row>
-    <row r="949" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="949" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D949" s="4"/>
       <c r="E949" s="4"/>
       <c r="F949" s="4"/>
@@ -15218,7 +15215,7 @@
       <c r="N949" s="4"/>
       <c r="O949" s="4"/>
     </row>
-    <row r="950" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="950" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D950" s="4"/>
       <c r="E950" s="4"/>
       <c r="F950" s="4"/>
@@ -15231,7 +15228,7 @@
       <c r="N950" s="4"/>
       <c r="O950" s="4"/>
     </row>
-    <row r="951" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="951" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D951" s="4"/>
       <c r="E951" s="4"/>
       <c r="F951" s="4"/>
@@ -15244,7 +15241,7 @@
       <c r="N951" s="4"/>
       <c r="O951" s="4"/>
     </row>
-    <row r="952" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="952" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D952" s="4"/>
       <c r="E952" s="4"/>
       <c r="F952" s="4"/>
@@ -15257,7 +15254,7 @@
       <c r="N952" s="4"/>
       <c r="O952" s="4"/>
     </row>
-    <row r="953" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="953" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D953" s="4"/>
       <c r="E953" s="4"/>
       <c r="F953" s="4"/>
@@ -15270,7 +15267,7 @@
       <c r="N953" s="4"/>
       <c r="O953" s="4"/>
     </row>
-    <row r="954" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="954" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D954" s="4"/>
       <c r="E954" s="4"/>
       <c r="F954" s="4"/>
@@ -15283,7 +15280,7 @@
       <c r="N954" s="4"/>
       <c r="O954" s="4"/>
     </row>
-    <row r="955" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="955" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D955" s="4"/>
       <c r="E955" s="4"/>
       <c r="F955" s="4"/>
@@ -15296,7 +15293,7 @@
       <c r="N955" s="4"/>
       <c r="O955" s="4"/>
     </row>
-    <row r="956" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="956" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D956" s="4"/>
       <c r="E956" s="4"/>
       <c r="F956" s="4"/>
@@ -15309,7 +15306,7 @@
       <c r="N956" s="4"/>
       <c r="O956" s="4"/>
     </row>
-    <row r="957" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="957" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D957" s="4"/>
       <c r="E957" s="4"/>
       <c r="F957" s="4"/>
@@ -15322,7 +15319,7 @@
       <c r="N957" s="4"/>
       <c r="O957" s="4"/>
     </row>
-    <row r="958" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="958" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D958" s="4"/>
       <c r="E958" s="4"/>
       <c r="F958" s="4"/>
@@ -15335,7 +15332,7 @@
       <c r="N958" s="4"/>
       <c r="O958" s="4"/>
     </row>
-    <row r="959" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="959" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D959" s="4"/>
       <c r="E959" s="4"/>
       <c r="F959" s="4"/>
@@ -15348,7 +15345,7 @@
       <c r="N959" s="4"/>
       <c r="O959" s="4"/>
     </row>
-    <row r="960" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="960" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D960" s="4"/>
       <c r="E960" s="4"/>
       <c r="F960" s="4"/>
@@ -15361,7 +15358,7 @@
       <c r="N960" s="4"/>
       <c r="O960" s="4"/>
     </row>
-    <row r="961" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="961" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D961" s="4"/>
       <c r="E961" s="4"/>
       <c r="F961" s="4"/>
@@ -15374,7 +15371,7 @@
       <c r="N961" s="4"/>
       <c r="O961" s="4"/>
     </row>
-    <row r="962" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="962" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D962" s="4"/>
       <c r="E962" s="4"/>
       <c r="F962" s="4"/>
@@ -15387,7 +15384,7 @@
       <c r="N962" s="4"/>
       <c r="O962" s="4"/>
     </row>
-    <row r="963" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="963" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D963" s="4"/>
       <c r="E963" s="4"/>
       <c r="F963" s="4"/>
@@ -15400,7 +15397,7 @@
       <c r="N963" s="4"/>
       <c r="O963" s="4"/>
     </row>
-    <row r="964" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="964" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D964" s="4"/>
       <c r="E964" s="4"/>
       <c r="F964" s="4"/>
@@ -15413,7 +15410,7 @@
       <c r="N964" s="4"/>
       <c r="O964" s="4"/>
     </row>
-    <row r="965" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="965" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D965" s="4"/>
       <c r="E965" s="4"/>
       <c r="F965" s="4"/>
@@ -15426,7 +15423,7 @@
       <c r="N965" s="4"/>
       <c r="O965" s="4"/>
     </row>
-    <row r="966" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="966" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D966" s="4"/>
       <c r="E966" s="4"/>
       <c r="F966" s="4"/>
@@ -15439,7 +15436,7 @@
       <c r="N966" s="4"/>
       <c r="O966" s="4"/>
     </row>
-    <row r="967" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="967" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D967" s="4"/>
       <c r="E967" s="4"/>
       <c r="F967" s="4"/>
@@ -15452,7 +15449,7 @@
       <c r="N967" s="4"/>
       <c r="O967" s="4"/>
     </row>
-    <row r="968" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="968" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D968" s="4"/>
       <c r="E968" s="4"/>
       <c r="F968" s="4"/>
@@ -15465,7 +15462,7 @@
       <c r="N968" s="4"/>
       <c r="O968" s="4"/>
     </row>
-    <row r="969" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="969" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D969" s="4"/>
       <c r="E969" s="4"/>
       <c r="F969" s="4"/>
@@ -15478,7 +15475,7 @@
       <c r="N969" s="4"/>
       <c r="O969" s="4"/>
     </row>
-    <row r="970" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="970" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D970" s="4"/>
       <c r="E970" s="4"/>
       <c r="F970" s="4"/>
@@ -15491,7 +15488,7 @@
       <c r="N970" s="4"/>
       <c r="O970" s="4"/>
     </row>
-    <row r="971" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="971" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D971" s="4"/>
       <c r="E971" s="4"/>
       <c r="F971" s="4"/>
@@ -15504,7 +15501,7 @@
       <c r="N971" s="4"/>
       <c r="O971" s="4"/>
     </row>
-    <row r="972" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="972" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D972" s="4"/>
       <c r="E972" s="4"/>
       <c r="F972" s="4"/>
@@ -15517,7 +15514,7 @@
       <c r="N972" s="4"/>
       <c r="O972" s="4"/>
     </row>
-    <row r="973" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="973" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D973" s="4"/>
       <c r="E973" s="4"/>
       <c r="F973" s="4"/>
@@ -15530,7 +15527,7 @@
       <c r="N973" s="4"/>
       <c r="O973" s="4"/>
     </row>
-    <row r="974" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="974" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D974" s="4"/>
       <c r="E974" s="4"/>
       <c r="F974" s="4"/>
@@ -15543,7 +15540,7 @@
       <c r="N974" s="4"/>
       <c r="O974" s="4"/>
     </row>
-    <row r="975" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="975" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D975" s="4"/>
       <c r="E975" s="4"/>
       <c r="F975" s="4"/>
@@ -15556,7 +15553,7 @@
       <c r="N975" s="4"/>
       <c r="O975" s="4"/>
     </row>
-    <row r="976" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="976" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D976" s="4"/>
       <c r="E976" s="4"/>
       <c r="F976" s="4"/>
@@ -15569,7 +15566,7 @@
       <c r="N976" s="4"/>
       <c r="O976" s="4"/>
     </row>
-    <row r="977" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="977" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D977" s="4"/>
       <c r="E977" s="4"/>
       <c r="F977" s="4"/>
@@ -15582,7 +15579,7 @@
       <c r="N977" s="4"/>
       <c r="O977" s="4"/>
     </row>
-    <row r="978" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="978" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D978" s="4"/>
       <c r="E978" s="4"/>
       <c r="F978" s="4"/>
@@ -15595,7 +15592,7 @@
       <c r="N978" s="4"/>
       <c r="O978" s="4"/>
     </row>
-    <row r="979" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="979" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D979" s="4"/>
       <c r="E979" s="4"/>
       <c r="F979" s="4"/>
@@ -15608,7 +15605,7 @@
       <c r="N979" s="4"/>
       <c r="O979" s="4"/>
     </row>
-    <row r="980" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="980" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D980" s="4"/>
       <c r="E980" s="4"/>
       <c r="F980" s="4"/>
@@ -15621,7 +15618,7 @@
       <c r="N980" s="4"/>
       <c r="O980" s="4"/>
     </row>
-    <row r="981" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="981" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D981" s="4"/>
       <c r="E981" s="4"/>
       <c r="F981" s="4"/>
@@ -15634,7 +15631,7 @@
       <c r="N981" s="4"/>
       <c r="O981" s="4"/>
     </row>
-    <row r="982" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="982" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D982" s="4"/>
       <c r="E982" s="4"/>
       <c r="F982" s="4"/>
@@ -15647,7 +15644,7 @@
       <c r="N982" s="4"/>
       <c r="O982" s="4"/>
     </row>
-    <row r="983" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="983" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D983" s="4"/>
       <c r="E983" s="4"/>
       <c r="F983" s="4"/>
@@ -15660,7 +15657,7 @@
       <c r="N983" s="4"/>
       <c r="O983" s="4"/>
     </row>
-    <row r="984" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="984" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D984" s="4"/>
       <c r="E984" s="4"/>
       <c r="F984" s="4"/>
@@ -15673,7 +15670,7 @@
       <c r="N984" s="4"/>
       <c r="O984" s="4"/>
     </row>
-    <row r="985" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="985" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D985" s="4"/>
       <c r="E985" s="4"/>
       <c r="F985" s="4"/>
@@ -15686,7 +15683,7 @@
       <c r="N985" s="4"/>
       <c r="O985" s="4"/>
     </row>
-    <row r="986" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="986" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D986" s="4"/>
       <c r="E986" s="4"/>
       <c r="F986" s="4"/>
@@ -15699,7 +15696,7 @@
       <c r="N986" s="4"/>
       <c r="O986" s="4"/>
     </row>
-    <row r="987" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="987" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D987" s="4"/>
       <c r="E987" s="4"/>
       <c r="F987" s="4"/>
@@ -15712,7 +15709,7 @@
       <c r="N987" s="4"/>
       <c r="O987" s="4"/>
     </row>
-    <row r="988" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="988" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D988" s="4"/>
       <c r="E988" s="4"/>
       <c r="F988" s="4"/>
@@ -15725,7 +15722,7 @@
       <c r="N988" s="4"/>
       <c r="O988" s="4"/>
     </row>
-    <row r="989" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="989" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D989" s="4"/>
       <c r="E989" s="4"/>
       <c r="F989" s="4"/>
@@ -15738,7 +15735,7 @@
       <c r="N989" s="4"/>
       <c r="O989" s="4"/>
     </row>
-    <row r="990" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="990" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D990" s="4"/>
       <c r="E990" s="4"/>
       <c r="F990" s="4"/>
@@ -15751,7 +15748,7 @@
       <c r="N990" s="4"/>
       <c r="O990" s="4"/>
     </row>
-    <row r="991" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="991" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D991" s="4"/>
       <c r="E991" s="4"/>
       <c r="F991" s="4"/>
@@ -15764,7 +15761,7 @@
       <c r="N991" s="4"/>
       <c r="O991" s="4"/>
     </row>
-    <row r="992" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="992" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D992" s="4"/>
       <c r="E992" s="4"/>
       <c r="F992" s="4"/>
@@ -15777,7 +15774,7 @@
       <c r="N992" s="4"/>
       <c r="O992" s="4"/>
     </row>
-    <row r="993" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="993" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D993" s="4"/>
       <c r="E993" s="4"/>
       <c r="F993" s="4"/>
@@ -15790,7 +15787,7 @@
       <c r="N993" s="4"/>
       <c r="O993" s="4"/>
     </row>
-    <row r="994" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="994" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D994" s="4"/>
       <c r="E994" s="4"/>
       <c r="F994" s="4"/>
@@ -15803,7 +15800,7 @@
       <c r="N994" s="4"/>
       <c r="O994" s="4"/>
     </row>
-    <row r="995" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="995" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D995" s="4"/>
       <c r="E995" s="4"/>
       <c r="F995" s="4"/>
@@ -15816,7 +15813,7 @@
       <c r="N995" s="4"/>
       <c r="O995" s="4"/>
     </row>
-    <row r="996" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="996" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D996" s="4"/>
       <c r="E996" s="4"/>
       <c r="F996" s="4"/>
@@ -15829,7 +15826,7 @@
       <c r="N996" s="4"/>
       <c r="O996" s="4"/>
     </row>
-    <row r="997" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="997" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D997" s="4"/>
       <c r="E997" s="4"/>
       <c r="F997" s="4"/>
@@ -15842,7 +15839,7 @@
       <c r="N997" s="4"/>
       <c r="O997" s="4"/>
     </row>
-    <row r="998" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="998" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D998" s="4"/>
       <c r="E998" s="4"/>
       <c r="F998" s="4"/>
@@ -15855,7 +15852,7 @@
       <c r="N998" s="4"/>
       <c r="O998" s="4"/>
     </row>
-    <row r="999" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="999" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D999" s="4"/>
       <c r="E999" s="4"/>
       <c r="F999" s="4"/>
@@ -15868,7 +15865,7 @@
       <c r="N999" s="4"/>
       <c r="O999" s="4"/>
     </row>
-    <row r="1000" spans="4:15" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="1000" spans="4:15" ht="12.75" x14ac:dyDescent="0.2">
       <c r="D1000" s="4"/>
       <c r="E1000" s="4"/>
       <c r="F1000" s="4"/>

--- a/datos/Malla_Curricular_LLYA.xlsx
+++ b/datos/Malla_Curricular_LLYA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consumo_horas_educacion_secundaria\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024B4E04-5757-437C-BE6D-35C849F1C0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98CB854-F388-40C5-9E72-010A40BBEC95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,15 +20,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -37,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="91">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -781,18 +772,16 @@
         <v>20</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>2</v>
       </c>
       <c r="L4" s="4">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>21</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M4" s="5"/>
       <c r="N4" s="5" t="s">
         <v>21</v>
       </c>

--- a/datos/Malla_Curricular_LLYA.xlsx
+++ b/datos/Malla_Curricular_LLYA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consumo_horas_educacion_secundaria\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98CB854-F388-40C5-9E72-010A40BBEC95}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262D75B8-1845-48EA-99AD-D1B3DCE8DEDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="91">
   <si>
     <t>PROGRAMA</t>
   </si>
@@ -588,10 +588,9 @@
     <col min="1" max="1" width="20.140625" customWidth="1"/>
     <col min="2" max="2" width="23.140625" customWidth="1"/>
     <col min="3" max="3" width="36.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="8" width="18" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="5" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" customWidth="1"/>
     <col min="10" max="10" width="18.28515625" customWidth="1"/>
     <col min="11" max="11" width="19.7109375" customWidth="1"/>
@@ -1760,18 +1759,16 @@
         <v>20</v>
       </c>
       <c r="J25" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25" s="5">
         <v>2</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>21</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="M25" s="5"/>
       <c r="N25" s="5" t="s">
         <v>21</v>
       </c>

--- a/datos/Malla_Curricular_LLYA.xlsx
+++ b/datos/Malla_Curricular_LLYA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consumo_horas_educacion_secundaria\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{262D75B8-1845-48EA-99AD-D1B3DCE8DEDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE49ACF-1D0A-458B-A11E-DEEB9370E010}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3320,7 +3320,7 @@
         <v>28</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J58" s="5">
         <v>2</v>
@@ -3333,10 +3333,10 @@
         <v>4</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="N58" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="O58" s="5" t="s">
         <v>22</v>
@@ -15865,6 +15865,7 @@
       <c r="O1000" s="4"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O66" xr:uid="{437749D5-0DDE-4276-9DD6-17B2BC08D6F2}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>